--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -1101,7 +1101,7 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>illustrative</t>
+          <t>disabled</t>
         </is>
       </c>
       <c r="BB2" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>DreamFinder collects your name, email, and optional phone number to deliver your mattress recommendations and Savings Pass. Your information is only used for this purpose and is never sold or shared with third parties.</t>
+          <t>DreamFinder collects your name, email, and optional phone number to deliver your mattress recommendations. Your information is only used for this purpose and is never sold. DreamFinder does not send your information to lenders. If you choose to open Lacks' financing or application pages, you continue on lacks.com — a separate secure site governed by its own privacy terms.</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>DreamFinder is a product recommendation tool. Match percentages and Sleep Brief guidance are generated from your quiz answers and should be treated as starting points, not guarantees. This tool does not provide medical advice — consult a healthcare provider for medical sleep concerns. Discounts and product availability are subject to Lacks Furniture store terms.</t>
+          <t>DreamFinder is a product recommendation tool. Match percentages and Sleep Brief guidance are generated from your quiz answers and should be treated as starting points, not guarantees. This tool does not provide medical advice — consult a healthcare provider for medical sleep concerns. Payment options, pricing, and product availability are subject to Lacks Furniture store terms and approval.</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr"/>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>DreamFinder recopila tu nombre, correo electrónico y número de teléfono opcional para enviarte tus recomendaciones de colchón y tu Pase de Ahorro. Tu información se usa únicamente para este fin y nunca se vende ni se comparte con terceros.</t>
+          <t>DreamFinder recopila tu nombre, correo electrónico y número de teléfono opcional para enviarte tus recomendaciones de colchón. Tu información se usa únicamente para este fin y nunca se vende. DreamFinder no envía tu información a prestamistas. Si decides abrir las páginas de financiamiento o solicitud de Lacks, continúas en lacks.com — un sitio seguro aparte, regido por sus propios términos de privacidad.</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>DreamFinder es una herramienta de recomendación de productos. Los porcentajes de compatibilidad y la guía del Resumen de Sueño se generan a partir de tus respuestas y deben tomarse como punto de partida, no como garantía. Esta herramienta no ofrece asesoramiento médico — consulta a un profesional de la salud para problemas médicos del sueño. Los descuentos y la disponibilidad de productos están sujetos a los términos de las tiendas Lacks Furniture.</t>
+          <t>DreamFinder es una herramienta de recomendación de productos. Los porcentajes de compatibilidad y la guía del Resumen de Sueño se generan a partir de tus respuestas y deben tomarse como punto de partida, no como garantía. Esta herramienta no ofrece asesoramiento médico — consulta a un profesional de la salud para problemas médicos del sueño. Las opciones de pago, los precios y la disponibilidad de productos están sujetos a los términos de las tiendas Lacks Furniture y a aprobación.</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>Sleep Brief · Mattress Matches · Sleep System Picks · Savings Pass</t>
+          <t>Sleep Brief · Mattress Matches · Sleep System Picks · Payment Choices</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>Resumen de Sueño · Opciones de Colchón · Sistema de Sueño · Pase de Ahorro</t>
+          <t>Resumen de Sueño · Opciones de Colchón · Sistema de Sueño · Opciones de Pago</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -6606,13 +6606,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>Promotions JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-30T10:53:32-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue privately on your phone — scan to open Lacks' official financing page.","es":"Continúa en privado desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"externalNotice":{"en":"Opens lacks.com — a separate secure site governed by its own privacy terms.","es":"Abre lacks.com — un sitio seguro aparte, regido por sus propios términos de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"An available path if past credit has been difficult. Lease-to-own is not conventional financing. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"Una opción disponible si el crédito ha sido difícil en el pasado. El arrendamiento con opción a compra no es financiamiento convencional. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"Details and application on Lacks' official pages. This program is offered to any customer purchasing for delivery to Mexico and is never suggested based on language.","es":"Detalles y solicitud en las páginas oficiales de Lacks. Este programa se ofrece a cualquier cliente que compre para entrega en México y nunca se sugiere por el idioma."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6619,7 +6619,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-30T10:53:32-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue privately on your phone — scan to open Lacks' official financing page.","es":"Continúa en privado desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"externalNotice":{"en":"Opens lacks.com — a separate secure site governed by its own privacy terms.","es":"Abre lacks.com — un sitio seguro aparte, regido por sus propios términos de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"An available path if past credit has been difficult. Lease-to-own is not conventional financing. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"Una opción disponible si el crédito ha sido difícil en el pasado. El arrendamiento con opción a compra no es financiamiento convencional. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"Details and application on Lacks' official pages. This program is offered to any customer purchasing for delivery to Mexico and is never suggested based on language.","es":"Detalles y solicitud en las páginas oficiales de Lacks. Este programa se ofrece a cualquier cliente que compre para entrega en México y nunca se sugiere por el idioma."}}]}}</t>
+          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-30T10:53:32-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue privately on your phone — scan to open Lacks' official financing page.","es":"Continúa en privado desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"externalNotice":{"en":"Opens lacks.com — a separate secure site governed by its own privacy terms.","es":"Abre lacks.com — un sitio seguro aparte, regido por sus propios términos de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"An available path if past credit has been difficult. Lease-to-own is not conventional financing. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"Una opción disponible si el crédito ha sido difícil en el pasado. El arrendamiento con opción a compra no es financiamiento convencional. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"Details and application on Lacks' official pages. This program is offered to any customer purchasing for delivery to Mexico and is never suggested based on language.","es":"Detalles y solicitud en las páginas oficiales de Lacks. Este programa se ofrece a cualquier cliente que compre para entrega en México y nunca se sugiere por el idioma."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6619,7 +6619,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-30T10:53:32-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue privately on your phone — scan to open Lacks' official financing page.","es":"Continúa en privado desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"externalNotice":{"en":"Opens lacks.com — a separate secure site governed by its own privacy terms.","es":"Abre lacks.com — un sitio seguro aparte, regido por sus propios términos de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"An available path if past credit has been difficult. Lease-to-own is not conventional financing. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"Una opción disponible si el crédito ha sido difícil en el pasado. El arrendamiento con opción a compra no es financiamiento convencional. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-30T10:53:32-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"Details and application on Lacks' official pages. This program is offered to any customer purchasing for delivery to Mexico and is never suggested based on language.","es":"Detalles y solicitud en las páginas oficiales de Lacks. Este programa se ofrece a cualquier cliente que compre para entrega en México y nunca se sugiere por el idioma."}}]}}</t>
+          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue privately on your phone — scan to open Lacks' official financing page.","es":"Continúa en privado desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"externalNotice":{"en":"Opens lacks.com — a separate secure site governed by its own privacy terms.","es":"Abre lacks.com — un sitio seguro aparte, regido por sus propios términos de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"An available path if past credit has been difficult. Lease-to-own is not conventional financing. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"Una opción disponible si el crédito ha sido difícil en el pasado. El arrendamiento con opción a compra no es financiamiento convencional. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"Details and application on Lacks' official pages. This program is offered to any customer purchasing for delivery to Mexico and is never suggested based on language.","es":"Detalles y solicitud en las páginas oficiales de Lacks. Este programa se ofrece a cualquier cliente que compre para entrega en México y nunca se sugiere por el idioma."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6619,7 +6619,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue privately on your phone — scan to open Lacks' official financing page.","es":"Continúa en privado desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"externalNotice":{"en":"Opens lacks.com — a separate secure site governed by its own privacy terms.","es":"Abre lacks.com — un sitio seguro aparte, regido por sus propios términos de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"An available path if past credit has been difficult. Lease-to-own is not conventional financing. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"Una opción disponible si el crédito ha sido difícil en el pasado. El arrendamiento con opción a compra no es financiamiento convencional. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"Details and application on Lacks' official pages. This program is offered to any customer purchasing for delivery to Mexico and is never suggested based on language.","es":"Detalles y solicitud en las páginas oficiales de Lacks. Este programa se ofrece a cualquier cliente que compre para entrega en México y nunca se sugiere por el idioma."}}]}}</t>
+          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue privately on your phone — scan to open Lacks' official financing page.","es":"Continúa en privado desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate secure site governed by its own privacy terms.","es":"Abre lacks.com — un sitio seguro aparte, regido por sus propios términos de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"An available path if past credit has been difficult. Lease-to-own is not conventional financing. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"Una opción disponible si el crédito ha sido difícil en el pasado. El arrendamiento con opción a compra no es financiamiento convencional. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"Details and application on Lacks' official pages. This program is offered to any customer purchasing for delivery to Mexico and is never suggested based on language.","es":"Detalles y solicitud en las páginas oficiales de Lacks. Este programa se ofrece a cualquier cliente que compre para entrega en México y nunca se sugiere por el idioma."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Quiz" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6626,4 +6627,32 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Quiz JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{"quiz":{"questions":[{"id":"sleep_quality","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"How well do you sleep right now?","es":"¿Qué tan bien duermes actualmente?"},"helpText":{"en":"Be honest. It helps us solve the real problem, not guess.","es":"Sé honesto — podemos ayudarte de cualquier manera"},"type":"single","options":[{"id":"poor","label":{"en":"Poorly","es":"Mal"},"icon":"stiff","sublabel":{"en":"Restless, waking often","es":"Inquieto, despertando seguido"},"scores":{}},{"id":"fair","label":{"en":"Not Great","es":"No Muy Bien"},"icon":"combo","sublabel":{"en":"Could be a lot better","es":"Podría ser mucho mejor"},"scores":{}},{"id":"okay","label":{"en":"Okay","es":"Más o Menos"},"icon":"smile","sublabel":{"en":"Mostly fine","es":"Generalmente bien"},"scores":{}},{"id":"well","label":{"en":"Pretty Well","es":"Bastante Bien"},"icon":"check","sublabel":{"en":"Usually rested","es":"Generalmente descansado"},"scores":{}}]},{"id":"trigger","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What can we help you with today?","es":"¿En qué te podemos ayudar hoy?"},"helpText":{"en":"No pressure — this just helps your specialist focus on what matters to you.","es":"Sin presión — esto ayuda a tu especialista a enfocarse en lo que te importa."},"type":"single","options":[{"id":"pain","label":{"en":"Back or Body Pain","es":"Dolor de Espalda o Cuerpo"},"icon":"spine","sublabel":{"en":"Current mattress is hurting me","es":"Mi colchón actual me lastima"},"scores":{}},{"id":"worn_out","label":{"en":"Old Mattress","es":"Colchón Viejo"},"icon":"sagging","sublabel":{"en":"Time for an upgrade","es":"Es hora de un cambio"},"scores":{}},{"id":"moving","label":{"en":"Moving or New Space","es":"Mudanza o Espacio Nuevo"},"icon":"family","sublabel":{"en":"New home, new bed","es":"Casa nueva, cama nueva"},"scores":{}},{"id":"upgrade","label":{"en":"Just Upgrading","es":"Mejorando"},"icon":"cloud","sublabel":{"en":"Ready for something better","es":"Listo para algo mejor"},"scores":{}},{"id":"browsing","label":{"en":"Just Browsing","es":"Solo Explorando"},"icon":"smile","sublabel":{"en":"Getting ideas, no rush","es":"Sin prisa, juntando ideas"},"scores":{}}]},{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"So every mattress we show actually fits your space.","es":"Nos aseguraremos de que las recomendaciones se ajusten a tu espacio"},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"Who shares your bed shapes which features matter most.","es":"Esto determina qué características importan más"},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"Motion isolation is one of the first upgrades you'll feel.","es":"El aislamiento de movimiento es una de las mayores mejoras en un colchón nuevo"},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"Your sleep position is the biggest clue to the support you need.","es":"Piensa en cómo terminas naturalmente"},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"Sleeping hot or cold is an easy fix with the right materials.","es":"La regulación de temperatura es clave para un sueño profundo"},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to what feels best.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"current_mattress_age","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"How old is your current mattress?","es":"¿Cuántos años tiene tu colchón actual?"},"helpText":{"en":"Most mattresses lose their support after about 8 years.","es":"La mayoría de los colchones duran 7–10 años"},"type":"single","options":[{"id":"under_2","label":{"en":"Less Than 2 Years","es":"Menos de 2 Años"},"icon":"check","sublabel":{"en":"Pretty new","es":"Bastante nuevo"},"scores":{}},{"id":"three_seven","label":{"en":"3 to 7 Years","es":"3 a 7 Años"},"icon":"combo","sublabel":{"en":"Middle of its life","es":"A mitad de su vida"},"scores":{}},{"id":"eight_fifteen","label":{"en":"8 to 15 Years","es":"8 a 15 Años"},"icon":"aging","sublabel":{"en":"Past its prime","es":"Ya pasó su mejor momento"},"scores":{}},{"id":"fifteen_plus","label":{"en":"Over 15 Years","es":"Más de 15 Años"},"icon":"sagging","sublabel":{"en":"Long overdue","es":"Ya era hora"},"scores":{}},{"id":"not_sure","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"Can't remember","es":"No recuerdo"},"scores":{}}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. Each one points us toward a fix.","es":"Toca las que apliquen"},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durable":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. A few of these change what we'd suggest.","es":"Toca las que apliquen"},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durable":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>DreamFinder collects your name, email, and optional phone number to deliver your mattress recommendations. Your information is only used for this purpose and is never sold. DreamFinder does not send your information to lenders. If you choose to open Lacks' financing or application pages, you continue on lacks.com — a separate secure site governed by its own privacy terms.</t>
+          <t>DreamFinder collects your name, email, and optional phone number to deliver your mattress recommendations. Your information is only used for this purpose and is never sold. DreamFinder does not send your information to lenders. If you choose to open Lacks' financing or application pages, you continue on lacks.com — a separate site governed by its own terms and privacy policy.</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>DreamFinder recopila tu nombre, correo electrónico y número de teléfono opcional para enviarte tus recomendaciones de colchón. Tu información se usa únicamente para este fin y nunca se vende. DreamFinder no envía tu información a prestamistas. Si decides abrir las páginas de financiamiento o solicitud de Lacks, continúas en lacks.com — un sitio seguro aparte, regido por sus propios términos de privacidad.</t>
+          <t>DreamFinder recopila tu nombre, correo electrónico y número de teléfono opcional para enviarte tus recomendaciones de colchón. Tu información se usa únicamente para este fin y nunca se vende. DreamFinder no envía tu información a prestamistas. Si decides abrir las páginas de financiamiento o solicitud de Lacks, continúas en lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad.</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -6620,7 +6620,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue privately on your phone — scan to open Lacks' official financing page.","es":"Continúa en privado desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate secure site governed by its own privacy terms.","es":"Abre lacks.com — un sitio seguro aparte, regido por sus propios términos de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"An available path if past credit has been difficult. Lease-to-own is not conventional financing. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"Una opción disponible si el crédito ha sido difícil en el pasado. El arrendamiento con opción a compra no es financiamiento convencional. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"Details and application on Lacks' official pages. This program is offered to any customer purchasing for delivery to Mexico and is never suggested based on language.","es":"Detalles y solicitud en las páginas oficiales de Lacks. Este programa se ofrece a cualquier cliente que compre para entrega en México y nunca se sugiere por el idioma."}}]}}</t>
+          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"interestMarkedAnnounce":{"en":"Marked for your specialist. Nothing is submitted and no application is started.","es":"Marcado para tu especialista. No se envía nada y no se inicia ninguna solicitud."},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6620,7 +6620,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"interestMarkedAnnounce":{"en":"Marked for your specialist. Nothing is submitted and no application is started.","es":"Marcado para tu especialista. No se envía nada y no se inicia ninguna solicitud."},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
+          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"interestMarkedAnnounce":{"en":"Marked for your specialist. Nothing is submitted and no application is started.","es":"Marcado para tu especialista. No se envía nada y no se inicia ninguna solicitud."},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6620,7 +6620,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"interestMarkedAnnounce":{"en":"Marked for your specialist. Nothing is submitted and no application is started.","es":"Marcado para tu especialista. No se envía nada y no se inicia ninguna solicitud."},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","separatePath":true,"verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
+          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"interestMarkedAnnounce":{"en":"Marked for your specialist. Nothing is submitted and no application is started.","es":"Marcado para tu especialista. No se envía nada y no se inicia ninguna solicitud."},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Brands" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Quiz" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brands" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quiz" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6620,7 +6620,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"ctaSecondary":{"en":"Review with a Lacks specialist","es":"Revisar con un especialista de Lacks"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Ask my specialist","es":"Preguntar a mi especialista"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Discuss payment options","es":"Conversar opciones de pago"},"drawerMarked":{"en":"Marked to discuss","es":"Marcado para conversar"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"interestPrompt":{"en":"Would you like to review flexible payment options with your Lacks specialist?","es":"¿Te gustaría revisar opciones de pago flexibles con un especialista de Lacks?"},"interestYes":{"en":"Yes, I'm interested","es":"Sí, me interesa"},"interestNotNow":{"en":"Not right now","es":"Ahora no"},"interestMarkedAnnounce":{"en":"Marked for your specialist. Nothing is submitted and no application is started.","es":"Marcado para tu especialista. No se envía nada y no se inicia ninguna solicitud."},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
+          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Plan the conversation","es":"Planear la conversación"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Plan the conversation","es":"Planear la conversación"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"agendaPrompt":{"en":"As you review these together, mark any options the customer wants to discuss.","es":"Mientras revisan estas opciones juntos, marca las opciones de pago que el cliente quiera conversar."},"agendaMark":{"en":"Add to discussion","es":"Agregar a la conversación"},"agendaMarked":{"en":"Added to discussion","es":"Agregado a la conversación"},"agendaEmpty":{"en":"No options are marked yet.","es":"Todavía no hay opciones de pago marcadas."},"agendaConsequence":{"en":"Use this agenda to guide the conversation together. Nothing is submitted and no application is started.","es":"Usen esta agenda para guiar la conversación juntos. No se envía nada y no se inicia ninguna solicitud."},"agendaChange":{"en":"Change discussion agenda","es":"Cambiar agenda de conversación"},"agendaNotNow":{"en":"Not right now","es":"Ahora no"},"agendaDismissed":{"en":"No options marked for review right now.","es":"No hay opciones de pago marcadas para revisar por ahora."},"agendaDone":{"en":"Done","es":"Listo"},"interestMarkedAnnounce":{"en":"Added to the discussion. Nothing is submitted and no application is started.","es":"Agregado a la conversación. No se envía nada y no se inicia ninguna solicitud."},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brands" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quiz" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Brands" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Quiz" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6620,7 +6620,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Plan the conversation","es":"Planear la conversación"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Plan the conversation","es":"Planear la conversación"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"agendaPrompt":{"en":"As you review these together, mark any options the customer wants to discuss.","es":"Mientras revisan estas opciones juntos, marca las opciones de pago que el cliente quiera conversar."},"agendaMark":{"en":"Add to discussion","es":"Agregar a la conversación"},"agendaMarked":{"en":"Added to discussion","es":"Agregado a la conversación"},"agendaEmpty":{"en":"No options are marked yet.","es":"Todavía no hay opciones de pago marcadas."},"agendaConsequence":{"en":"Use this agenda to guide the conversation together. Nothing is submitted and no application is started.","es":"Usen esta agenda para guiar la conversación juntos. No se envía nada y no se inicia ninguna solicitud."},"agendaChange":{"en":"Change discussion agenda","es":"Cambiar agenda de conversación"},"agendaNotNow":{"en":"Not right now","es":"Ahora no"},"agendaDismissed":{"en":"No options marked for review right now.","es":"No hay opciones de pago marcadas para revisar por ahora."},"agendaDone":{"en":"Done","es":"Listo"},"interestMarkedAnnounce":{"en":"Added to the discussion. Nothing is submitted and no application is started.","es":"Agregado a la conversación. No se envía nada y no se inicia ninguna solicitud."},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
+          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Plan the conversation","es":"Planear la conversación"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Plan the conversation","es":"Planear la conversación"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"agendaPrompt":{"en":"As you review these together, mark any options the customer wants to discuss.","es":"Mientras revisan estas opciones juntos, marca las opciones de pago que el cliente quiera conversar."},"agendaMark":{"en":"Add to discussion","es":"Agregar a la conversación"},"agendaMarked":{"en":"Added to discussion","es":"Agregado a la conversación"},"agendaEmpty":{"en":"No options are marked yet.","es":"Todavía no hay opciones de pago marcadas."},"agendaConsequence":{"en":"Use this agenda to guide the conversation together. Nothing is submitted and no application is started.","es":"Usen esta agenda para guiar la conversación juntos. No se envía nada y no se inicia ninguna solicitud."},"agendaChange":{"en":"Change discussion agenda","es":"Cambiar agenda de conversación"},"agendaNotNow":{"en":"Not right now","es":"Ahora no"},"agendaDismissed":{"en":"No options marked for review right now.","es":"No hay opciones de pago marcadas para revisar por ahora."},"agendaDone":{"en":"Done","es":"Listo"},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6371,7 +6371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6417,27 +6417,37 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Implication</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Lead (ES)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Demo (ES)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Close (ES)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>RSA Note (ES)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Story (ES)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Implication (ES)</t>
         </is>
       </c>
     </row>
@@ -6466,11 +6476,13 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>Fabricado localmente en Texas y nombrado Best Buy por Consumers Digest año tras año, el Marvelous Middle de Restonic construye 25% más soporte en el tercio central de cada cama — donde el soporte más importa.</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6497,11 +6509,13 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>Chattam &amp; Wells es lujo artesanal construido por los mejores artesanos de Restonic — lana Merino, cachemira y látex de grafito sobre resortes de precisión para un descanso de calidad heredable.</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6528,11 +6542,13 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>La colección Copper patentada de Spring Air combina la tela de cobre NatuVerex con espumas infundidas de cobre para un descanso más fresco y saludable.</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6559,11 +6575,13 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Desarrollado a partir del material de alivio de presión diseñado por la NASA, Tempur-Pedic es el referente del confort adaptable, la innovación en frescura y la cero transferencia de movimiento.</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6590,9 +6608,1076 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Genesis de Kingdom Mattress está diseñado completamente en EE. UU. por una empresa familiar de 30 años — confort honesto y duradero hecho para la vida familiar real.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sleep_quality.poor</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>aiming for a real change in nightly rest</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>buscando un cambio real en el descanso</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sleep_quality.fair</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>aiming to sleep noticeably better</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>buscando dormir notablemente mejor</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sleep_quality.okay</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>building on what already works</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>mejorando lo que ya funciona</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sleep_quality.well</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>protecting a setup that already works</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>cuidando un descanso que ya funciona</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>trigger.pain</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>here to solve a comfort problem</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>aquí para resolver un problema de comodidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>trigger.worn_out</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>replacing an old mattress</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>reemplazando un colchón viejo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>trigger.moving</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>furnishing a new space</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>amueblando un espacio nuevo</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>trigger.upgrade</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ready for an upgrade</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>buscando una mejora</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>trigger.browsing</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>exploring options today</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>explorando opciones hoy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sleep_issues.back_pain</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>test lower-back support carefully</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>probar con cuidado el soporte lumbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sleep_issues.hip_pain</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>focus on pressure relief at hips and shoulders</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>enfocarse en aliviar la presión en caderas y hombros</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sleep_issues.hot</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>prioritize temperature control</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>priorizar el control de temperatura</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sleep_issues.tossing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>notice how easy it is to settle in</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>notar qué tan fácil es acomodarse</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sleep_issues.stiff</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>compare alignment and morning comfort</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>comparar la alineación y la comodidad al despertar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>sleep_issues.sagging</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>check for durable, consistent support</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>revisar que el soporte sea duradero y consistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sleep_issues.too_soft</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>try firmer, more supportive feels</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>probar sensaciones más firmes y con más soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>sleep_issues.none</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sleep_position.side</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>prioritize shoulder and hip cushioning</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>priorizar el acolchado de hombros y caderas</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sleep_position.back</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>look for even lumbar support</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>buscar soporte lumbar uniforme</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sleep_position.stomach</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>keep the midsection supported</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>mantener la zona media con soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sleep_position.combo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>notice ease of movement between positions</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>notar la facilidad para cambiar de posición</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sleep_position.no_idea</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>compare a few different feels to find a starting point</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>comparar varias sensaciones para encontrar un punto de partida</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>health_conditions.nerve_pain</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>compare gentle, even pressure relief</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>comparar un alivio de presión suave y uniforme</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>health_conditions.allergies</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ask about washable and protective covers</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>preguntar por fundas lavables y protectoras</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>health_conditions.snoring</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>test head-of-bed elevation on an adjustable base</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>probar la elevación de la cabecera en una base ajustable</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>health_conditions.reflux</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>notice how a raised upper body feels</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>notar cómo se siente el torso elevado</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>health_conditions.extra_support</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>prioritize reinforced, sturdy support</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>priorizar un soporte reforzado y resistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>health_conditions.getting_older</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>compare ease of getting in and out of bed</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>comparar la facilidad para acostarse y levantarse</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>health_conditions.none</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>temperature.hot</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>compare cooling covers and airflow</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>comparar fundas frescas y ventilación</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>temperature.comfortable</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>temperature.cold</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>notice warmth and cozier surface feels</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>notar calidez y superficies más acogedoras</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>consultation</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>temperature.opposite</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>compare temperature balance for two sleepers</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>comparar el equilibrio de temperatura para dos personas</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Brands" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Quiz" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brands" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quiz" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1180,7 +1180,7 @@
       <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>McAllen · Pharr · Harlingen · Brownsville · Rio Grande City · Laredo · Alice · Corpus Christi</t>
+          <t>Brownsville · Laredo · McAllen · Alice · Harlingen · Rio Grande City</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brands" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quiz" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Store Info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Brands" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Mattresses" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Accessories" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Quiz" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1784,11 +1784,7 @@
           <t>Luxury Natural Fibers|Plush|Euro-Top</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Our most indulgent plush — wool, cashmere, and 16.5 inches of luxury</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1812,21 +1808,13 @@
           <t>A deep plush euro-top of wool and cashmere over layered coils — indulgent softness that never loses its support.</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>The most luxurious plush in the store — natural fibers over layered coil support.</t>
-        </is>
-      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
           <t>Deep plush euro-top</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>A sink-in soft surface for side sleepers who want cloud comfort without bottoming out.</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>Breathable natural fill</t>
@@ -1842,11 +1830,7 @@
           <t>Fibras Naturales de Lujo|Suave|Euro-Top</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>Nuestro suave más indulgente — lana, cachemira y 16.5 pulgadas de lujo</t>
-        </is>
-      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
@@ -1860,21 +1844,13 @@
           <t>Un euro-top suave y profundo de lana y cachemira sobre capas de resortes — suavidad indulgente que nunca pierde su soporte.</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>El suave más lujoso de la tienda — fibras naturales sobre capas de resortes.</t>
-        </is>
-      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
           <t>Euro-top suave y profundo</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>Una superficie envolvente para quienes duermen de lado y quieren confort de nube sin hundirse hasta el fondo.</t>
-        </is>
-      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr">
         <is>
           <t>Relleno natural transpirable</t>
@@ -1984,11 +1960,7 @@
           <t>Hand-tufted construction</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Tufting locks the layers so the pillowtop can't shift or pocket over years of use.</t>
-        </is>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>4,294 Resortes|Firme|Copetudo a Mano</t>
@@ -2032,11 +2004,7 @@
           <t>Construcción copetuda a mano</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>El copetudo fija las capas para que el pillowtop no se mueva ni se deforme con los años.</t>
-        </is>
-      </c>
+      <c r="AT4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2088,11 +2056,7 @@
           <t>Cooling|Soft|Memory Foam</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Feels up to 10° cooler, soft TEMPUR comfort</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>no</t>
@@ -2116,21 +2080,9 @@
           <t>Tempur-Pedic's coolest mattress — Pure Cool Plus material pulls heat away while soft TEMPUR cradles every curve.</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>The coolest-sleeping soft mattress in the store — up to 10° cooler all night.</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Feels up to 10° cooler</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Phase-change cooling you can feel the moment you lie down — made for hot sleepers.</t>
-        </is>
-      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>Soft TEMPUR contour</t>
@@ -2146,11 +2098,7 @@
           <t>Frescura|Suave|Espuma Viscoelástica</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Se siente hasta 10° más fresco, confort TEMPUR suave</t>
-        </is>
-      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
@@ -2164,21 +2112,9 @@
           <t>El colchón más fresco de Tempur-Pedic — el material Pure Cool Plus disipa el calor mientras el TEMPUR suave abraza cada curva.</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>El colchón suave que duerme más fresco de la tienda — hasta 10° más fresco toda la noche.</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Se siente hasta 10° más fresco</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>Frescura de cambio de fase que se siente al momento de acostarte — hecho para quienes duermen con calor.</t>
-        </is>
-      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="inlineStr">
         <is>
           <t>Contorno TEMPUR suave</t>
@@ -2240,11 +2176,7 @@
           <t>Cooling|Hybrid|Medium</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>All-night cooling with TEMPUR comfort and coil support</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>no</t>
@@ -2268,11 +2200,7 @@
           <t>Cool-to-the-touch Breeze cover and Pure Cool material over a hybrid coil base — cooling plus true TEMPUR pressure relief.</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Proven all-night cooling with adaptive TEMPUR contour and hybrid support.</t>
-        </is>
-      </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>Cool-to-touch Breeze cover</t>
@@ -2298,11 +2226,7 @@
           <t>Frescura|Híbrido|Medio</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>Frescura toda la noche con confort TEMPUR y soporte de resortes</t>
-        </is>
-      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
@@ -2316,11 +2240,7 @@
           <t>Funda Breeze fresca al tacto y material Pure Cool sobre una base híbrida de resortes — frescura más el verdadero alivio de presión TEMPUR.</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Frescura comprobada toda la noche con contorno TEMPUR adaptable y soporte híbrido.</t>
-        </is>
-      </c>
+      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
           <t>Funda Breeze fresca al tacto</t>
@@ -2572,11 +2492,7 @@
           <t>Hand-made with natural materials in a balanced medium tight-top — luxury that works for almost every sleeper.</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Hand-made luxury in a true medium — the most versatile bed in the Reserve line.</t>
-        </is>
-      </c>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>True balanced medium</t>
@@ -2620,11 +2536,7 @@
           <t>Hecho a mano con materiales naturales en un tight-top medio equilibrado — lujo que funciona para casi todos.</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Lujo hecho a mano en un medio verdadero — la cama más versátil de la línea Reserve.</t>
-        </is>
-      </c>
+      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
           <t>Medio verdaderamente equilibrado</t>
@@ -2724,21 +2636,13 @@
           <t>The firmest bed in the Reserve line — hand-made hybrid support with natural materials for sleepers who want maximum lift.</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Hand-made extra-firm support — the choice for back and stomach sleepers who want luxury.</t>
-        </is>
-      </c>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>True extra-firm lift</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Holds you fully on top of the bed — the firmest luxury option in the store.</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>Hand-made durability</t>
@@ -2772,21 +2676,13 @@
           <t>La cama más firme de la línea Reserve — soporte híbrido hecho a mano con materiales naturales para quienes quieren máxima elevación.</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Soporte extra firme hecho a mano — la elección para quienes duermen boca arriba o boca abajo y quieren lujo.</t>
-        </is>
-      </c>
+      <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
           <t>Verdadera elevación extra firme</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>Te mantiene completamente sobre la cama — la opción de lujo más firme de la tienda.</t>
-        </is>
-      </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr">
         <is>
           <t>Durabilidad hecha a mano</t>
@@ -2876,21 +2772,13 @@
           <t>Patented NatuVerex copper fabric and copper-infused memory foam — a cleaner, cooler sleep over cushion-firm hybrid support.</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Copper cooling and recovery benefits with balanced cushion-firm hybrid support.</t>
-        </is>
-      </c>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
           <t>Copper-infused sleep surface</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Copper fabric and foams dissipate heat and stay naturally fresher than standard foam.</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>Cushion-firm balance</t>
@@ -2924,21 +2812,13 @@
           <t>Tela de cobre patentada NatuVerex y espuma viscoelástica con cobre — un sueño más limpio y fresco sobre soporte híbrido cushion-firm.</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Frescura y recuperación del cobre con soporte híbrido cushion-firm equilibrado.</t>
-        </is>
-      </c>
+      <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
           <t>Superficie con infusión de cobre</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>La tela y las espumas de cobre disipan el calor y se mantienen naturalmente más frescas que la espuma estándar.</t>
-        </is>
-      </c>
+      <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr">
         <is>
           <t>Equilibrio cushion-firm</t>
@@ -3200,11 +3080,7 @@
           <t>Zoned center third</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>Marvelous Middle reinforcement keeps hips level in every position.</t>
-        </is>
-      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
           <t>Marvelous Middle|Extra Firme|Híbrido</t>
@@ -3248,11 +3124,7 @@
           <t>Tercio central zonificado</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>El refuerzo Marvelous Middle mantiene las caderas niveladas en cualquier posición.</t>
-        </is>
-      </c>
+      <c r="AT12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3327,11 +3199,7 @@
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>A 15-inch plush box top with 25% thicker center coils and 3-inch edge encasement — soft where you feel it, supported where you need it.</t>
-        </is>
-      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
           <t>Plush box-top softness with zoned wrapped-coil support and strong edges.</t>
@@ -3352,11 +3220,7 @@
           <t>Zoned wrapped coils</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>Individually wrapped coils isolate motion and firm up under your hips.</t>
-        </is>
-      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>Box Top Suave|Resortes Zonificados|Soporte de Borde</t>
@@ -3375,11 +3239,7 @@
       <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Un box top suave de 15 pulgadas con resortes centrales 25% más gruesos y encasado de borde de 3 pulgadas — suave donde lo sientes, con soporte donde lo necesitas.</t>
-        </is>
-      </c>
+      <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr">
         <is>
           <t>Suavidad box-top con soporte de resortes envueltos zonificados y bordes fuertes.</t>
@@ -3400,11 +3260,7 @@
           <t>Resortes envueltos zonificados</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>Resortes envueltos individualmente aíslan el movimiento y se refuerzan bajo las caderas.</t>
-        </is>
-      </c>
+      <c r="AT13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3656,11 +3512,7 @@
           <t>Firm hybrid core</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>Keeps your spine aligned while the gel layer softens contact points.</t>
-        </is>
-      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>Gel Fresco|Firme|Híbrido</t>
@@ -3704,11 +3556,7 @@
           <t>Núcleo híbrido firme</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>Mantiene tu columna alineada mientras la capa de gel suaviza los puntos de contacto.</t>
-        </is>
-      </c>
+      <c r="AT15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3737,11 +3585,7 @@
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Cool-gel balanced hybrid</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1</v>
       </c>
@@ -3757,14 +3601,10 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Cool Gel|Medium|Hybrid</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Balanced medium comfort with cool gel memory foam</t>
-        </is>
-      </c>
+          <t>Medium|Hybrid</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3783,16 +3623,8 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Cool-gel memory foam on a balanced medium hybrid — pressure relief, cooling, and support in the feel most sleepers pick.</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>The balanced pick — medium hybrid comfort with a cooling gel layer.</t>
-        </is>
-      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
           <t>Crowd-pleasing medium</t>
@@ -3803,26 +3635,14 @@
           <t>The feel most couples agree on — balanced give and support.</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gel-cooled surface</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>Cool gel tempers the memory-foam warmth common in medium beds.</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Gel Fresco|Medio|Híbrido</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>Confort medio equilibrado con espuma de gel fresco</t>
-        </is>
-      </c>
+          <t>Medio|Híbrido</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
@@ -3831,16 +3651,8 @@
       <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Espuma con gel fresco sobre un híbrido medio equilibrado — alivio de presión, frescura y soporte en la sensación que la mayoría elige.</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>La elección equilibrada — confort híbrido medio con capa de gel refrescante.</t>
-        </is>
-      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
           <t>Medio que agrada a todos</t>
@@ -3851,16 +3663,8 @@
           <t>La sensación en la que la mayoría de las parejas están de acuerdo — equilibrio entre suavidad y soporte.</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>Superficie enfriada por gel</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>El gel fresco compensa el calor de la espuma viscoelástica común en camas medias.</t>
-        </is>
-      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3889,11 +3693,7 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Cool-gel plush hybrid</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>1</v>
       </c>
@@ -3909,14 +3709,10 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Cool Gel|Plush|Hybrid</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Plush gel-cooled comfort over hybrid support</t>
-        </is>
-      </c>
+          <t>Plush|Hybrid</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3935,46 +3731,22 @@
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Plush gel memory foam over hybrid coils — soft, cool pressure relief for side sleepers who sleep warm.</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Soft, cooling pressure relief — plush without the heat.</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Plush that stays cool</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Gel-infused foam keeps the soft layers from trapping heat.</t>
-        </is>
-      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>Supported softness</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>Hybrid coils under the plush top prevent the hammock feel of all-foam soft beds.</t>
-        </is>
-      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Gel Fresco|Suave|Híbrido</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>Confort suave enfriado por gel sobre soporte híbrido</t>
-        </is>
-      </c>
+          <t>Suave|Híbrido</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
@@ -3983,36 +3755,16 @@
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Espuma viscoelástica suave con gel sobre resortes híbridos — alivio de presión suave y fresco para quienes duermen de lado con calor.</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>Alivio de presión suave y refrescante — suavidad sin el calor.</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>Suave que se mantiene fresco</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>La espuma con gel evita que las capas suaves atrapen el calor.</t>
-        </is>
-      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
       <c r="AS17" t="inlineStr">
         <is>
           <t>Suavidad con soporte</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>Los resortes híbridos bajo la capa suave evitan la sensación de hamaca de las camas blandas de pura espuma.</t>
-        </is>
-      </c>
+      <c r="AT17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4244,21 +3996,13 @@
           <t>Layers of conforming foam over wrapped coils — balanced medium comfort that absorbs a partner's movement.</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Balanced medium comfort with wrapped coils that keep partner movement on their side.</t>
-        </is>
-      </c>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>Wrapped-coil motion isolation</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Each coil moves alone, so a restless partner doesn't wake you.</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>Conforming comfort layers</t>
@@ -4292,21 +4036,13 @@
           <t>Capas de espuma adaptable sobre resortes envueltos — confort medio equilibrado que absorbe el movimiento de la pareja.</t>
         </is>
       </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>Confort medio equilibrado con resortes envueltos que mantienen el movimiento de tu pareja de su lado.</t>
-        </is>
-      </c>
+      <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
           <t>Aislamiento de movimiento con resortes envueltos</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>Cada resorte se mueve solo, así una pareja inquieta no te despierta.</t>
-        </is>
-      </c>
+      <c r="AR19" t="inlineStr"/>
       <c r="AS19" t="inlineStr">
         <is>
           <t>Capas de confort adaptables</t>
@@ -4391,16 +4127,8 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Extra-firm hybrid support with 25% thicker center coils — maximum alignment without the luxury price tag.</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Serious extra-firm zoned support at the best price in its class.</t>
-        </is>
-      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
           <t>Extra-firm tight top</t>
@@ -4439,16 +4167,8 @@
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Soporte híbrido extra firme con resortes centrales 25% más gruesos — máxima alineación sin precio de lujo.</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>Soporte extra firme zonificado serio al mejor precio de su clase.</t>
-        </is>
-      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
           <t>Tight top extra firme</t>
@@ -4548,11 +4268,7 @@
           <t>A 12.5-inch plush build that cushions shoulders and hips — easy softness at a price that makes sense.</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Honest plush comfort for side sleepers at an everyday price.</t>
-        </is>
-      </c>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
           <t>True plush surface</t>
@@ -4596,11 +4312,7 @@
           <t>Una construcción suave de 12.5 pulgadas que acolcha hombros y caderas — suavidad fácil a un precio razonable.</t>
         </is>
       </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>Confort suave honesto para quienes duermen de lado a precio cotidiano.</t>
-        </is>
-      </c>
+      <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
           <t>Superficie verdaderamente suave</t>
@@ -5128,11 +4840,7 @@
           <t>Marvelous Middle|Plush|Side Sleeper</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Plush pressure relief with 25% thicker center coils</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>yes</t>
@@ -5151,26 +4859,10 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>25% thicker center coils relieve shoulder and hip pressure — a side-sleeper favorite with real edge support.</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Zoned plush pressure relief — a proven pick for side sleepers.</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Shoulder-and-hip relief</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>The plush surface and center zoning target exactly where side sleepers ache.</t>
-        </is>
-      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
           <t>3-inch edge encasement</t>
@@ -5186,11 +4878,7 @@
           <t>Marvelous Middle|Suave|Para Dormir de Lado</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>Alivio de presión suave con resortes centrales 25% más gruesos</t>
-        </is>
-      </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
@@ -5199,26 +4887,10 @@
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Resortes centrales 25% más gruesos alivian la presión de hombros y caderas — favorito de quienes duermen de lado con soporte de borde real.</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr">
-        <is>
-          <t>Alivio de presión suave zonificado — elección comprobada para dormir de lado.</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>Alivio de hombros y caderas</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>La superficie suave y la zonificación central atienden justo donde duele al dormir de lado.</t>
-        </is>
-      </c>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
       <c r="AS25" t="inlineStr">
         <is>
           <t>Encasado de borde de 3 pulgadas</t>
@@ -5303,11 +4975,7 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>An extra-firm hybrid with 25% thicker center coils — maximum support at the most accessible price.</t>
-        </is>
-      </c>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
         <is>
           <t>The value path to real extra-firm zoned support.</t>
@@ -5351,11 +5019,7 @@
       <c r="AL26" t="inlineStr"/>
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Un híbrido extra firme con resortes centrales 25% más gruesos — máximo soporte al precio más accesible.</t>
-        </is>
-      </c>
+      <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr">
         <is>
           <t>El camino de valor al verdadero soporte extra firme zonificado.</t>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -3335,11 +3335,7 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Firm box-top support with 25% thicker center coils and full edge encasement — alignment-first comfort with a finished luxury feel.</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
           <t>Firm zoned support in a box-top build with lasting edge-to-edge comfort.</t>
@@ -3383,11 +3379,7 @@
       <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Soporte box-top firme con resortes centrales 25% más gruesos y encasado completo de borde — confort que prioriza la alineación con acabado de lujo.</t>
-        </is>
-      </c>
+      <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr">
         <is>
           <t>Soporte firme zonificado en construcción box-top con confort de borde a borde.</t>
@@ -3816,11 +3808,7 @@
           <t>Marvelous Middle|Firm|Euro Top</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Firm euro-top comfort with 25% thicker center coils</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3839,11 +3827,7 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>25% thicker coils in the center third support your hips and lower back while the euro top softens the firm surface.</t>
-        </is>
-      </c>
+      <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
         <is>
           <t>Zoned firm support with a euro-top finish — firm without feeling bare.</t>
@@ -3874,11 +3858,7 @@
           <t>Marvelous Middle|Firme|Euro Top</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>Confort euro-top firme con resortes centrales 25% más gruesos</t>
-        </is>
-      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
@@ -3887,11 +3867,7 @@
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Resortes 25% más gruesos en el tercio central soportan caderas y espalda baja mientras el euro top suaviza la superficie firme.</t>
-        </is>
-      </c>
+      <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr">
         <is>
           <t>Soporte firme zonificado con acabado euro-top — firme sin sentirse desnudo.</t>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6011,7 +6011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sleep_quality.poor</t>
+          <t>trigger.pain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -6275,7 +6275,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>aiming for a real change in nightly rest</t>
+          <t>here to solve a comfort problem</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -6285,7 +6285,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>buscando un cambio real en el descanso</t>
+          <t>aquí para resolver un problema de comodidad</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sleep_quality.fair</t>
+          <t>trigger.worn_out</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -6308,7 +6308,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>aiming to sleep noticeably better</t>
+          <t>replacing an old mattress</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -6318,7 +6318,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>buscando dormir notablemente mejor</t>
+          <t>reemplazando un colchón viejo</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sleep_quality.okay</t>
+          <t>trigger.moving</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -6341,7 +6341,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>building on what already works</t>
+          <t>furnishing a new space</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -6351,7 +6351,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>mejorando lo que ya funciona</t>
+          <t>amueblando un espacio nuevo</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sleep_quality.well</t>
+          <t>trigger.upgrade</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>protecting a setup that already works</t>
+          <t>ready for an upgrade</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -6384,7 +6384,7 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>cuidando un descanso que ya funciona</t>
+          <t>buscando una mejora</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6396,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>trigger.pain</t>
+          <t>trigger.browsing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -6407,7 +6407,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>here to solve a comfort problem</t>
+          <t>exploring options today</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -6417,7 +6417,7 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>aquí para resolver un problema de comodidad</t>
+          <t>explorando opciones hoy</t>
         </is>
       </c>
     </row>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>trigger.worn_out</t>
+          <t>sleep_issues.back_pain</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -6440,7 +6440,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>replacing an old mattress</t>
+          <t>test lower-back support carefully</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -6450,7 +6450,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>reemplazando un colchón viejo</t>
+          <t>probar con cuidado el soporte lumbar</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>trigger.moving</t>
+          <t>sleep_issues.hip_pain</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -6473,7 +6473,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>furnishing a new space</t>
+          <t>focus on pressure relief at hips and shoulders</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -6483,7 +6483,7 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>amueblando un espacio nuevo</t>
+          <t>enfocarse en aliviar la presión en caderas y hombros</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>trigger.upgrade</t>
+          <t>sleep_issues.hot</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -6506,7 +6506,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ready for an upgrade</t>
+          <t>prioritize temperature control</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -6516,7 +6516,7 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>buscando una mejora</t>
+          <t>priorizar el control de temperatura</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>trigger.browsing</t>
+          <t>sleep_issues.tossing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -6539,7 +6539,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>exploring options today</t>
+          <t>notice how easy it is to settle in</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -6549,7 +6549,7 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>explorando opciones hoy</t>
+          <t>notar qué tan fácil es acomodarse</t>
         </is>
       </c>
     </row>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sleep_issues.back_pain</t>
+          <t>sleep_issues.stiff</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -6572,7 +6572,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>test lower-back support carefully</t>
+          <t>compare alignment and morning comfort</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -6582,7 +6582,7 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>probar con cuidado el soporte lumbar</t>
+          <t>comparar la alineación y la comodidad al despertar</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sleep_issues.hip_pain</t>
+          <t>sleep_issues.sagging</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -6605,7 +6605,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>focus on pressure relief at hips and shoulders</t>
+          <t>check for durable, consistent support</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -6615,7 +6615,7 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>enfocarse en aliviar la presión en caderas y hombros</t>
+          <t>revisar que el soporte sea duradero y consistente</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sleep_issues.hot</t>
+          <t>sleep_issues.too_soft</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -6638,7 +6638,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>prioritize temperature control</t>
+          <t>try firmer, more supportive feels</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -6648,7 +6648,7 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>priorizar el control de temperatura</t>
+          <t>probar sensaciones más firmes y con más soporte</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sleep_issues.tossing</t>
+          <t>sleep_issues.none</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -6669,21 +6669,13 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>notice how easy it is to settle in</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>notar qué tan fácil es acomodarse</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6693,7 +6685,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sleep_issues.stiff</t>
+          <t>sleep_position.side</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -6704,7 +6696,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>compare alignment and morning comfort</t>
+          <t>prioritize shoulder and hip cushioning</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -6714,7 +6706,7 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>comparar la alineación y la comodidad al despertar</t>
+          <t>priorizar el acolchado de hombros y caderas</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6718,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sleep_issues.sagging</t>
+          <t>sleep_position.back</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -6737,7 +6729,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>check for durable, consistent support</t>
+          <t>look for even lumbar support</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -6747,7 +6739,7 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>revisar que el soporte sea duradero y consistente</t>
+          <t>buscar soporte lumbar uniforme</t>
         </is>
       </c>
     </row>
@@ -6759,7 +6751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sleep_issues.too_soft</t>
+          <t>sleep_position.stomach</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -6770,7 +6762,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>try firmer, more supportive feels</t>
+          <t>keep the midsection supported</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -6780,7 +6772,7 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>probar sensaciones más firmes y con más soporte</t>
+          <t>mantener la zona media con soporte</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sleep_issues.none</t>
+          <t>sleep_position.combo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -6801,13 +6793,21 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>notice ease of movement between positions</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>notar la facilidad para cambiar de posición</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sleep_position.side</t>
+          <t>sleep_position.no_idea</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -6828,7 +6828,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>prioritize shoulder and hip cushioning</t>
+          <t>compare a few different feels to find a starting point</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -6838,7 +6838,7 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>priorizar el acolchado de hombros y caderas</t>
+          <t>comparar varias sensaciones para encontrar un punto de partida</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6850,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sleep_position.back</t>
+          <t>health_conditions.nerve_pain</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -6861,7 +6861,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>look for even lumbar support</t>
+          <t>compare gentle, even pressure relief</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -6871,7 +6871,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>buscar soporte lumbar uniforme</t>
+          <t>comparar un alivio de presión suave y uniforme</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sleep_position.stomach</t>
+          <t>health_conditions.allergies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -6894,7 +6894,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>keep the midsection supported</t>
+          <t>ask about washable and protective covers</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -6904,7 +6904,7 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>mantener la zona media con soporte</t>
+          <t>preguntar por fundas lavables y protectoras</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sleep_position.combo</t>
+          <t>health_conditions.snoring</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -6927,7 +6927,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>notice ease of movement between positions</t>
+          <t>test head-of-bed elevation on an adjustable base</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -6937,7 +6937,7 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>notar la facilidad para cambiar de posición</t>
+          <t>probar la elevación de la cabecera en una base ajustable</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sleep_position.no_idea</t>
+          <t>health_conditions.reflux</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -6960,7 +6960,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>compare a few different feels to find a starting point</t>
+          <t>notice how a raised upper body feels</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -6970,7 +6970,7 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>comparar varias sensaciones para encontrar un punto de partida</t>
+          <t>notar cómo se siente el torso elevado</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>health_conditions.nerve_pain</t>
+          <t>health_conditions.extra_support</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -6993,7 +6993,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>compare gentle, even pressure relief</t>
+          <t>prioritize reinforced, sturdy support</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -7003,7 +7003,7 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>comparar un alivio de presión suave y uniforme</t>
+          <t>priorizar un soporte reforzado y resistente</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>health_conditions.allergies</t>
+          <t>health_conditions.getting_older</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -7026,7 +7026,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ask about washable and protective covers</t>
+          <t>compare ease of getting in and out of bed</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -7036,7 +7036,7 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>preguntar por fundas lavables y protectoras</t>
+          <t>comparar la facilidad para acostarse y levantarse</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>health_conditions.snoring</t>
+          <t>health_conditions.none</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -7057,21 +7057,13 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>test head-of-bed elevation on an adjustable base</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>probar la elevación de la cabecera en una base ajustable</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7081,7 +7073,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>health_conditions.reflux</t>
+          <t>temperature.hot</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -7092,7 +7084,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>notice how a raised upper body feels</t>
+          <t>compare cooling covers and airflow</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -7102,7 +7094,7 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>notar cómo se siente el torso elevado</t>
+          <t>comparar fundas frescas y ventilación</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7106,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>health_conditions.extra_support</t>
+          <t>temperature.comfortable</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -7123,21 +7115,13 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>prioritize reinforced, sturdy support</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>priorizar un soporte reforzado y resistente</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7147,7 +7131,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>health_conditions.getting_older</t>
+          <t>temperature.cold</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -7158,7 +7142,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>compare ease of getting in and out of bed</t>
+          <t>notice warmth and cozier surface feels</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -7168,7 +7152,7 @@
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>comparar la facilidad para acostarse y levantarse</t>
+          <t>notar calidez y superficies más acogedoras</t>
         </is>
       </c>
     </row>
@@ -7180,7 +7164,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>health_conditions.none</t>
+          <t>temperature.opposite</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -7189,133 +7173,17 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>compare temperature balance for two sleepers</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>temperature.hot</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>compare cooling covers and airflow</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>comparar fundas frescas y ventilación</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>temperature.comfortable</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>temperature.cold</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>notice warmth and cozier surface feels</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>notar calidez y superficies más acogedoras</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>temperature.opposite</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>compare temperature balance for two sleepers</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>comparar el equilibrio de temperatura para dos personas</t>
         </is>
@@ -7373,7 +7241,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"quiz":{"questions":[{"id":"sleep_quality","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"How well do you sleep right now?","es":"¿Qué tan bien duermes actualmente?"},"helpText":{"en":"Be honest. It helps us solve the real problem, not guess.","es":"Sé honesto — podemos ayudarte de cualquier manera"},"type":"single","options":[{"id":"poor","label":{"en":"Poorly","es":"Mal"},"icon":"stiff","sublabel":{"en":"Restless, waking often","es":"Inquieto, despertando seguido"},"scores":{}},{"id":"fair","label":{"en":"Not Great","es":"No Muy Bien"},"icon":"combo","sublabel":{"en":"Could be a lot better","es":"Podría ser mucho mejor"},"scores":{}},{"id":"okay","label":{"en":"Okay","es":"Más o Menos"},"icon":"smile","sublabel":{"en":"Mostly fine","es":"Generalmente bien"},"scores":{}},{"id":"well","label":{"en":"Pretty Well","es":"Bastante Bien"},"icon":"check","sublabel":{"en":"Usually rested","es":"Generalmente descansado"},"scores":{}}]},{"id":"trigger","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What can we help you with today?","es":"¿En qué te podemos ayudar hoy?"},"helpText":{"en":"No pressure — this just helps your specialist focus on what matters to you.","es":"Sin presión — esto ayuda a tu especialista a enfocarse en lo que te importa."},"type":"single","options":[{"id":"pain","label":{"en":"Back or Body Pain","es":"Dolor de Espalda o Cuerpo"},"icon":"spine","sublabel":{"en":"Current mattress is hurting me","es":"Mi colchón actual me lastima"},"scores":{}},{"id":"worn_out","label":{"en":"Old Mattress","es":"Colchón Viejo"},"icon":"sagging","sublabel":{"en":"Time for an upgrade","es":"Es hora de un cambio"},"scores":{}},{"id":"moving","label":{"en":"Moving or New Space","es":"Mudanza o Espacio Nuevo"},"icon":"family","sublabel":{"en":"New home, new bed","es":"Casa nueva, cama nueva"},"scores":{}},{"id":"upgrade","label":{"en":"Just Upgrading","es":"Mejorando"},"icon":"cloud","sublabel":{"en":"Ready for something better","es":"Listo para algo mejor"},"scores":{}},{"id":"browsing","label":{"en":"Just Browsing","es":"Solo Explorando"},"icon":"smile","sublabel":{"en":"Getting ideas, no rush","es":"Sin prisa, juntando ideas"},"scores":{}}]},{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"So every mattress we show actually fits your space.","es":"Nos aseguraremos de que las recomendaciones se ajusten a tu espacio"},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"Who shares your bed shapes which features matter most.","es":"Esto determina qué características importan más"},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"Motion isolation is one of the first upgrades you'll feel.","es":"El aislamiento de movimiento es una de las mayores mejoras en un colchón nuevo"},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"Your sleep position is the biggest clue to the support you need.","es":"Piensa en cómo terminas naturalmente"},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"Sleeping hot or cold is an easy fix with the right materials.","es":"La regulación de temperatura es clave para un sueño profundo"},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to what feels best.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"current_mattress_age","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"How old is your current mattress?","es":"¿Cuántos años tiene tu colchón actual?"},"helpText":{"en":"Most mattresses lose their support after about 8 years.","es":"La mayoría de los colchones duran 7–10 años"},"type":"single","options":[{"id":"under_2","label":{"en":"Less Than 2 Years","es":"Menos de 2 Años"},"icon":"check","sublabel":{"en":"Pretty new","es":"Bastante nuevo"},"scores":{}},{"id":"three_seven","label":{"en":"3 to 7 Years","es":"3 a 7 Años"},"icon":"combo","sublabel":{"en":"Middle of its life","es":"A mitad de su vida"},"scores":{}},{"id":"eight_fifteen","label":{"en":"8 to 15 Years","es":"8 a 15 Años"},"icon":"aging","sublabel":{"en":"Past its prime","es":"Ya pasó su mejor momento"},"scores":{}},{"id":"fifteen_plus","label":{"en":"Over 15 Years","es":"Más de 15 Años"},"icon":"sagging","sublabel":{"en":"Long overdue","es":"Ya era hora"},"scores":{}},{"id":"not_sure","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"Can't remember","es":"No recuerdo"},"scores":{}}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. Each one points us toward a fix.","es":"Toca las que apliquen"},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durable":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. A few of these change what we'd suggest.","es":"Toca las que apliquen"},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durable":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
+          <t>{"quiz":{"questions":[{"id":"trigger","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What can we help you with today?","es":"¿En qué te podemos ayudar hoy?"},"helpText":{"en":"No pressure — this just helps your specialist focus on what matters to you.","es":"Sin presión — esto ayuda a tu especialista a enfocarse en lo que te importa."},"type":"single","options":[{"id":"pain","label":{"en":"Back or Body Pain","es":"Dolor de Espalda o Cuerpo"},"icon":"spine","sublabel":{"en":"Current mattress is hurting me","es":"Mi colchón actual me lastima"},"scores":{}},{"id":"worn_out","label":{"en":"Old Mattress","es":"Colchón Viejo"},"icon":"sagging","sublabel":{"en":"Time for an upgrade","es":"Es hora de un cambio"},"scores":{}},{"id":"moving","label":{"en":"Moving or New Space","es":"Mudanza o Espacio Nuevo"},"icon":"family","sublabel":{"en":"New home, new bed","es":"Casa nueva, cama nueva"},"scores":{}},{"id":"upgrade","label":{"en":"Just Upgrading","es":"Mejorando"},"icon":"cloud","sublabel":{"en":"Ready for something better","es":"Listo para algo mejor"},"scores":{}},{"id":"browsing","label":{"en":"Just Browsing","es":"Solo Explorando"},"icon":"smile","sublabel":{"en":"Getting ideas, no rush","es":"Sin prisa, juntando ideas"},"scores":{}}]},{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"So every mattress we show actually fits your space.","es":"Nos aseguraremos de que las recomendaciones se ajusten a tu espacio"},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"Who shares your bed shapes which features matter most.","es":"Esto determina qué características importan más"},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"Motion isolation is one of the first upgrades you'll feel.","es":"El aislamiento de movimiento es una de las mayores mejoras en un colchón nuevo"},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"Your sleep position is the biggest clue to the support you need.","es":"Piensa en cómo terminas naturalmente"},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"Sleeping hot or cold is an easy fix with the right materials.","es":"La regulación de temperatura es clave para un sueño profundo"},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to what feels best.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. Each one points us toward a fix.","es":"Toca las que apliquen"},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durable":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. A few of these change what we'd suggest.","es":"Toca las que apliquen"},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durable":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -2289,11 +2289,7 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Hand-made plush luxury hybrid</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -2309,14 +2305,10 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Hand-Made|Plush|Natural Materials</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Hand-made in Texas — plush euro-top luxury</t>
-        </is>
-      </c>
+          <t>Plush</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2335,46 +2327,18 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>A hand-made hybrid of natural materials with a plush euro-top — built by Restonic craftspeople to last a lifetime.</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Hand-made plush luxury with natural materials, made regionally by Restonic.</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Hand-made construction</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Assembled by hand with natural materials most factory beds skip.</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Plush euro-top feel</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>Cushioned sink-in comfort over a supportive hybrid core.</t>
-        </is>
-      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Hecho a Mano|Suave|Materiales Naturales</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>Hecho a mano en Texas — lujo suave con euro-top</t>
-        </is>
-      </c>
+          <t>Suave</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
@@ -2383,36 +2347,12 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Un híbrido hecho a mano con materiales naturales y euro-top suave — construido por artesanos de Restonic para durar toda la vida.</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Lujo suave hecho a mano con materiales naturales, fabricado regionalmente por Restonic.</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>Construcción a mano</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>Ensamblado a mano con materiales naturales que la mayoría de las camas de fábrica omiten.</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Sensación de euro-top suave</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>Confort acolchado y envolvente sobre un núcleo híbrido de soporte.</t>
-        </is>
-      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2441,11 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Hand-made balanced luxury hybrid</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -2461,14 +2397,10 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Hand-Made|Medium|Natural Materials</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Hand-made balanced luxury with natural materials</t>
-        </is>
-      </c>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2487,42 +2419,18 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Hand-made with natural materials in a balanced medium tight-top — luxury that works for almost every sleeper.</t>
-        </is>
-      </c>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>True balanced medium</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Neither plush nor firm — a safe luxury pick for couples who disagree.</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Natural-material build</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>Hand-made with breathable natural layers built to outlast foam-only beds.</t>
-        </is>
-      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Hecho a Mano|Medio|Materiales Naturales</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>Lujo equilibrado hecho a mano con materiales naturales</t>
-        </is>
-      </c>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
@@ -2531,32 +2439,12 @@
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Hecho a mano con materiales naturales en un tight-top medio equilibrado — lujo que funciona para casi todos.</t>
-        </is>
-      </c>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>Medio verdaderamente equilibrado</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>Ni suave ni firme — una elección de lujo segura para parejas que no se ponen de acuerdo.</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Construcción de materiales naturales</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>Hecho a mano con capas naturales transpirables que duran más que las camas de pura espuma.</t>
-        </is>
-      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2585,11 +2473,7 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Hand-made extra-firm luxury</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -2605,14 +2489,10 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Hand-Made|Extra Firm|Natural Materials</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Hand-made extra-firm — maximum support, luxury materials</t>
-        </is>
-      </c>
+          <t>Extra Firm</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -2631,38 +2511,18 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>The firmest bed in the Reserve line — hand-made hybrid support with natural materials for sleepers who want maximum lift.</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>True extra-firm lift</t>
-        </is>
-      </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hand-made durability</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>Natural materials and hand assembly keep the firm feel from softening early.</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Hecho a Mano|Extra Firme|Materiales Naturales</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>Extra firme hecho a mano — máximo soporte, materiales de lujo</t>
-        </is>
-      </c>
+          <t>Extra Firme</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
@@ -2671,28 +2531,12 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>La cama más firme de la línea Reserve — soporte híbrido hecho a mano con materiales naturales para quienes quieren máxima elevación.</t>
-        </is>
-      </c>
+      <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>Verdadera elevación extra firme</t>
-        </is>
-      </c>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Durabilidad hecha a mano</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>Los materiales naturales y el ensamblaje a mano evitan que la firmeza se ablande antes de tiempo.</t>
-        </is>
-      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2721,11 +2565,7 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Copper-infused cooling hybrid</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>1</v>
       </c>
@@ -2741,14 +2581,10 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Copper-Infused|Cooling|Cushion Firm</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Copper-infused cooling with cushion-firm support</t>
-        </is>
-      </c>
+          <t>Cushion Firm</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>no</t>
@@ -2767,38 +2603,18 @@
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Patented NatuVerex copper fabric and copper-infused memory foam — a cleaner, cooler sleep over cushion-firm hybrid support.</t>
-        </is>
-      </c>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Copper-infused sleep surface</t>
-        </is>
-      </c>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Cushion-firm balance</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>Supportive like a firm with a thin comfort cushion — firm without the board feel.</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Infusión de Cobre|Frescura|Cushion Firm</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>Frescura con infusión de cobre y soporte cushion-firm</t>
-        </is>
-      </c>
+          <t>Cushion Firm</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
@@ -2807,28 +2623,12 @@
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Tela de cobre patentada NatuVerex y espuma viscoelástica con cobre — un sueño más limpio y fresco sobre soporte híbrido cushion-firm.</t>
-        </is>
-      </c>
+      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Superficie con infusión de cobre</t>
-        </is>
-      </c>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Equilibrio cushion-firm</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>Soporta como un firme con un cojín delgado de confort — firme sin sentirse como tabla.</t>
-        </is>
-      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3153,11 +2953,7 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Plush box-top zoned hybrid</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -3173,14 +2969,10 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Plush Box Top|Zoned Coils|Edge Support</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Deep plush box top over zoned wrapped coils</t>
-        </is>
-      </c>
+          <t>Plush Box Top</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3200,37 +2992,17 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Plush box-top softness with zoned wrapped-coil support and strong edges.</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Deep box-top plush</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>A pillowy sewn-on top layer with more depth than a standard plush.</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Zoned wrapped coils</t>
-        </is>
-      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Box Top Suave|Resortes Zonificados|Soporte de Borde</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>Box top suave y profundo sobre resortes envueltos zonificados</t>
-        </is>
-      </c>
+          <t>Box Top Suave</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
@@ -3240,26 +3012,10 @@
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>Suavidad box-top con soporte de resortes envueltos zonificados y bordes fuertes.</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>Suavidad box-top profunda</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>Una capa superior acolchada cosida con más profundidad que un suave estándar.</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>Resortes envueltos zonificados</t>
-        </is>
-      </c>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
     </row>
     <row r="14">

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6969,7 +6969,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Plan the conversation","es":"Planear la conversación"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Plan the conversation","es":"Planear la conversación"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"agendaPrompt":{"en":"As you review these together, mark any options the customer wants to discuss.","es":"Mientras revisan estas opciones juntos, marca las opciones de pago que el cliente quiera conversar."},"agendaMark":{"en":"Add to discussion","es":"Agregar a la conversación"},"agendaMarked":{"en":"Added to discussion","es":"Agregado a la conversación"},"agendaEmpty":{"en":"No options are marked yet.","es":"Todavía no hay opciones de pago marcadas."},"agendaConsequence":{"en":"Use this agenda to guide the conversation together. Nothing is submitted and no application is started.","es":"Usen esta agenda para guiar la conversación juntos. No se envía nada y no se inicia ninguna solicitud."},"agendaChange":{"en":"Change discussion agenda","es":"Cambiar agenda de conversación"},"agendaNotNow":{"en":"Not right now","es":"Ahora no"},"agendaDismissed":{"en":"No options marked for review right now.","es":"No hay opciones de pago marcadas para revisar por ahora."},"agendaDone":{"en":"Done","es":"Listo"},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
+          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Plan the conversation","es":"Planear la conversación"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Plan the conversation","es":"Planear la conversación"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"agendaPrompt":{"en":"As you review these together, mark any options the customer wants to discuss.","es":"Mientras revisan estas opciones juntos, marca las opciones de pago que el cliente quiera conversar."},"agendaMark":{"en":"Add to discussion","es":"Agregar a la conversación"},"agendaMarked":{"en":"Added to discussion","es":"Agregado a la conversación"},"agendaEmpty":{"en":"No options are marked yet.","es":"Todavía no hay opciones de pago marcadas."},"agendaConsequence":{"en":"Use this agenda to guide the conversation together. Nothing is submitted and no application is started.","es":"Usen esta agenda para guiar la conversación juntos. No se envía nada y no se inicia ninguna solicitud."},"agendaChange":{"en":"Change discussion agenda","es":"Cambiar agenda de conversación"},"agendaNotNow":{"en":"Not right now","es":"Ahora no"},"agendaDismissed":{"en":"No options marked for review right now.","es":"No hay opciones de pago marcadas para revisar por ahora."},"agendaDone":{"en":"Done","es":"Listo"},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6969,7 +6969,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Plan the conversation","es":"Planear la conversación"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Plan the conversation","es":"Planear la conversación"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"agendaPrompt":{"en":"As you review these together, mark any options the customer wants to discuss.","es":"Mientras revisan estas opciones juntos, marca las opciones de pago que el cliente quiera conversar."},"agendaMark":{"en":"Add to discussion","es":"Agregar a la conversación"},"agendaMarked":{"en":"Added to discussion","es":"Agregado a la conversación"},"agendaEmpty":{"en":"No options are marked yet.","es":"Todavía no hay opciones de pago marcadas."},"agendaConsequence":{"en":"Use this agenda to guide the conversation together. Nothing is submitted and no application is started.","es":"Usen esta agenda para guiar la conversación juntos. No se envía nada y no se inicia ninguna solicitud."},"agendaChange":{"en":"Change discussion agenda","es":"Cambiar agenda de conversación"},"agendaNotNow":{"en":"Not right now","es":"Ahora no"},"agendaDismissed":{"en":"No options marked for review right now.","es":"No hay opciones de pago marcadas para revisar por ahora."},"agendaDone":{"en":"Done","es":"Listo"},"interestNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"interestClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
+          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Plan the conversation","es":"Planear la conversación"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Plan the conversation","es":"Planear la conversación"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"agendaPrompt":{"en":"As you review these together, mark any options the customer wants to discuss.","es":"Mientras revisan estas opciones juntos, marca las opciones de pago que el cliente quiera conversar."},"agendaMark":{"en":"Add to discussion","es":"Agregar a la conversación"},"agendaMarked":{"en":"Added to discussion","es":"Agregado a la conversación"},"agendaEmpty":{"en":"No options are marked yet.","es":"Todavía no hay opciones de pago marcadas."},"agendaConsequence":{"en":"Use this agenda to guide the conversation together. Nothing is submitted and no application is started.","es":"Usen esta agenda para guiar la conversación juntos. No se envía nada y no se inicia ninguna solicitud."},"agendaChange":{"en":"Change discussion agenda","es":"Cambiar agenda de conversación"},"preferenceNotNow":{"en":"Not right now","es":"Ahora no"},"agendaDismissed":{"en":"No options marked for review right now.","es":"No hay opciones de pago marcadas para revisar por ahora."},"sheetDone":{"en":"Done","es":"Listo"},"preferenceNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"preferenceClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6969,7 +6969,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"resultsAsk":{"en":"Plan the conversation","es":"Planear la conversación"},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"drawerMark":{"en":"Plan the conversation","es":"Planear la conversación"},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"agendaPrompt":{"en":"As you review these together, mark any options the customer wants to discuss.","es":"Mientras revisan estas opciones juntos, marca las opciones de pago que el cliente quiera conversar."},"agendaMark":{"en":"Add to discussion","es":"Agregar a la conversación"},"agendaMarked":{"en":"Added to discussion","es":"Agregado a la conversación"},"agendaEmpty":{"en":"No options are marked yet.","es":"Todavía no hay opciones de pago marcadas."},"agendaConsequence":{"en":"Use this agenda to guide the conversation together. Nothing is submitted and no application is started.","es":"Usen esta agenda para guiar la conversación juntos. No se envía nada y no se inicia ninguna solicitud."},"agendaChange":{"en":"Change discussion agenda","es":"Cambiar agenda de conversación"},"preferenceNotNow":{"en":"Not right now","es":"Ahora no"},"agendaDismissed":{"en":"No options marked for review right now.","es":"No hay opciones de pago marcadas para revisar por ahora."},"sheetDone":{"en":"Done","es":"Listo"},"preferenceNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"preferenceClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBody":{"en":"You explored Lacks Payment Choice: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Exploraste las Opciones de Pago Lacks: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
+          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"paymentPreferenceLabel":{"en":"Payment preference","es":"Preferencia de pago"},"preferenceNone":{"en":"Not selected","es":"Sin seleccionar"},"optionsExploredLabel":{"en":"Options explored","es":"Opciones exploradas"},"reviewOption":{"en":"Review this option","es":"Revisar esta opción"},"hideDetails":{"en":"Hide details","es":"Ocultar detalles"},"considerOption":{"en":"Consider this option","es":"Considerar esta opción"},"currentlyConsidering":{"en":"Currently considering ✓","es":"En consideración ✓"},"clearPreference":{"en":"Clear preference","es":"Quitar preferencia"},"preferenceNotNow":{"en":"Not right now","es":"Ahora no"},"exploreConsequence":{"en":"Explore options together. Nothing is submitted and no application is started.","es":"Exploren las opciones juntos. No se envía nada y no se inicia ninguna solicitud."},"sheetDone":{"en":"Done","es":"Listo"},"preferenceNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"preferenceClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6969,7 +6969,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"paymentPreferenceLabel":{"en":"Payment preference","es":"Preferencia de pago"},"preferenceNone":{"en":"Not selected","es":"Sin seleccionar"},"optionsExploredLabel":{"en":"Options explored","es":"Opciones exploradas"},"reviewOption":{"en":"Review this option","es":"Revisar esta opción"},"hideDetails":{"en":"Hide details","es":"Ocultar detalles"},"considerOption":{"en":"Consider this option","es":"Considerar esta opción"},"currentlyConsidering":{"en":"Currently considering ✓","es":"En consideración ✓"},"clearPreference":{"en":"Clear preference","es":"Quitar preferencia"},"preferenceNotNow":{"en":"Not right now","es":"Ahora no"},"exploreConsequence":{"en":"Explore options together. Nothing is submitted and no application is started.","es":"Exploren las opciones juntos. No se envía nada y no se inicia ninguna solicitud."},"sheetDone":{"en":"Done","es":"Listo"},"preferenceNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"preferenceClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
+          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","surfaces":{"drawer":false,"sleepSystem":false},"allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"paymentPreferenceLabel":{"en":"Payment preference","es":"Preferencia de pago"},"preferenceNone":{"en":"Not selected","es":"Sin seleccionar"},"optionsExploredLabel":{"en":"Options explored","es":"Opciones exploradas"},"reviewOption":{"en":"Review this option","es":"Revisar esta opción"},"hideDetails":{"en":"Hide details","es":"Ocultar detalles"},"considerOption":{"en":"Consider this option","es":"Considerar esta opción"},"currentlyConsidering":{"en":"Currently considering ✓","es":"En consideración ✓"},"clearPreference":{"en":"Clear preference","es":"Quitar preferencia"},"preferenceNotNow":{"en":"Not right now","es":"Ahora no"},"exploreConsequence":{"en":"Explore options together. Nothing is submitted and no application is started.","es":"Exploren las opciones juntos. No se envía nada y no se inicia ninguna solicitud."},"sheetDone":{"en":"Done","es":"Listo"},"preferenceNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"preferenceClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6997,7 +6997,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"quiz":{"questions":[{"id":"trigger","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What can we help you with today?","es":"¿En qué te podemos ayudar hoy?"},"helpText":{"en":"No pressure — this just helps your specialist focus on what matters to you.","es":"Sin presión — esto ayuda a tu especialista a enfocarse en lo que te importa."},"type":"single","options":[{"id":"pain","label":{"en":"Back or Body Pain","es":"Dolor de Espalda o Cuerpo"},"icon":"spine","sublabel":{"en":"Current mattress is hurting me","es":"Mi colchón actual me lastima"},"scores":{}},{"id":"worn_out","label":{"en":"Old Mattress","es":"Colchón Viejo"},"icon":"sagging","sublabel":{"en":"Time for an upgrade","es":"Es hora de un cambio"},"scores":{}},{"id":"moving","label":{"en":"Moving or New Space","es":"Mudanza o Espacio Nuevo"},"icon":"family","sublabel":{"en":"New home, new bed","es":"Casa nueva, cama nueva"},"scores":{}},{"id":"upgrade","label":{"en":"Just Upgrading","es":"Mejorando"},"icon":"cloud","sublabel":{"en":"Ready for something better","es":"Listo para algo mejor"},"scores":{}},{"id":"browsing","label":{"en":"Just Browsing","es":"Solo Explorando"},"icon":"smile","sublabel":{"en":"Getting ideas, no rush","es":"Sin prisa, juntando ideas"},"scores":{}}]},{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"So every mattress we show actually fits your space.","es":"Nos aseguraremos de que las recomendaciones se ajusten a tu espacio"},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"Who shares your bed shapes which features matter most.","es":"Esto determina qué características importan más"},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"Motion isolation is one of the first upgrades you'll feel.","es":"El aislamiento de movimiento es una de las mayores mejoras en un colchón nuevo"},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"Your sleep position is the biggest clue to the support you need.","es":"Piensa en cómo terminas naturalmente"},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"Sleeping hot or cold is an easy fix with the right materials.","es":"La regulación de temperatura es clave para un sueño profundo"},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to what feels best.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. Each one points us toward a fix.","es":"Toca las que apliquen"},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durable":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. A few of these change what we'd suggest.","es":"Toca las que apliquen"},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durable":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
+          <t>{"quiz":{"questions":[{"id":"trigger","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What can we help you with today?","es":"¿En qué te podemos ayudar hoy?"},"helpText":{"en":"This doesn't change your sleep-fit ranking. It helps your specialist focus on what matters to you.","es":"Esto no cambia el orden de tus opciones. Ayuda a tu especialista a enfocarse en lo que te importa."},"type":"single","options":[{"id":"pain","label":{"en":"Back or Body Pain","es":"Dolor de Espalda o Cuerpo"},"icon":"spine","sublabel":{"en":"Current mattress is hurting me","es":"Mi colchón actual me lastima"},"scores":{}},{"id":"worn_out","label":{"en":"Old Mattress","es":"Colchón Viejo"},"icon":"sagging","sublabel":{"en":"Time for an upgrade","es":"Es hora de un cambio"},"scores":{}},{"id":"moving","label":{"en":"Moving or New Space","es":"Mudanza o Espacio Nuevo"},"icon":"family","sublabel":{"en":"New home, new bed","es":"Casa nueva, cama nueva"},"scores":{}},{"id":"upgrade","label":{"en":"Just Upgrading","es":"Mejorando"},"icon":"cloud","sublabel":{"en":"Ready for something better","es":"Listo para algo mejor"},"scores":{}},{"id":"browsing","label":{"en":"Just Browsing","es":"Solo Explorando"},"icon":"smile","sublabel":{"en":"Getting ideas, no rush","es":"Sin prisa, juntando ideas"},"scores":{}}]},{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"We carry your selected size into the consultation. Your sleep-fit ranking is based on your comfort and support answers.","es":"Llevamos el tamaño que elijas a la consulta. El orden de tus opciones se basa en tus respuestas sobre comodidad y soporte."},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"This shapes the questions that follow and what we suggest testing together.","es":"Esto define las preguntas que siguen y lo que sugerimos probar juntos."},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"The more movement wakes you, the more it shapes your matches and what we suggest testing.","es":"Cuanto más te despierte el movimiento, más influye en tus opciones y en lo que sugerimos probar."},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"This helps us favor pressure relief, support, or a responsive feel.","es":"Esto nos ayuda a priorizar alivio de presión, soporte o una sensación más reactiva."},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"If you sleep hot, we favor cooling features in your matches.","es":"Si duermes con calor, priorizamos características frescas en tus opciones."},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to the feel you prefer.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. These shape which features we favor and what we suggest testing.","es":"Toca lo que hayas notado. Esto define qué características priorizamos y qué sugerimos probar."},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durable":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. Some shape your matches; some change what we suggest trying, like an adjustable base or a mattress protector.","es":"Marca lo que aplique. Algunas influyen en tus opciones; otras cambian lo que sugerimos probar, como una base ajustable o un protector de colchón."},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durable":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6997,7 +6997,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"quiz":{"questions":[{"id":"trigger","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What can we help you with today?","es":"¿En qué te podemos ayudar hoy?"},"helpText":{"en":"This doesn't change your sleep-fit ranking. It helps your specialist focus on what matters to you.","es":"Esto no cambia el orden de tus opciones. Ayuda a tu especialista a enfocarse en lo que te importa."},"type":"single","options":[{"id":"pain","label":{"en":"Back or Body Pain","es":"Dolor de Espalda o Cuerpo"},"icon":"spine","sublabel":{"en":"Current mattress is hurting me","es":"Mi colchón actual me lastima"},"scores":{}},{"id":"worn_out","label":{"en":"Old Mattress","es":"Colchón Viejo"},"icon":"sagging","sublabel":{"en":"Time for an upgrade","es":"Es hora de un cambio"},"scores":{}},{"id":"moving","label":{"en":"Moving or New Space","es":"Mudanza o Espacio Nuevo"},"icon":"family","sublabel":{"en":"New home, new bed","es":"Casa nueva, cama nueva"},"scores":{}},{"id":"upgrade","label":{"en":"Just Upgrading","es":"Mejorando"},"icon":"cloud","sublabel":{"en":"Ready for something better","es":"Listo para algo mejor"},"scores":{}},{"id":"browsing","label":{"en":"Just Browsing","es":"Solo Explorando"},"icon":"smile","sublabel":{"en":"Getting ideas, no rush","es":"Sin prisa, juntando ideas"},"scores":{}}]},{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"We carry your selected size into the consultation. Your sleep-fit ranking is based on your comfort and support answers.","es":"Llevamos el tamaño que elijas a la consulta. El orden de tus opciones se basa en tus respuestas sobre comodidad y soporte."},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"This shapes the questions that follow and what we suggest testing together.","es":"Esto define las preguntas que siguen y lo que sugerimos probar juntos."},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"The more movement wakes you, the more it shapes your matches and what we suggest testing.","es":"Cuanto más te despierte el movimiento, más influye en tus opciones y en lo que sugerimos probar."},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"This helps us favor pressure relief, support, or a responsive feel.","es":"Esto nos ayuda a priorizar alivio de presión, soporte o una sensación más reactiva."},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"If you sleep hot, we favor cooling features in your matches.","es":"Si duermes con calor, priorizamos características frescas en tus opciones."},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to the feel you prefer.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. These shape which features we favor and what we suggest testing.","es":"Toca lo que hayas notado. Esto define qué características priorizamos y qué sugerimos probar."},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durable":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. Some shape your matches; some change what we suggest trying, like an adjustable base or a mattress protector.","es":"Marca lo que aplique. Algunas influyen en tus opciones; otras cambian lo que sugerimos probar, como una base ajustable o un protector de colchón."},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durable":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
+          <t>{"quiz":{"questions":[{"id":"trigger","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What can we help you with today?","es":"¿En qué te podemos ayudar hoy?"},"helpText":{"en":"This doesn't change your sleep-fit ranking. It helps your specialist focus on what matters to you.","es":"Esto no cambia el orden de tus opciones. Ayuda a tu especialista a enfocarse en lo que te importa."},"type":"single","options":[{"id":"pain","label":{"en":"Back or Body Pain","es":"Dolor de Espalda o Cuerpo"},"icon":"spine","sublabel":{"en":"Current mattress is hurting me","es":"Mi colchón actual me lastima"},"scores":{}},{"id":"worn_out","label":{"en":"Old Mattress","es":"Colchón Viejo"},"icon":"sagging","sublabel":{"en":"Time for an upgrade","es":"Es hora de un cambio"},"scores":{}},{"id":"moving","label":{"en":"Moving or New Space","es":"Mudanza o Espacio Nuevo"},"icon":"family","sublabel":{"en":"New home, new bed","es":"Casa nueva, cama nueva"},"scores":{}},{"id":"upgrade","label":{"en":"Just Upgrading","es":"Mejorando"},"icon":"cloud","sublabel":{"en":"Ready for something better","es":"Listo para algo mejor"},"scores":{}},{"id":"browsing","label":{"en":"Just Browsing","es":"Solo Explorando"},"icon":"smile","sublabel":{"en":"Getting ideas, no rush","es":"Sin prisa, juntando ideas"},"scores":{}}]},{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"We carry your selected size into the consultation. Your sleep-fit ranking is based on your comfort and support answers.","es":"Tomamos en cuenta el tamaño que elijas en la consulta. El orden de tus opciones se basa en tus respuestas sobre comodidad y soporte."},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"This shapes the questions that follow and what we suggest testing together.","es":"Esto define las preguntas que siguen y lo que sugerimos probar juntos."},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"The more movement wakes you, the more it shapes your matches and what we suggest testing.","es":"Cuanto más te despierte el movimiento, más influye en tus opciones y en lo que sugerimos probar."},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"This helps us favor pressure relief, support, or a responsive feel.","es":"Esto nos ayuda a priorizar alivio de presión, soporte o una sensación con más respuesta."},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"If you sleep hot, we favor cooling features in your matches.","es":"Si duermes con calor, priorizamos materiales refrescantes en tus opciones."},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to the feel you prefer.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. These shape which features we favor and what we suggest testing.","es":"Toca lo que hayas notado. Esto define qué características priorizamos y qué sugerimos probar."},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durable":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. Some shape your matches; some change what we suggest trying, like an adjustable base or a mattress protector.","es":"Toca lo que aplique. Algunas influyen en tus opciones; otras cambian lo que sugerimos probar, como una base ajustable o un protector de colchón."},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durable":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6969,7 +6969,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","surfaces":{"drawer":false,"sleepSystem":false},"allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"welcomeTagline":{"en":"Flexible ways to bring better sleep home.","es":"Formas flexibles de llevar mejor descanso a casa."},"welcomeSupport":{"en":"Explore payment options after finding your strongest mattress matches.","es":"Explora opciones de pago después de encontrar tus mejores opciones de colchón."},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"paymentPreferenceLabel":{"en":"Payment preference","es":"Preferencia de pago"},"preferenceNone":{"en":"Not selected","es":"Sin seleccionar"},"optionsExploredLabel":{"en":"Options explored","es":"Opciones exploradas"},"reviewOption":{"en":"Review this option","es":"Revisar esta opción"},"hideDetails":{"en":"Hide details","es":"Ocultar detalles"},"considerOption":{"en":"Consider this option","es":"Considerar esta opción"},"currentlyConsidering":{"en":"Currently considering ✓","es":"En consideración ✓"},"clearPreference":{"en":"Clear preference","es":"Quitar preferencia"},"preferenceNotNow":{"en":"Not right now","es":"Ahora no"},"exploreConsequence":{"en":"Explore options together. Nothing is submitted and no application is started.","es":"Exploren las opciones juntos. No se envía nada y no se inicia ninguna solicitud."},"sheetDone":{"en":"Done","es":"Listo"},"preferenceNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"preferenceClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
+          <t>{"promotions":{"schemaVersion":1,"activeScenario":null,"allowedSourceHosts":["lacks.com"],"scenarios":{}},"financing":{"enabled":true,"experience":"payment-choice","offerVersion":"2026-07-30a","verifiedAt":"2026-07-31T16:43:00-05:00","maxAgeDays":7,"sourceUrl":"https://www.lacks.com/financing","applicationUrl":"https://www.lacks.com/credit-application","mexicoInfoUrl":"https://www.lacks.com/faq","mexicoApplicationUrl":{"url":"https://www.lacks.com/mexican-credit-application","verified":false,"note":"Published in Lacks' FAQ but returned 404 on 2026-07-30. Do not render as a link until it resolves; the Mexico card links to mexicoInfoUrl."},"savingsPassPolicy":"specialist_confirm","exactPromotionsEnabled":false,"esReviewStatus":"pending-native-legal-review","surfaces":{"drawer":false,"sleepSystem":false},"allowedSourceHosts":["lacks.com","www.lacks.com","synchrony.com","www.synchrony.com","mysynchrony.com"],"copy":{"eyebrow":{"en":"LACKS PAYMENT CHOICE","es":"OPCIONES DE PAGO LACKS"},"headline":{"en":"Better sleep. More ways to bring it home.","es":"Duerme mejor. Más opciones para llevarlo a casa."},"body":{"en":"Explore promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Options are subject to terms and approval.","es":"Explora financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. Las opciones están sujetas a términos y aprobación."},"cta":{"en":"Explore payment options","es":"Explorar opciones de pago"},"resultsLead":{"en":"Your strongest mattress match may have more than one way to bring it home.","es":"Tu mejor opción de colchón puede tener más de una forma de llegar a casa."},"fitFirst":{"en":"Your matches are based on sleep fit — never on payment method.","es":"Tus opciones se basan en tu descanso — nunca en la forma de pago."},"drawerTitle":{"en":"Ways to bring it home","es":"Formas de llevarlo a casa"},"drawerBody":{"en":"This recommendation is based on your sleep fit. When you're ready, Lacks offers more than one way to bring it home.","es":"Esta recomendación se basa en tu descanso. Cuando estés listo, Lacks ofrece más de una forma de llevarlo a casa."},"sleepSystemGuidance":{"en":"Build the sleep setup that fits you first. Your Lacks specialist can then review current payment options for the complete plan.","es":"Primero arma el sistema de sueño que te quede bien. Después, tu especialista de Lacks puede revisar las opciones de pago actuales para el plan completo."},"handoffHeadline":{"en":"Your Sleep Plan. Your Payment Choices.","es":"Tu Plan de Sueño. Tus Opciones de Pago."},"handoffPrivate":{"en":"Continue on your phone — scan to open Lacks' official financing page.","es":"Continúa desde tu teléfono — escanea para abrir la página oficial de financiamiento de Lacks."},"paymentPreferenceLabel":{"en":"Payment preference","es":"Preferencia de pago"},"preferenceNone":{"en":"Not selected","es":"Sin seleccionar"},"optionsExploredLabel":{"en":"Options explored","es":"Opciones exploradas"},"reviewOption":{"en":"Review this option","es":"Revisar esta opción"},"hideDetails":{"en":"Hide details","es":"Ocultar detalles"},"considerOption":{"en":"Consider this option","es":"Considerar esta opción"},"currentlyConsidering":{"en":"Currently considering ✓","es":"En consideración ✓"},"clearPreference":{"en":"Clear preference","es":"Quitar preferencia"},"preferenceNotNow":{"en":"Not right now","es":"Ahora no"},"exploreConsequence":{"en":"Explore options together. Nothing is submitted and no application is started.","es":"Exploren las opciones juntos. No se envía nada y no se inicia ninguna solicitud."},"sheetDone":{"en":"Done","es":"Listo"},"preferenceNotNowAnnounce":{"en":"Not right now selected. You can change this choice.","es":"Se seleccionó 'Ahora no'. Puedes cambiar esta opción."},"preferenceClearedAnnounce":{"en":"Selection cleared. Choose again when you're ready.","es":"Se borró la selección. Elige de nuevo cuando quieras."},"staleNotice":{"en":"Current payment options are available from your Lacks specialist.","es":"Tu especialista de Lacks tiene las opciones de pago actuales."},"staleAnnouncement":{"en":"Exact rates and terms are not shown right now. Your Lacks specialist can confirm current payment options in store.","es":"Las tasas y los plazos exactos no se muestran en este momento. Tu especialista de Lacks puede confirmar las opciones de pago actuales en tienda."},"externalNotice":{"en":"Opens lacks.com — a separate site governed by its own terms and privacy policy.","es":"Abre lacks.com — un sitio aparte, regido por sus propios términos y política de privacidad."},"emailHeading":{"en":"Payment options","es":"Opciones de pago"},"emailBodyAvailable":{"en":"Lacks Payment Choice offers more than one way to bring it home: promotional financing, Lacks In-House Credit, lease-to-own, and Build My Credit. Final pricing, eligibility, terms, and approval are confirmed by Lacks.","es":"Las Opciones de Pago Lacks ofrecen más de una forma de llevarlo a casa: financiamiento promocional, Crédito Interno de Lacks, arrendamiento con opción a compra y Build My Credit. El precio final, la elegibilidad, los términos y la aprobación los confirma Lacks."},"disclosureFooter":{"en":"All payment options are subject to terms and approval. Advertised purchase minimums, rates, and terms are set by Lacks and its financing partners and may change or end at any time. Your Lacks specialist confirms current details in store.","es":"Todas las opciones de pago están sujetas a términos y aprobación. Los mínimos de compra, tasas y plazos anunciados los establecen Lacks y sus socios financieros y pueden cambiar o terminar en cualquier momento. Tu especialista de Lacks confirma los detalles vigentes en tienda."},"prequalNote":{"en":"See if you prequalify on Lacks' official financing page — prequalification is not approval.","es":"Consulta si precalificas en la página oficial de financiamiento de Lacks — precalificar no es una aprobación."}},"plans":[{"id":"synchrony-9-99-72","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":9.99,"termMonths":72,"minimumPurchase":500,"channel":"per-current-source","calculationMode":"published-fixed-factor","paymentCalculationEnabled":false,"headline":{"en":"9.99% APR for 72 months","es":"9.99% APR por 72 meses"},"detail":{"en":"On qualifying purchases of $500 or more with the Lacks Furniture Synchrony HOME Credit Card. Fixed monthly payments required. Interest is charged from the purchase date at the reduced APR. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras que califiquen de $500 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales fijos. Se cobra interés desde la fecha de compra a la tasa APR reducida. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2. Lacks may alter or discontinue this offer at any time.","es":"Sujeto a aprobación de crédito. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2. Lacks puede modificar o descontinuar esta oferta en cualquier momento."}},{"id":"synchrony-0-48","kind":"open-end-promotional-credit","provider":"Synchrony","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","apr":0,"termMonths":48,"minimumPurchase":4200,"channel":"in-store","calculationMode":"not-published","paymentCalculationEnabled":false,"headline":{"en":"0% APR for 48 months","es":"0% APR por 48 meses"},"detail":{"en":"On qualifying in-store purchases of $4,200 or more with the Lacks Furniture Synchrony HOME Credit Card. Equal monthly payments required. A minimum purchase and a down payment, plus tax and delivery fee, are required. The advertised purchase minimum must be met on one receipt; discounts may reduce the purchase below it.","es":"En compras en tienda que califiquen de $4,200 o más con la tarjeta Lacks Furniture Synchrony HOME. Se requieren pagos mensuales iguales. Se requiere una compra mínima y un enganche, más impuestos y cargo de entrega. El mínimo de compra anunciado debe cumplirse en un solo recibo; los descuentos pueden reducir la compra por debajo del mínimo."},"disclosure":{"en":"Subject to credit approval. No interest is charged on the promotional purchase. Regular account terms apply to non-promo purchases; for new accounts as of 07/31/2025 the purchase APR is 34.99%, penalty APR 39.99%, minimum interest charge $2.","es":"Sujeto a aprobación de crédito. No se cobra interés en la compra promocional. Los términos regulares de la cuenta aplican a compras fuera de promoción; para cuentas nuevas al 07/31/2025 la tasa APR de compra es 34.99%, la APR de penalización 39.99% y el cargo mínimo por interés $2."}},{"id":"lacks-in-house","kind":"closed-end-installment","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lacks In-House Credit","es":"Crédito Interno de Lacks"},"detail":{"en":"Installment contracts may be available from 6–36 months for qualifying customers, with in-house approvals by Lacks' own credit team. Purchases may also qualify for promotional pricing. Subject to Lacks approval and applicable offer terms.","es":"Para clientes que califiquen, puede haber contratos a plazos de 6 a 36 meses, con aprobación interna del propio equipo de crédito de Lacks. Las compras también pueden calificar para precios promocionales. Sujeto a la aprobación de Lacks y a los términos de la oferta aplicable."},"disclosure":{"en":"Availability, terms, and promotional pricing are confirmed by Lacks in store.","es":"La disponibilidad, los términos y los precios promocionales los confirma Lacks en tienda."}},{"id":"lease-to-own","kind":"lease-to-own","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Lease-to-own","es":"Arrendamiento con opción a compra"},"detail":{"en":"Lease-to-own is available. Program details, costs, eligibility, and ownership terms are confirmed in store.","es":"El arrendamiento con opción a compra está disponible. Los detalles del programa, costos, elegibilidad y términos de propiedad se confirman en tienda."}},{"id":"build-my-credit","kind":"credit-builder","provider":"Lacks","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/financing","paymentCalculationEnabled":false,"headline":{"en":"Build My Credit","es":"Build My Credit"},"detail":{"en":"An available path for customers with little or no credit history. Program details are confirmed in store.","es":"Una opción disponible para clientes con poco o ningún historial de crédito. Los detalles del programa se confirman en tienda."}},{"id":"mexico-in-house","kind":"closed-end-installment","provider":"Lacks","presentationScenario":"mexico-delivery","verified":true,"verifiedAt":"2026-07-31T16:43:00-05:00","sourceUrl":"https://www.lacks.com/faq","apr":24,"termMonths":24,"paymentCalculationEnabled":false,"headline":{"en":"Purchasing for delivery to Mexico?","es":"¿Compras para entrega en México?"},"detail":{"en":"An optional program for customers purchasing for delivery to Mexico: Lacks in-house credit for up to 24 months with a maximum contract APR of 24% (which may vary). Requirements currently include two official IDs, three personal references, and income verification.","es":"Un programa opcional para clientes que compran para entrega en México: crédito interno de Lacks hasta por 24 meses con un interés máximo del contrato de 24% APR (mismo que puede variar). Los requisitos actuales incluyen dos identificaciones oficiales, 3 referencias personales y verificación de ingresos."},"representativeExample":{"en":"Lacks' published example: $999 financed for 24 months at 24% APR equals 24 monthly payments of $52.82.","es":"Ejemplo publicado por Lacks: $999 financiados durante 24 meses con 24% APR tendrán 24 pagos mensuales de $52.82."},"disclosure":{"en":"For purchases intended for delivery to Mexico, ask a Lacks specialist to confirm current details and requirements.","es":"Para compras destinadas a entrega en México, consulta con un especialista de Lacks para confirmar los detalles y requisitos actuales."}}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -14,6 +14,7 @@
     <sheet name="SalesNotes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Promotions" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Quiz" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Pricing" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7004,4 +7005,32 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Pricing JSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{"pricing":{"schemaVersion":1,"enabled":false,"displayEnabled":false,"currency":"USD","authority":{"owner":"","role":""},"mapClearance":{"status":"not-cleared","clearedBy":"","clearedAt":null},"esReviewStatus":"pending-native-legal-review","maxAgeDays":7,"allowedSourceHosts":["lacks.com","www.lacks.com"],"sizes":["twin","twin_xl","full","queen","king","cal_king"],"surfaces":{"drawer":false,"sleepSystem":false,"results":false,"handoff":false,"sleepPlan":false},"purchaseAssessment":{"basis":"unknown"},"products":[],"formulas":[]}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -7026,7 +7026,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"pricing":{"schemaVersion":1,"enabled":false,"displayEnabled":false,"currency":"USD","authority":{"owner":"","role":""},"mapClearance":{"status":"not-cleared","clearedBy":"","clearedAt":null},"esReviewStatus":"pending-native-legal-review","maxAgeDays":7,"allowedSourceHosts":["lacks.com","www.lacks.com"],"sizes":["twin","twin_xl","full","queen","king","cal_king"],"surfaces":{"drawer":false,"sleepSystem":false,"results":false,"handoff":false,"sleepPlan":false},"purchaseAssessment":{"basis":"unknown"},"products":[],"formulas":[]}}</t>
+          <t>{"pricing":{"schemaVersion":1,"enabled":false,"displayEnabled":false,"currency":"USD","authority":{"owner":"","role":""},"freshness":{"status":"unapproved","maxAgeDays":null,"approvedBy":"","approvedAt":null},"sourcePolicy":{"status":"unapproved","allowedSourceHosts":[],"approvedBy":"","approvedAt":null},"purchaseAssessment":{"policy":"runtime-transaction-amount"},"sizes":["twin","twin_xl","full","queen","king","cal_king"],"surfaces":{"drawer":false,"sleepSystem":false,"results":false,"handoff":false,"sleepPlan":false},"presentation":{"status":"unapproved","approvals":{"business":{"status":"unapproved","by":"","at":null},"legal":{"status":"unapproved","by":"","at":null},"nativeReview":{"status":"pending","by":"","at":null}},"assumptions":[],"disclosures":[],"states":{}},"products":[],"formulas":[]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -2699,7 +2699,11 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Individually pocketed coils that move independently, zoned for targeted support, with foam encasement around the edge.</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
@@ -2747,7 +2751,11 @@
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Resortes embolsados individualmente que se mueven de forma independiente, zonificados para brindar soporte focalizado, con encapsulado de espuma alrededor del borde.</t>
+        </is>
+      </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
@@ -3234,7 +3242,11 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rated Firm, with less give at the surface and a tight-top construction without a pillow-top layer.</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
@@ -3278,7 +3290,11 @@
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Nivel de confort firme, con menos hundimiento en la superficie y una construcción tight top sin capa tipo pillow top.</t>
+        </is>
+      </c>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr">
         <is>
@@ -4138,7 +4154,11 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rated Firm, with less give and more pushback at the surface.</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr">
         <is>
@@ -4186,7 +4206,11 @@
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
+        </is>
+      </c>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr">
         <is>
@@ -4849,7 +4873,11 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Rated Medium — a balanced feel between plush and firm.</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
@@ -4897,7 +4925,11 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Nivel de confort medio: una sensación equilibrada entre suave y firme.</t>
+        </is>
+      </c>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr">

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -2862,7 +2862,11 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rated Extra Firm — a very firm feel with little give at the surface.</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2906,7 +2910,11 @@
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Nivel de confort extra firme: una sensación muy firme, con poco hundimiento en la superficie.</t>
+        </is>
+      </c>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr">
         <is>
@@ -3098,7 +3106,11 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rated Firm, with less give and more pushback at the surface.</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
@@ -3142,7 +3154,11 @@
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
+        </is>
+      </c>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr">
@@ -3385,7 +3401,11 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Rated Medium — a balanced feel between plush and firm.</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
@@ -3413,7 +3433,11 @@
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Nivel de confort medio: una sensación equilibrada entre suave y firme.</t>
+        </is>
+      </c>
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
@@ -3492,7 +3516,11 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Rated Plush — a softer feel with more give at the surface.</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
@@ -3516,7 +3544,11 @@
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Nivel de confort suave: una sensación más suave, con más hundimiento en la superficie.</t>
+        </is>
+      </c>
       <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
@@ -3598,7 +3630,11 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rated Firm, with less give and more pushback at the surface.</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
@@ -3638,7 +3674,11 @@
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
+        </is>
+      </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr">
@@ -4466,7 +4506,11 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rated Firm, with less give and more pushback at the surface.</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
@@ -4514,7 +4558,11 @@
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
+        </is>
+      </c>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr">
         <is>
@@ -4612,7 +4660,11 @@
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Rated Plush — a softer feel with more give at the surface.</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
@@ -4640,7 +4692,11 @@
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Nivel de confort suave: una sensación más suave, con más hundimiento en la superficie.</t>
+        </is>
+      </c>
       <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
@@ -4730,7 +4786,11 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rated Extra Firm — a very firm feel with little give at the surface.</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
@@ -4774,7 +4834,11 @@
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Nivel de confort extra firme: una sensación muy firme, con poco hundimiento en la superficie.</t>
+        </is>
+      </c>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr">

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -1348,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT27"/>
+  <dimension ref="A1:BL27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,82 +1504,172 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
+          <t>storyHeadline</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>storyNarrative</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>trialCue</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>proof1Title</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>proof1Cue</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>proof2Title</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>proof2Cue</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>constructionComfort</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>constructionSupport</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
           <t>displayBadges (ES)</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>highlight (ES)</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>reason_cooling (ES)</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>reason_pressureRelief (ES)</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>reason_motionIsolation (ES)</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>reason_support (ES)</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>reason_plush (ES)</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>reason_medium (ES)</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>reason_firm (ES)</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>reason_durability (ES)</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>reason_default (ES)</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>topPickReason (ES)</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>differentiator1Title (ES)</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>differentiator1Detail (ES)</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>differentiator2Title (ES)</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>differentiator2Detail (ES)</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>storyHeadline (ES)</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>storyNarrative (ES)</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>trialCue (ES)</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>proof1Title (ES)</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>proof1Cue (ES)</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>proof2Title (ES)</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>proof2Cue (ES)</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>constructionComfort (ES)</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>constructionSupport (ES)</t>
         </is>
       </c>
     </row>
@@ -1688,50 +1778,140 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
+          <t>Natural materials, architectural support.</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Merino wool, camel hair, cashmere and graphite latex create a tailored natural-fiber experience over layered coils.</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>Lie on your back and notice how the surface supports you before it gives.</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Natural-fiber comfort</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Reveal the wool, camel hair and cashmere comfort materials.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Responsive layered support</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Roll once and feel the buoyant response of latex over multiple coil layers.</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Merino wool, camel hair, cashmere and graphite latex</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Multiple coil layers</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
           <t>Fibras Naturales de Lujo|Firme|Euro-Top</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>Lujo firme artesanal en lana Merino y cachemira</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
         <is>
           <t>Lana Merino, cachemira y látex de grafito sobre múltiples capas de resortes — soporte firme que respira y dura.</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>Lujo artesanal de fibras naturales con soporte firme de doble resorte que respira.</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AZ2" t="inlineStr">
         <is>
           <t>Capas de confort de fibras naturales</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>La lana Merino, el pelo de camello y la cachemira respiran y regulan el calor como las espumas sintéticas no pueden.</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>Doble resorte con látex de grafito</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>Elevación receptiva y estabilidad en lugar del hundimiento lento de la espuma viscoelástica.</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>Materiales naturales, soporte arquitectónico.</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>Lana Merino, pelo de camello, cachemira y látex de grafito crean una experiencia a medida de fibras naturales sobre capas de resortes.</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>Acuéstate boca arriba y nota cómo la superficie te sostiene antes de ceder.</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Confort de fibras naturales</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>Muestra los materiales de confort: lana, pelo de camello y cachemira.</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>Soporte receptivo en capas</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>Gira una vez y siente la respuesta elástica del látex sobre varias capas de resortes.</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>Lana Merino, pelo de camello, cachemira y látex de grafito</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>Varias capas de resortes</t>
         </is>
       </c>
     </row>
@@ -1828,40 +2008,122 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
+          <t>Natural-fiber indulgence.</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>A deep plush euro-top turns wool and cashmere into a softer, enveloping expression of handcrafted comfort.</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Settle in slowly and let the euro-top take your shoulder and hip.</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Deep plush euro-top</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Settle into the generously cushioned surface.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Breathable natural fill</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Reveal the wool and cashmere beneath the plush finish.</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Deep plush euro-top with wool and cashmere</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr">
+        <is>
           <t>Fibras Naturales de Lujo|Suave|Euro-Top</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Un euro-top suave y profundo de lana y cachemira sobre capas de resortes — suavidad indulgente que nunca pierde su soporte.</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr">
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>Euro-top suave y profundo</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>Relleno natural transpirable</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>La lana y la cachemira mantienen las capas suaves más frescas que los pillow-tops de espuma densa.</t>
         </is>
       </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>Indulgencia en fibras naturales.</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>Un euro-top mullido y profundo convierte la lana y la cachemira en una expresión más suave y envolvente del confort artesanal.</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>Acomódate despacio y deja que el euro-top reciba tu hombro y tu cadera.</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Euro-top mullido y profundo</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>Acomódate en la superficie generosamente acolchada.</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>Relleno natural transpirable</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>Muestra la lana y la cachemira bajo el acabado mullido.</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>Euro-top mullido y profundo con lana y cachemira</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1964,48 +2226,138 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
+          <t>Craft you can see.</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Hand tufting and 4,294 coils make construction, not decoration, the luxury story.</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Lie across the surface and notice how evenly it holds you.</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Hand-tufted construction</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Point out the visible tufting that holds the comfort layers together.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Fine-grained coil support</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Lie across the surface and feel the composed firm response.</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Hand-tufted comfort layers</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>4,294 coils</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
           <t>4,294 Resortes|Firme|Copetudo a Mano</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>4,294 resortes de soporte firme copetudo a mano</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr">
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr">
         <is>
           <t>4,294 resortes, lana Merino y construcción copetuda a mano — alineación firme diseñada para durar décadas.</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Enorme cantidad de 4,294 resortes con artesanía copetuda a mano para una alineación firme y duradera.</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>Sistema de 4,294 resortes</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>Varias veces los resortes de una cama estándar — soporte firme más fino y contorneado.</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>Construcción copetuda a mano</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>Artesanía a la vista.</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>El acolchado a mano y 4,294 resortes hacen de la construcción, no de la decoración, la historia de lujo.</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>Acuéstate a lo ancho y nota lo uniforme que te sostiene.</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Construcción acolchada a mano</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>Señala el acolchado visible que mantiene unidas las capas de confort.</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Soporte de resortes de grano fino</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>Acuéstate a lo ancho y siente la respuesta firme y serena.</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>Capas de confort acolchadas a mano</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>4,294 resortes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2096,36 +2448,118 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>Cool, slow-settling comfort.</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Cooling materials temper the deeply conforming character of soft TEMPUR material.</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Stay still for a full minute and feel the material settle around you.</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Cooling surface</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Touch the cover before lying down.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Soft TEMPUR contour</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Remain still long enough to feel the material gradually settle around the body.</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Cooling cover over soft TEMPUR material</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr">
+        <is>
           <t>Frescura|Suave|Espuma Viscoelástica</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>El colchón más fresco de Tempur-Pedic — el material Pure Cool Plus disipa el calor mientras el TEMPUR suave abraza cada curva.</t>
-        </is>
-      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr">
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>El colchón más fresco de Tempur-Pedic — el material Pure Cool Plus disipa el calor mientras el TEMPUR suave abraza cada curva.</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>Contorno TEMPUR suave</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>Se acomoda lentamente alrededor de los puntos de presión en lugar de empujar como los resortes.</t>
         </is>
       </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>Confort fresco que se asienta despacio.</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>Los materiales frescos moderan el carácter profundamente adaptable del material TEMPUR suave.</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>Quédate quieto un minuto completo y siente cómo el material se asienta a tu alrededor.</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Superficie fresca</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>Toca la funda antes de acostarte.</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Contorno suave TEMPUR</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>Quédate quieto lo suficiente para sentir cómo el material se asienta gradualmente alrededor del cuerpo.</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>Funda fresca sobre material TEMPUR suave</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2224,42 +2658,132 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>Cooling with responsive lift.</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>The Breeze surface and TEMPUR pressure relief sit over a responsive hybrid foundation.</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Roll over once and notice how easily you move.</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Cool-to-touch Breeze cover</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Place a hand on the surface and notice the immediate cool feel.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Hybrid coil response</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Roll or sit up and notice the coil-assisted movement.</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Breeze cover over TEMPUR material</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Hybrid coil base</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
           <t>Frescura|Híbrido|Medio</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Funda Breeze fresca al tacto y material Pure Cool sobre una base híbrida de resortes — frescura más el verdadero alivio de presión TEMPUR.</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr">
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>Funda Breeze fresca al tacto</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>Notablemente más fresco al contacto que los modelos TEMPUR estándar.</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>Base híbrida de resortes</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>Agrega ventilación y un toque de respuesta bajo la espuma viscoelástica.</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>Frescura con elevación receptiva.</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>La superficie Breeze y el alivio de presión TEMPUR descansan sobre una base híbrida receptiva.</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>Gira una vez y nota lo fácil que te mueves.</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Funda Breeze fresca al tacto</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>Coloca una mano sobre la superficie y nota la sensación fresca inmediata.</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Respuesta de resortes híbrida</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>Gira o siéntate y nota el movimiento asistido por los resortes.</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>Funda Breeze sobre material TEMPUR</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>Base híbrida de resortes</t>
         </is>
       </c>
     </row>
@@ -2336,24 +2860,114 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>Hand-built natural luxury with a plush finish.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>The Mayfair's natural and responsive comfort stack is presented with a deeply cushioned plush feel.</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Settle into the plush surface, then move and feel it recover.</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Hand-tufted cooling surface</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Touch the Tencel cover and notice the smooth, cool first contact.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Natural responsive comfort</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Press and release the wool, latex and microcoil comfort stack to feel its quick recovery.</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Hand-tufted Tencel cover over wool, latex and microcoils</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Zoned coils</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
           <t>Suave</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>Lujo natural hecho a mano con acabado mullido.</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>La capa de confort natural y receptiva del Mayfair se presenta con una sensación mullida y profundamente acolchada.</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>Acomódate en la superficie mullida, luego muévete y siente cómo se recupera.</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Superficie fresca acolchada a mano</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>Toca la funda de Tencel y nota el primer contacto suave y fresco.</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Confort natural y receptivo</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>Presiona y suelta la capa de lana, látex y microrresortes para sentir su rápida recuperación.</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>Funda de Tencel acolchada a mano sobre lana, látex y microrresortes</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>Resortes por zonas</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2428,24 +3042,114 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>Hand-tufted balance in natural materials.</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Wool, latex, specialty foams, microcoils and zoned coils create a composed medium feel.</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Lie on your side and notice the balanced give and quick recovery.</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Hand-tufted cooling surface</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Touch the Tencel cover and notice the smooth, cool first contact.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Natural responsive comfort</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Press and release the wool, latex and microcoil comfort stack to feel its quick recovery.</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Hand-tufted Tencel cover over wool, latex and microcoils</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Zoned coils</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>Equilibrio acolchado a mano en materiales naturales.</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>Lana, látex, espumas especiales, microrresortes y resortes por zonas crean una sensación media y serena.</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>Acuéstate de lado y nota la cesión equilibrada y la rápida recuperación.</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Superficie fresca acolchada a mano</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>Toca la funda de Tencel y nota el primer contacto suave y fresco.</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Confort natural y receptivo</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>Presiona y suelta la capa de lana, látex y microrresortes para sentir su rápida recuperación.</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>Funda de Tencel acolchada a mano sobre lana, látex y microrresortes</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>Resortes por zonas</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2520,24 +3224,114 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
+          <t>Natural luxury with an uncompromising foundation.</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>A hand-tufted cooling surface, wool, latex and microcoils dress an assertively firm support system.</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Lie on your back and feel how little the surface gives.</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Hand-tufted natural comfort</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Touch the cooling surface and reveal the wool and latex beneath it.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Reinforced extra-firm support</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Lie through the center and feel the restrained surface over zoned coils.</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Hand-tufted cooling surface over wool, latex and microcoils</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Zoned coils, extra-firm</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
           <t>Extra Firme</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>Lujo natural con una base sin concesiones.</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>Una superficie fresca acolchada a mano, lana, látex y microrresortes visten un sistema de soporte decididamente firme.</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>Acuéstate boca arriba y siente lo poco que cede la superficie.</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Confort natural acolchado a mano</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>Toca la superficie fresca y muestra la lana y el látex debajo.</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>Soporte extra firme reforzado</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>Acuéstate por el centro y siente la superficie contenida sobre los resortes por zonas.</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>Superficie fresca acolchada a mano sobre lana, látex y microrresortes</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>Resortes por zonas, extra firmes</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2612,24 +3406,114 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>Copper from surface to comfort core.</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Copper fabric and copper-infused comfort materials give this cushion-firm hybrid a distinctive material identity.</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Press a hand into the surface, then lie down and feel the cushion over the firm core.</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Copper textile</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Identify the copper-bearing surface fabric.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Copper-infused comfort</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Reveal how the copper story continues through the comfort materials.</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Copper fabric and copper-infused comfort materials</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Hybrid coils</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
           <t>Cushion Firm</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>Cobre desde la superficie hasta el núcleo de confort.</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>La tela de cobre y los materiales de confort infundidos con cobre dan a este híbrido cushion-firm una identidad material distintiva.</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>Presiona la superficie con la mano, luego acuéstate y siente el acolchado sobre el núcleo firme.</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Textil de cobre</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>Identifica la tela superficial con cobre.</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>Confort infundido con cobre</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>Muestra cómo la historia del cobre continúa en los materiales de confort.</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>Tela de cobre y materiales de confort infundidos con cobre</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>Resortes híbridos</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2740,54 +3624,144 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
+          <t>A grand box-top with a disciplined center.</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>The tall tailored profile delivers surface refinement while center zoning supplies the underlying structure.</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Lie through the center and feel the firm support under the tailored top.</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Tailored box-top</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Notice the finished comfort profile before settling into the firm core.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Marvelous Middle zoning</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Lie through the center and feel the reinforced support beneath the hips.</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Tall tailored box-top</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Marvelous Middle center zoning</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
           <t>Marvelous Middle|Firme|Box Top</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>Box top de lujo de 16 pulgadas con soporte firme zonificado</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr">
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr">
         <is>
           <t>Resortes embolsados individualmente que se mueven de forma independiente, zonificados para brindar soporte focalizado, con encapsulado de espuma alrededor del borde.</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr">
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr">
         <is>
           <t>El patentado Marvelous Middle brinda 25% más soporte en el tercio central — donde tu cuerpo más lo necesita.</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr">
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Confort box-top de lujo con soporte firme zonificado en el centro.</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>Zonificación Marvelous Middle</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>25% más soporte bajo caderas y espalda baja, donde la mayoría de las camas se hunden primero.</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>Construcción box-top de lujo</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>Un perfil de 16 pulgadas con capas superficiales suaves sobre un núcleo firme.</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>Un gran box-top con un centro disciplinado.</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>El perfil alto y a medida ofrece refinamiento en la superficie mientras las zonas centrales aportan la estructura de fondo.</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>Acuéstate por el centro y siente el soporte firme bajo la capa superior a medida.</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Box-top a medida</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>Nota el perfil de confort terminado antes de asentarte en el núcleo firme.</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Zonas Marvelous Middle</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>Acuéstate por el centro y siente el soporte reforzado bajo las caderas.</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>Box-top alto y a medida</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>Zonas centrales Marvelous Middle</t>
         </is>
       </c>
     </row>
@@ -2896,52 +3870,142 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
+          <t>Extra-firm support dressed in rich layers.</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Natural and temperature-conscious comfort layers add refinement without softening the mattress's decisive stance.</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Lie on your back and notice the limited give above the support.</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Rich comfort stack</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Reveal the natural and cooling materials above the support system.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Reinforced center and edge</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Test the center and perimeter while noticing the limited surface give.</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Natural and cooling comfort layers</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Reinforced center and edge</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
           <t>Marvelous Middle|Extra Firme|Híbrido</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>Máximo soporte con capas de confort de lujo Paige</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr">
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr">
         <is>
           <t>Nivel de confort extra firme: una sensación muy firme, con poco hundimiento en la superficie.</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr">
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Soporte híbrido extra firme con zonificación Marvelous Middle — máxima elevación sin renunciar a las capas de lujo.</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
+      <c r="AY12" t="inlineStr">
         <is>
           <t>El Platinum más firme — soporte extra firme zonificado en construcción de lujo.</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr">
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>Núcleo de soporte extra firme</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>Notablemente más firme que el Paige Firme — para quienes no quieren hundirse nada.</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>Tercio central zonificado</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>Soporte extra firme vestido con capas ricas.</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>Las capas de confort naturales y atentas a la temperatura añaden refinamiento sin suavizar el carácter decidido del colchón.</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>Acuéstate boca arriba y nota lo poco que cede sobre el soporte.</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Capa de confort rica</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>Muestra los materiales naturales y frescos sobre el sistema de soporte.</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>Centro y borde reforzados</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>Prueba el centro y el perímetro mientras notas la cesión limitada de la superficie.</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>Capas de confort naturales y frescas</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>Centro y borde reforzados</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3016,24 +4080,114 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
+          <t>Plush above, structured beneath.</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Cooling comfort layers create the welcome while zoned wrapped coils and edge encasement provide hidden discipline.</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>Lie on your side and let the shoulder settle before you judge the support.</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Plush box-top comfort</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Try a normal side-sleeping position and let the shoulder settle.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Zoned edge-to-edge structure</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Move toward the perimeter and feel the supported edge.</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Cooling comfort layers, plush box-top</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Zoned wrapped coils with edge encasement</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
           <t>Box Top Suave</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>Mullido arriba, estructurado debajo.</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>Las capas de confort frescas dan la bienvenida mientras los resortes envueltos por zonas y el borde reforzado aportan una disciplina oculta.</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>Acuéstate de lado y deja que el hombro se asiente antes de juzgar el soporte.</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Confort de box-top mullido</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>Prueba una posición normal de lado y deja que el hombro se asiente.</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>Estructura por zonas de borde a borde</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>Muévete hacia el perímetro y siente el borde con soporte.</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>Capas de confort frescas, box-top mullido</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>Resortes envueltos por zonas con borde reforzado</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3140,50 +4294,140 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
+          <t>Firm, finished, edge-to-edge.</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>A tailored box-top takes the severity out of firm support while the encased perimeter preserves the surface.</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>Lie down, then sit near the edge and notice the supported surface.</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Finished firm surface</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Feel the tailored top before reaching the firmer support underneath.</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Supported perimeter</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Sit or lie near the edge and notice the usable surface.</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Tailored box-top</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Firm support with an encased perimeter</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
           <t>Box Top Firme|Resortes Zonificados|Soporte de Borde</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
         <is>
           <t>Confort box-top firme con soporte de resortes zonificados</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr">
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr">
         <is>
           <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr">
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Soporte firme zonificado en construcción box-top con confort de borde a borde.</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>Firme con acabado superior</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
+      <c r="BA14" t="inlineStr">
         <is>
           <t>Alineación firme sin la sensación dura y desnuda de un firme tight-top.</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
+      <c r="BB14" t="inlineStr">
         <is>
           <t>Encasado de borde de 3 pulgadas</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>Rieles de espuma de alta densidad mantienen la superficie útil hasta el borde.</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>Firme, terminado, de borde a borde.</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>Un box-top a medida quita la severidad al soporte firme mientras el perímetro reforzado conserva la superficie.</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>Acuéstate y luego siéntate cerca del borde y nota la superficie con soporte.</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Superficie firme y terminada</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>Siente la capa superior a medida antes de llegar al soporte más firme debajo.</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Perímetro con soporte</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>Siéntate o acuéstate cerca del borde y nota la superficie aprovechable.</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>Box-top a medida</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>Soporte firme con perímetro reforzado</t>
         </is>
       </c>
     </row>
@@ -3292,52 +4536,142 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
+          <t>Cool comfort over a decisive core.</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>The Summit construction presents its cooling comfort layers over a firm hybrid foundation.</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>Lie on your back and feel for the stable firm support beneath the comfort layer.</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Cooling comfort layers</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Touch the cooling cover, then settle into the breathable comfort foam beneath it.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Pocketed zoned support</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Change positions and feel the coil system respond beneath the surface.</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Cooling cover over breathable comfort foam</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Pocketed zoned coils</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
           <t>Gel Fresco|Firme|Híbrido</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>Espuma viscoelástica con gel fresco sobre soporte híbrido firme</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr">
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr">
         <is>
           <t>Nivel de confort firme, con menos hundimiento en la superficie y una construcción tight top sin capa tipo pillow top.</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr">
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Una capa completa de espuma con gel fresco sobre un núcleo híbrido firme — alivio de presión con efecto refrescante y alineación sólida.</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="AY15" t="inlineStr">
         <is>
           <t>Soporte híbrido firme coronado con espuma viscoelástica de gel fresco.</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr">
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>Capa de espuma con gel fresco</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
+      <c r="BA15" t="inlineStr">
         <is>
           <t>Agrega confort refrescante que un firme de resortes común no tiene.</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
+      <c r="BB15" t="inlineStr">
         <is>
           <t>Núcleo híbrido firme</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>Confort fresco sobre un núcleo decidido.</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>La construcción Summit presenta sus capas de confort frescas sobre una base híbrida firme.</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>Acuéstate boca arriba y busca el soporte firme y estable bajo la capa de confort.</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Capas de confort frescas</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>Toca la funda fresca y luego acomódate en la espuma de confort transpirable debajo.</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>Soporte de resortes por zonas</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>Cambia de posición y siente cómo responde el sistema de resortes bajo la superficie.</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>Funda fresca sobre espuma de confort transpirable</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>Resortes ensacados por zonas</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3424,36 +4758,126 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
+          <t>Temperature-conscious balance.</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Cooling comfort and pocketed support create an approachable medium hybrid.</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>Change positions once and notice the balanced give and easy movement.</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Cooling comfort layers</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Touch the cooling cover, then settle into the breathable comfort foam beneath it.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Pocketed zoned support</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Change positions and feel the coil system respond beneath the surface.</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Cooling cover over breathable comfort foam</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Pocketed zoned coils</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
           <t>Medio|Híbrido</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Nivel de confort medio: una sensación equilibrada entre suave y firme.</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>Medio que agrada a todos</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>La sensación en la que la mayoría de las parejas están de acuerdo — equilibrio entre suavidad y soporte.</t>
-        </is>
-      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>Nivel de confort medio: una sensación equilibrada entre suave y firme.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>Medio que agrada a todos</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>La sensación en la que la mayoría de las parejas están de acuerdo — equilibrio entre suavidad y soporte.</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>Equilibrio atento a la temperatura.</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>El confort fresco y el soporte ensacado crean un híbrido medio y accesible.</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>Cambia de posición una vez y nota la cesión equilibrada y el movimiento fácil.</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Capas de confort frescas</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>Toca la funda fresca y luego acomódate en la espuma de confort transpirable debajo.</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>Soporte de resortes por zonas</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>Cambia de posición y siente cómo responde el sistema de resortes bajo la superficie.</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>Funda fresca sobre espuma de confort transpirable</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>Resortes ensacados por zonas</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3536,32 +4960,122 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
+          <t>Cooling comfort with a softer welcome.</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>The Summit construction is expressed through a plush surface while retaining its pocketed support beneath.</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>Settle into the plush comfort, then change position and feel the support respond.</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Cooling comfort layers</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Touch the cooling cover, then settle into the breathable comfort foam beneath it.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Pocketed zoned support</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Change positions and feel the coil system respond beneath the surface.</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Cooling cover over breathable comfort foam</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Pocketed zoned coils</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
           <t>Suave|Híbrido</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Nivel de confort suave: una sensación más suave, con más hundimiento en la superficie.</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr">
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>Nivel de confort suave: una sensación más suave, con más hundimiento en la superficie.</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr">
         <is>
           <t>Suavidad con soporte</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>Confort fresco con una bienvenida más suave.</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>La construcción Summit se expresa a través de una superficie mullida mientras conserva su soporte ensacado debajo.</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>Acomódate en el confort mullido, luego cambia de posición y siente cómo responde el soporte.</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Capas de confort frescas</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>Toca la funda fresca y luego acomódate en la espuma de confort transpirable debajo.</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>Soporte de resortes por zonas</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>Cambia de posición y siente cómo responde el sistema de resortes bajo la superficie.</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>Funda fresca sobre espuma de confort transpirable</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>Resortes ensacados por zonas</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3664,46 +5178,136 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
+          <t>A cushioned finish over purposeful support.</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>The euro-top softens first contact while center-third zoning maintains the mattress's firm identity.</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Feel the cushion first, then lie through the center for the firmer structure.</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Cushioned euro-top</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Feel the initial cushion at the surface.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Center-third support</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Lie through the center and find the firmer structure underneath.</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Euro-top</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Center-third zoning</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
           <t>Marvelous Middle|Firme|Euro Top</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr">
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr">
         <is>
           <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr">
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Soporte firme zonificado con acabado euro-top — firme sin sentirse desnudo.</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr">
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>Euro-top sobre resortes firmes</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
+      <c r="BA18" t="inlineStr">
         <is>
           <t>Una capa de cojín cosida por debajo suaviza la sensación de un firme verdadero.</t>
         </is>
       </c>
-      <c r="AS18" t="inlineStr">
+      <c r="BB18" t="inlineStr">
         <is>
           <t>Resortes centrales más gruesos</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>La zonificación distintiva de Restonic mantiene las caderas niveladas donde las camas fallan primero.</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>Un acabado acolchado sobre un soporte con propósito.</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>El euro-top suaviza el primer contacto mientras las zonas del tercio central mantienen la identidad firme del colchón.</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>Siente primero el acolchado y luego acuéstate por el centro para la estructura más firme.</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Euro-top acolchado</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>Siente el acolchado inicial en la superficie.</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>Soporte del tercio central</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>Acuéstate por el centro y encuentra la estructura más firme debajo.</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>Euro-top</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>Zonas del tercio central</t>
         </is>
       </c>
     </row>
@@ -3804,42 +5408,132 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
+          <t>Quiet comfort for two.</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Conforming foam and independently wrapped coils create a calm medium surface designed to limit transferred movement.</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Lie on your side, then ask your partner to move and notice what reaches you.</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Controlled contour</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Settle into the comfort layers without a deep foam sink.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Independently wrapped coils</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Let one person change position while the other remains still.</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Conforming foam</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Independently wrapped coils</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
           <t>Híbrido|Medio|Aislamiento de Movimiento</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>Medio de lujo que se adapta y permanece quieto toda la noche</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr">
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Capas de espuma adaptable sobre resortes envueltos — confort medio equilibrado que absorbe el movimiento de la pareja.</t>
         </is>
       </c>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr">
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>Aislamiento de movimiento con resortes envueltos</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr">
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr">
         <is>
           <t>Capas de confort adaptables</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>Las capas de espuma se contornean sin el hundimiento profundo de las camas viscoelásticas.</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>Confort tranquilo para dos.</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>La espuma adaptable y los resortes envueltos de forma independiente crean una superficie media y serena diseñada para limitar el movimiento transferido.</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>Acuéstate de lado, luego pide a tu pareja que se mueva y nota lo que llega hasta ti.</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Contorno controlado</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>Acomódate en las capas de confort sin un hundimiento profundo en la espuma.</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Resortes envueltos de forma independiente</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>Deja que una persona cambie de posición mientras la otra permanece quieta.</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>Espuma adaptable</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>Resortes envueltos de forma independiente</t>
         </is>
       </c>
     </row>
@@ -3940,42 +5634,132 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
+          <t>Structured support with a cooling surface.</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Cooling comfort materials sit above an extra-firm tight-top with reinforced center and perimeter support.</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Touch the cover, then lie on your back and feel the limited give.</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Cooling surface</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Touch the cover before lying down.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Reinforced structure</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Test the center and edge while noticing the limited surface give.</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Cooling comfort materials, tight-top</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Reinforced center and perimeter</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
           <t>Marvelous Middle|Extra Firme|Tight Top</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
         <is>
           <t>Soporte extra firme zonificado a un precio accesible</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr">
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>Tight top extra firme</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
+      <c r="BA20" t="inlineStr">
         <is>
           <t>Una superficie plana y de soporte sin suavidad — para quienes quieren algo sólido.</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
+      <c r="BB20" t="inlineStr">
         <is>
           <t>Soporte central zonificado</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>Resortes centrales más gruesos protegen la firmeza de las marcas corporales tempranas.</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>Soporte estructurado con superficie fresca.</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>Los materiales de confort frescos descansan sobre un tight-top extra firme con soporte reforzado en el centro y el perímetro.</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>Toca la funda, luego acuéstate boca arriba y siente la cesión limitada.</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>Superficie fresca</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>Toca la funda antes de acostarte.</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>Estructura reforzada</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>Prueba el centro y el borde mientras notas la cesión limitada de la superficie.</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>Materiales de confort frescos, tight-top</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>Centro y perímetro reforzados</t>
         </is>
       </c>
     </row>
@@ -4080,46 +5864,136 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
+          <t>A cool, generous welcome.</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>A cool-to-touch surface and plush memory foam create the first impression, with pocketed zoned coils underneath.</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Touch the cover, then lie on your side and let the shoulder settle.</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Cool plush surface</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Touch the cover, then let the shoulder and hip settle into the smooth comfort layer.</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Zoned pocketed support</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Change positions and feel the support beneath the plush surface.</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Cool-to-touch surface over plush memory foam</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Pocketed zoned coils</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
           <t>Suave|12.5 Pulgadas|Valor</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>Suavidad acogedora a un precio cotidiano</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr">
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Una construcción suave de 12.5 pulgadas que acolcha hombros y caderas — suavidad fácil a un precio razonable.</t>
         </is>
       </c>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr">
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>Superficie verdaderamente suave</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
+      <c r="BA21" t="inlineStr">
         <is>
           <t>Más suave que el Gracie — hecho para quienes buscan acolchado primero.</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
+      <c r="BB21" t="inlineStr">
         <is>
           <t>Valor cotidiano</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr">
+      <c r="BC21" t="inlineStr">
         <is>
           <t>Calidad Restonic sin el precio Platinum.</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>Una bienvenida fresca y generosa.</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>Una superficie fresca al tacto y espuma viscoelástica mullida crean la primera impresión, con resortes ensacados por zonas debajo.</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>Toca la funda, luego acuéstate de lado y deja que el hombro se asiente.</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>Superficie mullida y fresca</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>Toca la funda y luego deja que el hombro y la cadera se asienten en la suave capa de confort.</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Soporte ensacado por zonas</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>Cambia de posición y siente el soporte bajo la superficie mullida.</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>Superficie fresca al tacto sobre espuma viscoelástica mullida</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>Resortes ensacados por zonas</t>
         </is>
       </c>
     </row>
@@ -4232,54 +6106,144 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
+          <t>Clean firmness with thoughtful engineering.</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>A cooling surface and pocketed center-zoned coils elevate a straightforward firm mattress.</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Lie through the center and notice the restrained surface.</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Cooling first contact</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Touch the cover before lying down.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Center-zoned firm support</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Lie through the center and notice the restrained surface.</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Cooling surface</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Pocketed center-zoned coils</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
           <t>Firme|12.5 Pulgadas|Valor</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AO22" t="inlineStr">
         <is>
           <t>Soporte firme directo a un precio cotidiano</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr">
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr">
         <is>
           <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr">
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Un firme de 12.5 pulgadas sin rodeos que mantiene tu columna alineada — soporte confiable noche tras noche.</t>
         </is>
       </c>
-      <c r="AP22" t="inlineStr">
+      <c r="AY22" t="inlineStr">
         <is>
           <t>Alineación firme confiable a precio cotidiano.</t>
         </is>
       </c>
-      <c r="AQ22" t="inlineStr">
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>Sensación firme directa</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
+      <c r="BA22" t="inlineStr">
         <is>
           <t>Soporte sólido sin capas suaves que ablanden la superficie.</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
+      <c r="BB22" t="inlineStr">
         <is>
           <t>Valor cotidiano</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr">
+      <c r="BC22" t="inlineStr">
         <is>
           <t>El camino accesible a un colchón firme verdadero.</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>Firmeza limpia con ingeniería cuidada.</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>Una superficie fresca y resortes ensacados con zona central elevan un colchón firme y directo.</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>Acuéstate por el centro y nota la superficie contenida.</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>Primer contacto fresco</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>Toca la funda antes de acostarte.</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>Soporte firme con zona central</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>Acuéstate por el centro y nota la superficie contenida.</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>Superficie fresca</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>Resortes ensacados con zona central</t>
         </is>
       </c>
     </row>
@@ -4388,50 +6352,140 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
+          <t>Family-built American comfort.</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>A family company's hybrid foundation receives a relaxed euro-top finish.</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Roll once and feel the coils respond under the cushioned top.</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Cushioned euro-top</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Feel the additional comfort at first contact.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Responsive hybrid foundation</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Roll once and feel the coil response beneath the cushion.</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Euro-top</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Hybrid coil foundation</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
           <t>Híbrido|Euro Top|Hecho en EE. UU.</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AO23" t="inlineStr">
         <is>
           <t>Híbrido euro-top de empresa familiar, diseñado en EE. UU.</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr">
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Treinta años de experiencia familiar de Kingdom Mattress en un híbrido euro-top diseñado completamente en EE. UU.</t>
         </is>
       </c>
-      <c r="AP23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>Un híbrido euro-top de empresa familiar hecho para aguantar años de vida real.</t>
         </is>
       </c>
-      <c r="AQ23" t="inlineStr">
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>Capa de confort euro-top</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
+      <c r="BA23" t="inlineStr">
         <is>
           <t>Una superficie acolchada que el Genesis Firme no tiene.</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="BB23" t="inlineStr">
         <is>
           <t>Ingeniería para durar</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr">
+      <c r="BC23" t="inlineStr">
         <is>
           <t>Diseñado por una empresa familiar de 30 años con la durabilidad primero.</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>Confort americano de una empresa familiar.</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>La base híbrida de una empresa familiar recibe un acabado euro-top relajado.</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>Gira una vez y siente cómo responden los resortes bajo la capa acolchada.</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>Euro-top acolchado</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>Siente el confort adicional en el primer contacto.</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Base híbrida receptiva</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>Gira una vez y siente la respuesta de los resortes bajo el acolchado.</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>Euro-top</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>Base híbrida de resortes</t>
         </is>
       </c>
     </row>
@@ -4544,54 +6598,144 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
+          <t>American-engineered response without excess.</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>A direct firm hybrid focuses on immediate coil response and an uncomplicated surface.</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Press the top, then roll or rise and feel the immediate response.</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Direct firm surface</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Press the top and notice its limited give.</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Responsive hybrid support</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Roll or rise and feel the mattress respond immediately.</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Firm surface</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Hybrid coils</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
           <t>Híbrido|Firme|Hecho en EE. UU.</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
         <is>
           <t>Híbrido firme de empresa familiar al mejor valor</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr">
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr">
         <is>
           <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr">
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Un híbrido firme diseñado completamente en EE. UU. por una empresa familiar de 30 años — soporte sólido al mejor valor de la tienda.</t>
         </is>
       </c>
-      <c r="AP24" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>Soporte híbrido firme, de empresa familiar y a un precio razonable.</t>
         </is>
       </c>
-      <c r="AQ24" t="inlineStr">
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>Núcleo híbrido firme</t>
         </is>
       </c>
-      <c r="AR24" t="inlineStr">
+      <c r="BA24" t="inlineStr">
         <is>
           <t>Soporte de resortes con superficie firme — más receptivo que las camas de espuma de valor.</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr">
+      <c r="BB24" t="inlineStr">
         <is>
           <t>Firme del mejor valor</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr">
+      <c r="BC24" t="inlineStr">
         <is>
           <t>El híbrido firme verdadero más accesible de la línea.</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>Respuesta de ingeniería americana sin excesos.</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>Un híbrido firme y directo se centra en la respuesta inmediata de los resortes y una superficie sin complicaciones.</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>Presiona la parte superior, luego gira o levántate y siente la respuesta inmediata.</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>Superficie firme y directa</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>Presiona la parte superior y nota su cesión limitada.</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>Soporte híbrido receptivo</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>Gira o levántate y siente cómo el colchón responde de inmediato.</t>
+        </is>
+      </c>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>Superficie firme</t>
+        </is>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>Resortes híbridos</t>
         </is>
       </c>
     </row>
@@ -4684,34 +6828,124 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
+          <t>Side-sleeper softness with hidden structure.</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>A plush surface welcomes the shoulder and hip while a reinforced center and encased edge provide structure.</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Lie on your side and let the shoulder settle, then move toward the edge.</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Plush pressure-conscious surface</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Try a normal side-sleeping position and let the shoulder settle naturally.</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Center and edge support</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Move toward the perimeter and feel the supported edge.</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Plush surface</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Reinforced center with an encased edge</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
           <t>Marvelous Middle|Suave|Para Dormir de Lado</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Nivel de confort suave: una sensación más suave, con más hundimiento en la superficie.</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr">
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>Nivel de confort suave: una sensación más suave, con más hundimiento en la superficie.</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr">
         <is>
           <t>Encasado de borde de 3 pulgadas</t>
         </is>
       </c>
-      <c r="AT25" t="inlineStr">
+      <c r="BC25" t="inlineStr">
         <is>
           <t>Rieles de espuma de alta densidad dan más superficie útil que las camas suaves de valor.</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>Suavidad para dormir de lado con estructura oculta.</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>Una superficie mullida recibe el hombro y la cadera mientras un centro reforzado y un borde encapsulado aportan estructura.</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>Acuéstate de lado y deja que el hombro se asiente, luego muévete hacia el borde.</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>Superficie mullida y atenta a la presión</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>Prueba una posición normal de lado y deja que el hombro se asiente de forma natural.</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>Soporte en el centro y el borde</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>Muévete hacia el perímetro y siente el borde con soporte.</t>
+        </is>
+      </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>Superficie mullida</t>
+        </is>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>Centro reforzado con borde encapsulado</t>
         </is>
       </c>
     </row>
@@ -4820,50 +7054,140 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
+          <t>Compact, extra-firm control.</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>A restrained tight-top places reinforced center support and perimeter structure ahead of decorative cushioning.</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Press the top, then lie down and test the center and the edge.</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Extra-firm surface</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Press the top and notice its limited give.</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Reinforced center and edge</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Test the middle and perimeter of the mattress.</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Restrained tight-top</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Reinforced center and perimeter</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
           <t>Marvelous Middle|Extra Firme|Híbrido</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AO26" t="inlineStr">
         <is>
           <t>Soporte híbrido extra firme a precio de valor</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr">
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr">
         <is>
           <t>Nivel de confort extra firme: una sensación muy firme, con poco hundimiento en la superficie.</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr">
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
         <is>
           <t>El camino de valor al verdadero soporte extra firme zonificado.</t>
         </is>
       </c>
-      <c r="AQ26" t="inlineStr">
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>Extra firme de valor</t>
         </is>
       </c>
-      <c r="AR26" t="inlineStr">
+      <c r="BA26" t="inlineStr">
         <is>
           <t>La sensación más firme del nivel bronce — sin nada de suavidad.</t>
         </is>
       </c>
-      <c r="AS26" t="inlineStr">
+      <c r="BB26" t="inlineStr">
         <is>
           <t>Núcleo híbrido zonificado</t>
         </is>
       </c>
-      <c r="AT26" t="inlineStr">
+      <c r="BC26" t="inlineStr">
         <is>
           <t>Refuerzo del tercio central que la mayoría de las camas firmes de valor omiten.</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>Control compacto y extra firme.</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>Un tight-top contenido pone el soporte central reforzado y la estructura del perímetro por delante del acolchado decorativo.</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>Presiona la parte superior, luego acuéstate y prueba el centro y el borde.</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>Superficie extra firme</t>
+        </is>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>Presiona la parte superior y nota su cesión limitada.</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>Centro y borde reforzados</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>Prueba el centro y el perímetro del colchón.</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>Tight-top contenido</t>
+        </is>
+      </c>
+      <c r="BL26" t="inlineStr">
+        <is>
+          <t>Centro y perímetro reforzados</t>
         </is>
       </c>
     </row>
@@ -4976,54 +7300,144 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
+          <t>Classic innerspring character, thoughtfully reinforced.</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Traditional coil response is paired with a stronger center, supportive perimeter and cooling cover.</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Roll once and feel the familiar spring response, then sit near the edge.</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Classic responsive feel</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Roll once and feel the familiar spring response.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Reinforced sleep surface</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Test the center and then sit near the supported edge.</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Cooling cover</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Innerspring coils with a reinforced center and perimeter</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
           <t>Resortes|Medio|Mejor Valor</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>Confort medio equilibrado al precio más amigable</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr">
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr">
         <is>
           <t>Nivel de confort medio: una sensación equilibrada entre suave y firme.</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr">
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Un colchón de resortes medio equilibrado con los resortes centrales más gruesos de Restonic — calidad real al precio más amigable de la tienda.</t>
         </is>
       </c>
-      <c r="AP27" t="inlineStr">
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Confort equilibrado fácil con soporte zonificado — la elección inteligente para empezar.</t>
         </is>
       </c>
-      <c r="AQ27" t="inlineStr">
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>Sensación de resortes receptiva</t>
         </is>
       </c>
-      <c r="AR27" t="inlineStr">
+      <c r="BA27" t="inlineStr">
         <is>
           <t>Rebote clásico de resortes fácil para moverse — sin sensación de quedar atrapado en espuma.</t>
         </is>
       </c>
-      <c r="AS27" t="inlineStr">
+      <c r="BB27" t="inlineStr">
         <is>
           <t>El precio más amigable</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
+      <c r="BC27" t="inlineStr">
         <is>
           <t>La forma más accesible de entrar a una construcción Restonic zonificada.</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>Carácter clásico de resortes, reforzado con cuidado.</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>La respuesta tradicional de los resortes se combina con un centro más fuerte, un perímetro con soporte y una funda fresca.</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>Gira una vez y siente la respuesta familiar de los resortes, luego siéntate cerca del borde.</t>
+        </is>
+      </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>Sensación clásica y receptiva</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>Gira una vez y siente la respuesta familiar de los resortes.</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>Superficie de descanso reforzada</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>Prueba el centro y luego siéntate cerca del borde con soporte.</t>
+        </is>
+      </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>Funda fresca</t>
+        </is>
+      </c>
+      <c r="BL27" t="inlineStr">
+        <is>
+          <t>Resortes tradicionales con centro y perímetro reforzados</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -9508,7 +9508,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"quiz":{"questions":[{"id":"trigger","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What can we help you with today?","es":"¿En qué te podemos ayudar hoy?"},"helpText":{"en":"This doesn't change your sleep-fit ranking. It helps your specialist focus on what matters to you.","es":"Esto no cambia el orden de tus opciones. Ayuda a tu especialista a enfocarse en lo que te importa."},"type":"single","options":[{"id":"pain","label":{"en":"Back or Body Pain","es":"Dolor de Espalda o Cuerpo"},"icon":"spine","sublabel":{"en":"Current mattress is hurting me","es":"Mi colchón actual me lastima"},"scores":{}},{"id":"worn_out","label":{"en":"Old Mattress","es":"Colchón Viejo"},"icon":"sagging","sublabel":{"en":"Time for an upgrade","es":"Es hora de un cambio"},"scores":{}},{"id":"moving","label":{"en":"Moving or New Space","es":"Mudanza o Espacio Nuevo"},"icon":"family","sublabel":{"en":"New home, new bed","es":"Casa nueva, cama nueva"},"scores":{}},{"id":"upgrade","label":{"en":"Just Upgrading","es":"Mejorando"},"icon":"cloud","sublabel":{"en":"Ready for something better","es":"Listo para algo mejor"},"scores":{}},{"id":"browsing","label":{"en":"Just Browsing","es":"Solo Explorando"},"icon":"smile","sublabel":{"en":"Getting ideas, no rush","es":"Sin prisa, juntando ideas"},"scores":{}}]},{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"We carry your selected size into the consultation. Your sleep-fit ranking is based on your comfort and support answers.","es":"Tomamos en cuenta el tamaño que elijas en la consulta. El orden de tus opciones se basa en tus respuestas sobre comodidad y soporte."},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"This shapes the questions that follow and what we suggest testing together.","es":"Esto define las preguntas que siguen y lo que sugerimos probar juntos."},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"The more movement wakes you, the more it shapes your matches and what we suggest testing.","es":"Cuanto más te despierte el movimiento, más influye en tus opciones y en lo que sugerimos probar."},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"This helps us favor pressure relief, support, or a responsive feel.","es":"Esto nos ayuda a priorizar alivio de presión, soporte o una sensación con más respuesta."},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"If you sleep hot, we favor cooling features in your matches.","es":"Si duermes con calor, priorizamos materiales refrescantes en tus opciones."},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to the feel you prefer.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. These shape which features we favor and what we suggest testing.","es":"Toca lo que hayas notado. Esto define qué características priorizamos y qué sugerimos probar."},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durable":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. Some shape your matches; some change what we suggest trying, like an adjustable base or a mattress protector.","es":"Toca lo que aplique. Algunas influyen en tus opciones; otras cambian lo que sugerimos probar, como una base ajustable o un protector de colchón."},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durable":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
+          <t>{"quiz":{"questions":[{"id":"trigger","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What can we help you with today?","es":"¿En qué te podemos ayudar hoy?"},"helpText":{"en":"This doesn't change your sleep-fit ranking. It helps your specialist focus on what matters to you.","es":"Esto no cambia el orden de tus opciones. Ayuda a tu especialista a enfocarse en lo que te importa."},"type":"single","options":[{"id":"pain","label":{"en":"Back or Body Pain","es":"Dolor de Espalda o Cuerpo"},"icon":"spine","sublabel":{"en":"Current mattress is hurting me","es":"Mi colchón actual me lastima"},"scores":{}},{"id":"worn_out","label":{"en":"Old Mattress","es":"Colchón Viejo"},"icon":"sagging","sublabel":{"en":"Time for an upgrade","es":"Es hora de un cambio"},"scores":{}},{"id":"moving","label":{"en":"Moving or New Space","es":"Mudanza o Espacio Nuevo"},"icon":"family","sublabel":{"en":"New home, new bed","es":"Casa nueva, cama nueva"},"scores":{}},{"id":"upgrade","label":{"en":"Just Upgrading","es":"Mejorando"},"icon":"cloud","sublabel":{"en":"Ready for something better","es":"Listo para algo mejor"},"scores":{}},{"id":"browsing","label":{"en":"Just Browsing","es":"Solo Explorando"},"icon":"smile","sublabel":{"en":"Getting ideas, no rush","es":"Sin prisa, juntando ideas"},"scores":{}}]},{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"We carry your selected size into the consultation. Your sleep-fit ranking is based on your comfort and support answers.","es":"Tomamos en cuenta el tamaño que elijas en la consulta. El orden de tus opciones se basa en tus respuestas sobre comodidad y soporte."},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"This shapes the questions that follow and what we suggest testing together.","es":"Esto define las preguntas que siguen y lo que sugerimos probar juntos."},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"The more movement wakes you, the more it shapes your matches and what we suggest testing.","es":"Cuanto más te despierte el movimiento, más influye en tus opciones y en lo que sugerimos probar."},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"This helps us favor pressure relief, support, or a responsive feel.","es":"Esto nos ayuda a priorizar alivio de presión, soporte o una sensación con más respuesta."},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"If you sleep hot, we favor cooling features in your matches.","es":"Si duermes con calor, priorizamos materiales refrescantes en tus opciones."},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to the feel you prefer.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. These shape which features we favor and what we suggest testing.","es":"Toca lo que hayas notado. Esto define qué características priorizamos y qué sugerimos probar."},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durability":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. Some shape your matches; some change what we suggest trying, like an adjustable base or a mattress protector.","es":"Toca lo que aplique. Algunas influyen en tus opciones; otras cambian lo que sugerimos probar, como una base ajustable o un protector de colchón."},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durability":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -8278,7 +8278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>trigger.pain</t>
+          <t>sleep_issues.back_pain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -8542,7 +8542,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>here to solve a comfort problem</t>
+          <t>test lower-back support carefully</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -8552,7 +8552,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>aquí para resolver un problema de comodidad</t>
+          <t>probar con cuidado el soporte lumbar</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>trigger.worn_out</t>
+          <t>sleep_issues.hip_pain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -8575,7 +8575,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>replacing an old mattress</t>
+          <t>focus on pressure relief at hips and shoulders</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -8585,7 +8585,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>reemplazando un colchón viejo</t>
+          <t>enfocarse en aliviar la presión en caderas y hombros</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>trigger.moving</t>
+          <t>sleep_issues.hot</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -8608,7 +8608,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>furnishing a new space</t>
+          <t>prioritize temperature control</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -8618,7 +8618,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>amueblando un espacio nuevo</t>
+          <t>priorizar el control de temperatura</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>trigger.upgrade</t>
+          <t>sleep_issues.tossing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -8641,7 +8641,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ready for an upgrade</t>
+          <t>notice how easy it is to settle in</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -8651,7 +8651,7 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>buscando una mejora</t>
+          <t>notar qué tan fácil es acomodarse</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>trigger.browsing</t>
+          <t>sleep_issues.stiff</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -8674,7 +8674,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>exploring options today</t>
+          <t>compare alignment and morning comfort</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -8684,7 +8684,7 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>explorando opciones hoy</t>
+          <t>comparar la alineación y la comodidad al despertar</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sleep_issues.back_pain</t>
+          <t>sleep_issues.sagging</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -8707,7 +8707,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>test lower-back support carefully</t>
+          <t>check for durable, consistent support</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -8717,7 +8717,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>probar con cuidado el soporte lumbar</t>
+          <t>revisar que el soporte sea duradero y consistente</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sleep_issues.hip_pain</t>
+          <t>sleep_issues.too_soft</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -8740,7 +8740,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>focus on pressure relief at hips and shoulders</t>
+          <t>try firmer, more supportive feels</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -8750,7 +8750,7 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>enfocarse en aliviar la presión en caderas y hombros</t>
+          <t>probar sensaciones más firmes y con más soporte</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sleep_issues.hot</t>
+          <t>sleep_issues.none</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -8771,21 +8771,13 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>prioritize temperature control</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>priorizar el control de temperatura</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8795,7 +8787,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sleep_issues.tossing</t>
+          <t>sleep_position.side</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -8806,7 +8798,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>notice how easy it is to settle in</t>
+          <t>prioritize shoulder and hip cushioning</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -8816,7 +8808,7 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>notar qué tan fácil es acomodarse</t>
+          <t>priorizar el acolchado de hombros y caderas</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8820,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sleep_issues.stiff</t>
+          <t>sleep_position.back</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -8839,7 +8831,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>compare alignment and morning comfort</t>
+          <t>look for even lumbar support</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -8849,7 +8841,7 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>comparar la alineación y la comodidad al despertar</t>
+          <t>buscar soporte lumbar uniforme</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8853,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sleep_issues.sagging</t>
+          <t>sleep_position.stomach</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -8872,7 +8864,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>check for durable, consistent support</t>
+          <t>keep the midsection supported</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -8882,7 +8874,7 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>revisar que el soporte sea duradero y consistente</t>
+          <t>mantener la zona media con soporte</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8886,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sleep_issues.too_soft</t>
+          <t>sleep_position.combo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -8905,7 +8897,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>try firmer, more supportive feels</t>
+          <t>notice ease of movement between positions</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -8915,7 +8907,7 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>probar sensaciones más firmes y con más soporte</t>
+          <t>notar la facilidad para cambiar de posición</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8919,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sleep_issues.none</t>
+          <t>sleep_position.no_idea</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -8936,13 +8928,21 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>compare a few different feels to find a starting point</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>comparar varias sensaciones para encontrar un punto de partida</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sleep_position.side</t>
+          <t>health_conditions.nerve_pain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -8963,7 +8963,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>prioritize shoulder and hip cushioning</t>
+          <t>compare gentle, even pressure relief</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -8973,7 +8973,7 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>priorizar el acolchado de hombros y caderas</t>
+          <t>comparar un alivio de presión suave y uniforme</t>
         </is>
       </c>
     </row>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sleep_position.back</t>
+          <t>health_conditions.allergies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -8996,7 +8996,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>look for even lumbar support</t>
+          <t>ask about washable and protective covers</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -9006,7 +9006,7 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>buscar soporte lumbar uniforme</t>
+          <t>preguntar por fundas lavables y protectoras</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sleep_position.stomach</t>
+          <t>health_conditions.snoring</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -9029,7 +9029,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>keep the midsection supported</t>
+          <t>test head-of-bed elevation on an adjustable base</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -9039,7 +9039,7 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>mantener la zona media con soporte</t>
+          <t>probar la elevación de la cabecera en una base ajustable</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9051,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sleep_position.combo</t>
+          <t>health_conditions.reflux</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>notice ease of movement between positions</t>
+          <t>notice how a raised upper body feels</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -9072,7 +9072,7 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>notar la facilidad para cambiar de posición</t>
+          <t>notar cómo se siente el torso elevado</t>
         </is>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sleep_position.no_idea</t>
+          <t>health_conditions.extra_support</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -9095,7 +9095,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>compare a few different feels to find a starting point</t>
+          <t>prioritize reinforced, sturdy support</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -9105,7 +9105,7 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>comparar varias sensaciones para encontrar un punto de partida</t>
+          <t>priorizar un soporte reforzado y resistente</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>health_conditions.nerve_pain</t>
+          <t>health_conditions.getting_older</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -9128,7 +9128,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>compare gentle, even pressure relief</t>
+          <t>compare ease of getting in and out of bed</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -9138,7 +9138,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>comparar un alivio de presión suave y uniforme</t>
+          <t>comparar la facilidad para acostarse y levantarse</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>health_conditions.allergies</t>
+          <t>health_conditions.none</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -9159,21 +9159,13 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>ask about washable and protective covers</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>preguntar por fundas lavables y protectoras</t>
-        </is>
-      </c>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9183,7 +9175,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>health_conditions.snoring</t>
+          <t>temperature.hot</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -9194,7 +9186,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>test head-of-bed elevation on an adjustable base</t>
+          <t>compare cooling covers and airflow</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -9204,7 +9196,7 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>probar la elevación de la cabecera en una base ajustable</t>
+          <t>comparar fundas frescas y ventilación</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9208,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>health_conditions.reflux</t>
+          <t>temperature.comfortable</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -9225,21 +9217,13 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>notice how a raised upper body feels</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>notar cómo se siente el torso elevado</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9249,7 +9233,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>health_conditions.extra_support</t>
+          <t>temperature.cold</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -9260,7 +9244,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>prioritize reinforced, sturdy support</t>
+          <t>notice warmth and cozier surface feels</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -9270,7 +9254,7 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>priorizar un soporte reforzado y resistente</t>
+          <t>notar calidez y superficies más acogedoras</t>
         </is>
       </c>
     </row>
@@ -9282,7 +9266,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>health_conditions.getting_older</t>
+          <t>temperature.opposite</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -9293,7 +9277,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>compare ease of getting in and out of bed</t>
+          <t>compare temperature balance for two sleepers</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -9302,155 +9286,6 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
-        <is>
-          <t>comparar la facilidad para acostarse y levantarse</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>health_conditions.none</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>temperature.hot</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>compare cooling covers and airflow</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>comparar fundas frescas y ventilación</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>temperature.comfortable</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>temperature.cold</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>notice warmth and cozier surface feels</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>notar calidez y superficies más acogedoras</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>temperature.opposite</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>compare temperature balance for two sleepers</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
         <is>
           <t>comparar el equilibrio de temperatura para dos personas</t>
         </is>
@@ -9508,7 +9343,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"quiz":{"questions":[{"id":"trigger","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What can we help you with today?","es":"¿En qué te podemos ayudar hoy?"},"helpText":{"en":"This doesn't change your sleep-fit ranking. It helps your specialist focus on what matters to you.","es":"Esto no cambia el orden de tus opciones. Ayuda a tu especialista a enfocarse en lo que te importa."},"type":"single","options":[{"id":"pain","label":{"en":"Back or Body Pain","es":"Dolor de Espalda o Cuerpo"},"icon":"spine","sublabel":{"en":"Current mattress is hurting me","es":"Mi colchón actual me lastima"},"scores":{}},{"id":"worn_out","label":{"en":"Old Mattress","es":"Colchón Viejo"},"icon":"sagging","sublabel":{"en":"Time for an upgrade","es":"Es hora de un cambio"},"scores":{}},{"id":"moving","label":{"en":"Moving or New Space","es":"Mudanza o Espacio Nuevo"},"icon":"family","sublabel":{"en":"New home, new bed","es":"Casa nueva, cama nueva"},"scores":{}},{"id":"upgrade","label":{"en":"Just Upgrading","es":"Mejorando"},"icon":"cloud","sublabel":{"en":"Ready for something better","es":"Listo para algo mejor"},"scores":{}},{"id":"browsing","label":{"en":"Just Browsing","es":"Solo Explorando"},"icon":"smile","sublabel":{"en":"Getting ideas, no rush","es":"Sin prisa, juntando ideas"},"scores":{}}]},{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"We carry your selected size into the consultation. Your sleep-fit ranking is based on your comfort and support answers.","es":"Tomamos en cuenta el tamaño que elijas en la consulta. El orden de tus opciones se basa en tus respuestas sobre comodidad y soporte."},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"This shapes the questions that follow and what we suggest testing together.","es":"Esto define las preguntas que siguen y lo que sugerimos probar juntos."},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"The more movement wakes you, the more it shapes your matches and what we suggest testing.","es":"Cuanto más te despierte el movimiento, más influye en tus opciones y en lo que sugerimos probar."},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"This helps us favor pressure relief, support, or a responsive feel.","es":"Esto nos ayuda a priorizar alivio de presión, soporte o una sensación con más respuesta."},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"If you sleep hot, we favor cooling features in your matches.","es":"Si duermes con calor, priorizamos materiales refrescantes en tus opciones."},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to the feel you prefer.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. These shape which features we favor and what we suggest testing.","es":"Toca lo que hayas notado. Esto define qué características priorizamos y qué sugerimos probar."},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durability":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. Some shape your matches; some change what we suggest trying, like an adjustable base or a mattress protector.","es":"Toca lo que aplique. Algunas influyen en tus opciones; otras cambian lo que sugerimos probar, como una base ajustable o un protector de colchón."},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durability":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
+          <t>{"quiz":{"questions":[{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"We carry your selected size into the consultation. Your sleep-fit ranking is based on your comfort and support answers.","es":"Tomamos en cuenta el tamaño que elijas en la consulta. El orden de tus opciones se basa en tus respuestas sobre comodidad y soporte."},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"This shapes the questions that follow and what we suggest testing together.","es":"Esto define las preguntas que siguen y lo que sugerimos probar juntos."},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"The more movement wakes you, the more it shapes your matches and what we suggest testing.","es":"Cuanto más te despierte el movimiento, más influye en tus opciones y en lo que sugerimos probar."},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"This helps us favor pressure relief, support, or a responsive feel.","es":"Esto nos ayuda a priorizar alivio de presión, soporte o una sensación con más respuesta."},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"If you sleep hot, we favor cooling features in your matches.","es":"Si duermes con calor, priorizamos materiales refrescantes en tus opciones."},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to the feel you prefer.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. These shape which features we favor and what we suggest testing.","es":"Toca lo que hayas notado. Esto define qué características priorizamos y qué sugerimos probar."},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durability":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. Some shape your matches; some change what we suggest trying, like an adjustable base or a mattress protector.","es":"Toca lo que aplique. Algunas influyen en tus opciones; otras cambian lo que sugerimos probar, como una base ajustable o un protector de colchón."},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durability":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -5864,7 +5864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>trigger.pain</t>
+          <t>sleep_issues.back_pain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -6128,7 +6128,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>here to solve a comfort problem</t>
+          <t>test lower-back support carefully</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -6138,7 +6138,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>aquí para resolver un problema de comodidad</t>
+          <t>probar con cuidado el soporte lumbar</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>trigger.worn_out</t>
+          <t>sleep_issues.hip_pain</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -6161,7 +6161,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>replacing an old mattress</t>
+          <t>focus on pressure relief at hips and shoulders</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -6171,7 +6171,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>reemplazando un colchón viejo</t>
+          <t>enfocarse en aliviar la presión en caderas y hombros</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>trigger.moving</t>
+          <t>sleep_issues.hot</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -6194,7 +6194,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>furnishing a new space</t>
+          <t>prioritize temperature control</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -6204,7 +6204,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>amueblando un espacio nuevo</t>
+          <t>priorizar el control de temperatura</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>trigger.upgrade</t>
+          <t>sleep_issues.tossing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -6227,7 +6227,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ready for an upgrade</t>
+          <t>notice how easy it is to settle in</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -6237,7 +6237,7 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>buscando una mejora</t>
+          <t>notar qué tan fácil es acomodarse</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>trigger.browsing</t>
+          <t>sleep_issues.stiff</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -6260,7 +6260,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>exploring options today</t>
+          <t>compare alignment and morning comfort</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -6270,7 +6270,7 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>explorando opciones hoy</t>
+          <t>comparar la alineación y la comodidad al despertar</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sleep_issues.back_pain</t>
+          <t>sleep_issues.sagging</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -6293,7 +6293,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>test lower-back support carefully</t>
+          <t>check for durable, consistent support</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -6303,7 +6303,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>probar con cuidado el soporte lumbar</t>
+          <t>revisar que el soporte sea duradero y consistente</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sleep_issues.hip_pain</t>
+          <t>sleep_issues.too_soft</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>focus on pressure relief at hips and shoulders</t>
+          <t>try firmer, more supportive feels</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -6336,7 +6336,7 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>enfocarse en aliviar la presión en caderas y hombros</t>
+          <t>probar sensaciones más firmes y con más soporte</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sleep_issues.hot</t>
+          <t>sleep_issues.none</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -6357,21 +6357,13 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>prioritize temperature control</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>priorizar el control de temperatura</t>
-        </is>
-      </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6381,7 +6373,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sleep_issues.tossing</t>
+          <t>sleep_position.side</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -6392,7 +6384,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>notice how easy it is to settle in</t>
+          <t>prioritize shoulder and hip cushioning</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -6402,7 +6394,7 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>notar qué tan fácil es acomodarse</t>
+          <t>priorizar el acolchado de hombros y caderas</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6406,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sleep_issues.stiff</t>
+          <t>sleep_position.back</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -6425,7 +6417,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>compare alignment and morning comfort</t>
+          <t>look for even lumbar support</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -6435,7 +6427,7 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>comparar la alineación y la comodidad al despertar</t>
+          <t>buscar soporte lumbar uniforme</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6439,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sleep_issues.sagging</t>
+          <t>sleep_position.stomach</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -6458,7 +6450,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>check for durable, consistent support</t>
+          <t>keep the midsection supported</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -6468,7 +6460,7 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>revisar que el soporte sea duradero y consistente</t>
+          <t>mantener la zona media con soporte</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6472,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sleep_issues.too_soft</t>
+          <t>sleep_position.combo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -6491,7 +6483,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>try firmer, more supportive feels</t>
+          <t>notice ease of movement between positions</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -6501,7 +6493,7 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>probar sensaciones más firmes y con más soporte</t>
+          <t>notar la facilidad para cambiar de posición</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6505,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sleep_issues.none</t>
+          <t>sleep_position.no_idea</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -6522,13 +6514,21 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>compare a few different feels to find a starting point</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>comparar varias sensaciones para encontrar un punto de partida</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sleep_position.side</t>
+          <t>health_conditions.nerve_pain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -6549,7 +6549,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>prioritize shoulder and hip cushioning</t>
+          <t>compare gentle, even pressure relief</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -6559,7 +6559,7 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>priorizar el acolchado de hombros y caderas</t>
+          <t>comparar un alivio de presión suave y uniforme</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sleep_position.back</t>
+          <t>health_conditions.allergies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -6582,7 +6582,7 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>look for even lumbar support</t>
+          <t>ask about washable and protective covers</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -6592,7 +6592,7 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>buscar soporte lumbar uniforme</t>
+          <t>preguntar por fundas lavables y protectoras</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sleep_position.stomach</t>
+          <t>health_conditions.snoring</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -6615,7 +6615,7 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>keep the midsection supported</t>
+          <t>test head-of-bed elevation on an adjustable base</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -6625,7 +6625,7 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>mantener la zona media con soporte</t>
+          <t>probar la elevación de la cabecera en una base ajustable</t>
         </is>
       </c>
     </row>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sleep_position.combo</t>
+          <t>health_conditions.reflux</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -6648,7 +6648,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>notice ease of movement between positions</t>
+          <t>notice how a raised upper body feels</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -6658,7 +6658,7 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>notar la facilidad para cambiar de posición</t>
+          <t>notar cómo se siente el torso elevado</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sleep_position.no_idea</t>
+          <t>health_conditions.extra_support</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -6681,7 +6681,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>compare a few different feels to find a starting point</t>
+          <t>prioritize reinforced, sturdy support</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -6691,7 +6691,7 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>comparar varias sensaciones para encontrar un punto de partida</t>
+          <t>priorizar un soporte reforzado y resistente</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>health_conditions.nerve_pain</t>
+          <t>health_conditions.getting_older</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -6714,7 +6714,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>compare gentle, even pressure relief</t>
+          <t>compare ease of getting in and out of bed</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>comparar un alivio de presión suave y uniforme</t>
+          <t>comparar la facilidad para acostarse y levantarse</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>health_conditions.allergies</t>
+          <t>health_conditions.none</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -6745,21 +6745,13 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>ask about washable and protective covers</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>preguntar por fundas lavables y protectoras</t>
-        </is>
-      </c>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6769,7 +6761,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>health_conditions.snoring</t>
+          <t>temperature.hot</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -6780,7 +6772,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>test head-of-bed elevation on an adjustable base</t>
+          <t>compare cooling covers and airflow</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -6790,7 +6782,7 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>probar la elevación de la cabecera en una base ajustable</t>
+          <t>comparar fundas frescas y ventilación</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6794,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>health_conditions.reflux</t>
+          <t>temperature.comfortable</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -6811,21 +6803,13 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>notice how a raised upper body feels</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>notar cómo se siente el torso elevado</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6835,7 +6819,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>health_conditions.extra_support</t>
+          <t>temperature.cold</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -6846,7 +6830,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>prioritize reinforced, sturdy support</t>
+          <t>notice warmth and cozier surface feels</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -6856,7 +6840,7 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>priorizar un soporte reforzado y resistente</t>
+          <t>notar calidez y superficies más acogedoras</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6852,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>health_conditions.getting_older</t>
+          <t>temperature.opposite</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -6879,7 +6863,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>compare ease of getting in and out of bed</t>
+          <t>compare temperature balance for two sleepers</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -6888,155 +6872,6 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
-        <is>
-          <t>comparar la facilidad para acostarse y levantarse</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>health_conditions.none</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>temperature.hot</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>compare cooling covers and airflow</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>comparar fundas frescas y ventilación</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>temperature.comfortable</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>temperature.cold</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>notice warmth and cozier surface feels</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>notar calidez y superficies más acogedoras</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>consultation</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>temperature.opposite</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>compare temperature balance for two sleepers</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
         <is>
           <t>comparar el equilibrio de temperatura para dos personas</t>
         </is>
@@ -7094,7 +6929,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"quiz":{"questions":[{"id":"trigger","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What can we help you with today?","es":"¿En qué te podemos ayudar hoy?"},"helpText":{"en":"This doesn't change your sleep-fit ranking. It helps your specialist focus on what matters to you.","es":"Esto no cambia el orden de tus opciones. Ayuda a tu especialista a enfocarse en lo que te importa."},"type":"single","options":[{"id":"pain","label":{"en":"Back or Body Pain","es":"Dolor de Espalda o Cuerpo"},"icon":"spine","sublabel":{"en":"Current mattress is hurting me","es":"Mi colchón actual me lastima"},"scores":{}},{"id":"worn_out","label":{"en":"Old Mattress","es":"Colchón Viejo"},"icon":"sagging","sublabel":{"en":"Time for an upgrade","es":"Es hora de un cambio"},"scores":{}},{"id":"moving","label":{"en":"Moving or New Space","es":"Mudanza o Espacio Nuevo"},"icon":"family","sublabel":{"en":"New home, new bed","es":"Casa nueva, cama nueva"},"scores":{}},{"id":"upgrade","label":{"en":"Just Upgrading","es":"Mejorando"},"icon":"cloud","sublabel":{"en":"Ready for something better","es":"Listo para algo mejor"},"scores":{}},{"id":"browsing","label":{"en":"Just Browsing","es":"Solo Explorando"},"icon":"smile","sublabel":{"en":"Getting ideas, no rush","es":"Sin prisa, juntando ideas"},"scores":{}}]},{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"We carry your selected size into the consultation. Your sleep-fit ranking is based on your comfort and support answers.","es":"Tomamos en cuenta el tamaño que elijas en la consulta. El orden de tus opciones se basa en tus respuestas sobre comodidad y soporte."},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"This shapes the questions that follow and what we suggest testing together.","es":"Esto define las preguntas que siguen y lo que sugerimos probar juntos."},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"The more movement wakes you, the more it shapes your matches and what we suggest testing.","es":"Cuanto más te despierte el movimiento, más influye en tus opciones y en lo que sugerimos probar."},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"This helps us favor pressure relief, support, or a responsive feel.","es":"Esto nos ayuda a priorizar alivio de presión, soporte o una sensación con más respuesta."},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"If you sleep hot, we favor cooling features in your matches.","es":"Si duermes con calor, priorizamos materiales refrescantes en tus opciones."},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to the feel you prefer.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. These shape which features we favor and what we suggest testing.","es":"Toca lo que hayas notado. Esto define qué características priorizamos y qué sugerimos probar."},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durable":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. Some shape your matches; some change what we suggest trying, like an adjustable base or a mattress protector.","es":"Toca lo que aplique. Algunas influyen en tus opciones; otras cambian lo que sugerimos probar, como una base ajustable o un protector de colchón."},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durable":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
+          <t>{"quiz":{"questions":[{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"We carry your selected size into the consultation. Your sleep-fit ranking is based on your comfort and support answers.","es":"Tomamos en cuenta el tamaño que elijas en la consulta. El orden de tus opciones se basa en tus respuestas sobre comodidad y soporte."},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"This shapes the questions that follow and what we suggest testing together.","es":"Esto define las preguntas que siguen y lo que sugerimos probar juntos."},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"The more movement wakes you, the more it shapes your matches and what we suggest testing.","es":"Cuanto más te despierte el movimiento, más influye en tus opciones y en lo que sugerimos probar."},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"This helps us favor pressure relief, support, or a responsive feel.","es":"Esto nos ayuda a priorizar alivio de presión, soporte o una sensación con más respuesta."},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"If you sleep hot, we favor cooling features in your matches.","es":"Si duermes con calor, priorizamos materiales refrescantes en tus opciones."},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to the feel you prefer.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. These shape which features we favor and what we suggest testing.","es":"Toca lo que hayas notado. Esto define qué características priorizamos y qué sugerimos probar."},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durable":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. Some shape your matches; some change what we suggest trying, like an adjustable base or a mattress protector.","es":"Toca lo que aplique. Algunas influyen en tus opciones; otras cambian lo que sugerimos probar, como una base ajustable o un protector de colchón."},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durable":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
         </is>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -1348,7 +1348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT27"/>
+  <dimension ref="A1:AU27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,155 +1429,160 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>skus</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>features</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>reason_cooling</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>reason_pressureRelief</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>reason_motionIsolation</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>reason_support</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>reason_plush</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>reason_medium</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>reason_firm</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>reason_durability</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>reason_default</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>topPickReason</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>differentiator1Title</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>differentiator1Detail</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>differentiator2Title</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>differentiator2Detail</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>displayBadges (ES)</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>highlight (ES)</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>reason_cooling (ES)</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>reason_pressureRelief (ES)</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>reason_motionIsolation (ES)</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>reason_support (ES)</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>reason_plush (ES)</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>reason_medium (ES)</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>reason_firm (ES)</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>reason_durability (ES)</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>reason_default (ES)</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>topPickReason (ES)</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>differentiator1Title (ES)</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>differentiator1Detail (ES)</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>differentiator2Title (ES)</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>differentiator2Detail (ES)</t>
         </is>
@@ -1643,12 +1648,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>support|firm|durability|hybrid|responsive|zoned</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
@@ -1656,47 +1661,47 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Merino wool, cashmere, and graphite latex over multiple coil layers — firm support that breathes and lasts.</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Handcrafted natural-fiber luxury with firm, breathable coil-on-coil support.</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Natural fiber comfort layers</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Merino wool, camel hair, and cashmere breathe and temper heat in a way synthetic foams can't.</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>Coil-on-coil with graphite latex</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Responsive lift and stability instead of the slow sink of memory foam.</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Fibras Naturales de Lujo|Firme|Euro-Top</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Lujo firme artesanal en lana Merino y cachemira</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
@@ -1704,32 +1709,33 @@
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>Lana Merino, cachemira y látex de grafito sobre múltiples capas de resortes — soporte firme que respira y dura.</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>Lujo artesanal de fibras naturales con soporte firme de doble resorte que respira.</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>Capas de confort de fibras naturales</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>La lana Merino, el pelo de camello y la cachemira respiran y regulan el calor como las espumas sintéticas no pueden.</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AT2" t="inlineStr">
         <is>
           <t>Doble resorte con látex de grafito</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>Elevación receptiva y estabilidad en lugar del hundimiento lento de la espuma viscoelástica.</t>
         </is>
@@ -1791,12 +1797,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>plush|soft|pressureRelief|durability|hybrid</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
@@ -1804,34 +1810,34 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>A deep plush euro-top of wool and cashmere over layered coils — indulgent softness that never loses its support.</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr">
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Deep plush euro-top</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>Breathable natural fill</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>Wool and cashmere keep the plush layers cooler than dense foam pillow-tops.</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>Fibras Naturales de Lujo|Suave|Euro-Top</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
@@ -1840,24 +1846,25 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>Un euro-top suave y profundo de lana y cachemira sobre capas de resortes — suavidad indulgente que nunca pierde su soporte.</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr">
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr">
         <is>
           <t>Euro-top suave y profundo</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr">
         <is>
           <t>Relleno natural transpirable</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>La lana y la cachemira mantienen las capas suaves más frescas que los pillow-tops de espuma densa.</t>
         </is>
@@ -1923,12 +1930,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>support|firm|durability|zoned|hybrid</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
@@ -1936,43 +1943,43 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>4,294 coils, Merino wool, and a hand-tufted build — firm alignment engineered to hold for decades.</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Massive 4,294-coil count with hand-tufted craftsmanship for firm, lasting alignment.</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>4,294-coil support system</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Several times the coil count of a standard bed — finer, more contoured firm support.</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Hand-tufted construction</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>4,294 Resortes|Firme|Copetudo a Mano</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>4,294 resortes de soporte firme copetudo a mano</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
@@ -1980,32 +1987,33 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>4,294 resortes, lana Merino y construcción copetuda a mano — alineación firme diseñada para durar décadas.</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>Enorme cantidad de 4,294 resortes con artesanía copetuda a mano para una alineación firme y duradera.</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>Sistema de 4,294 resortes</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>Varias veces los resortes de una cama estándar — soporte firme más fino y contorneado.</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AT4" t="inlineStr">
         <is>
           <t>Construcción copetuda a mano</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2063,12 +2071,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>cooling|soft|plush|pressureRelief|motionIsolation</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -2076,30 +2084,30 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Tempur-Pedic's coolest mattress — Pure Cool Plus material pulls heat away while soft TEMPUR cradles every curve.</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Soft TEMPUR contour</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>Slowly settles around pressure points instead of pushing back like coils.</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>Frescura|Suave|Espuma Viscoelástica</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
@@ -2108,20 +2116,21 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>El colchón más fresco de Tempur-Pedic — el material Pure Cool Plus disipa el calor mientras el TEMPUR suave abraza cada curva.</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr">
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr">
         <is>
           <t>Contorno TEMPUR suave</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>Se acomoda lentamente alrededor de los puntos de presión en lugar de empujar como los resortes.</t>
         </is>
@@ -2183,12 +2192,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>cooling|medium|hybrid|pressureRelief|support</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -2196,38 +2205,38 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>Cool-to-the-touch Breeze cover and Pure Cool material over a hybrid coil base — cooling plus true TEMPUR pressure relief.</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr">
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Cool-to-touch Breeze cover</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>Noticeably cooler on contact than standard TEMPUR models.</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Hybrid coil base</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>Adds airflow and a touch of responsiveness under the memory foam.</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>Frescura|Híbrido|Medio</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
@@ -2236,28 +2245,29 @@
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>Funda Breeze fresca al tacto y material Pure Cool sobre una base híbrida de resortes — frescura más el verdadero alivio de presión TEMPUR.</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr">
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr">
         <is>
           <t>Funda Breeze fresca al tacto</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>Notablemente más fresco al contacto que los modelos TEMPUR estándar.</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>Base híbrida de resortes</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>Agrega ventilación y un toque de respuesta bajo la espuma viscoelástica.</t>
         </is>
@@ -2315,12 +2325,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>plush|soft|pressureRelief|hybrid|durability</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -2334,12 +2344,12 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr">
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>Suave</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
@@ -2354,6 +2364,7 @@
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2407,12 +2418,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>medium|support|hybrid|durability|pressureRelief</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
@@ -2426,12 +2437,12 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr">
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
@@ -2446,6 +2457,7 @@
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2499,12 +2511,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>firm|support|durability|hybrid</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -2518,12 +2530,12 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr">
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>Extra Firme</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
@@ -2538,6 +2550,7 @@
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2591,12 +2604,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>cooling|medium|support|hybrid|responsive</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
@@ -2610,12 +2623,12 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr">
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>Cushion Firm</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
@@ -2630,6 +2643,7 @@
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2691,101 +2705,102 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>firm|support|zoned|hybrid|durability</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
         <is>
           <t>Individually pocketed coils that move independently, zoned for targeted support, with foam encasement around the edge.</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Patented Marvelous Middle delivers 25% more support in the center third — where your body needs it most.</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Luxury box-top comfort with firm, zoned center-third support.</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Marvelous Middle zoning</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>25% more support under hips and lower back, where most beds sag first.</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>Luxury box-top build</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>A tailored 16-inch profile with plush surface layers over a firm core.</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>Marvelous Middle|Firme|Box Top</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>Box top de lujo de 16 pulgadas con soporte firme zonificado</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
       <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr">
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr">
         <is>
           <t>Resortes embolsados individualmente que se mueven de forma independiente, zonificados para brindar soporte focalizado, con encapsulado de espuma alrededor del borde.</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>El patentado Marvelous Middle brinda 25% más soporte en el tercio central — donde tu cuerpo más lo necesita.</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>Confort box-top de lujo con soporte firme zonificado en el centro.</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>Zonificación Marvelous Middle</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>25% más soporte bajo caderas y espalda baja, donde la mayoría de las camas se hunden primero.</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AT11" t="inlineStr">
         <is>
           <t>Construcción box-top de lujo</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
         <is>
           <t>Un perfil de 16 pulgadas con capas superficiales suaves sobre un núcleo firme.</t>
         </is>
@@ -2851,97 +2866,98 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>firm|support|zoned|hybrid</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr">
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
         <is>
           <t>Rated Extra Firm — a very firm feel with little give at the surface.</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>Extra-firm hybrid support with Marvelous Middle zoning — maximum lift without giving up the luxury layers.</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>The firmest Platinum — extra-firm zoned support in a luxury build.</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Extra-firm support core</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>Noticeably firmer than the Paige Firm — for sleepers who want no sink at all.</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>Zoned center third</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr">
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>Marvelous Middle|Extra Firme|Híbrido</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>Máximo soporte con capas de confort de lujo Paige</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr">
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr">
         <is>
           <t>Nivel de confort extra firme: una sensación muy firme, con poco hundimiento en la superficie.</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>Soporte híbrido extra firme con zonificación Marvelous Middle — máxima elevación sin renunciar a las capas de lujo.</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>El Platinum más firme — soporte extra firme zonificado en construcción de lujo.</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>Núcleo de soporte extra firme</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>Notablemente más firme que el Paige Firme — para quienes no quieren hundirse nada.</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AT12" t="inlineStr">
         <is>
           <t>Tercio central zonificado</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2995,12 +3011,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>plush|soft|pressureRelief|zoned|hybrid|motionIsolation</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
@@ -3014,12 +3030,12 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr">
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>Box Top Suave</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
@@ -3034,6 +3050,7 @@
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3095,93 +3112,94 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>firm|support|zoned|hybrid|durability</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr">
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
         <is>
           <t>Rated Firm, with less give and more pushback at the surface.</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr">
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>Firm zoned support in a box-top build with lasting edge-to-edge comfort.</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>Firm with a finished top</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>Firm alignment without the bare, hard feel of a tight-top firm.</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>3-inch edge encasement</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>High-density foam rails keep the sleeping surface usable to the very edge.</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>Box Top Firme|Resortes Zonificados|Soporte de Borde</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>Confort box-top firme con soporte de resortes zonificados</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr">
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr">
         <is>
           <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr">
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr">
         <is>
           <t>Soporte firme zonificado en construcción box-top con confort de borde a borde.</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="AR14" t="inlineStr">
         <is>
           <t>Firme con acabado superior</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
+      <c r="AS14" t="inlineStr">
         <is>
           <t>Alineación firme sin la sensación dura y desnuda de un firme tight-top.</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
+      <c r="AT14" t="inlineStr">
         <is>
           <t>Encasado de borde de 3 pulgadas</t>
         </is>
       </c>
-      <c r="AT14" t="inlineStr">
+      <c r="AU14" t="inlineStr">
         <is>
           <t>Rieles de espuma de alta densidad mantienen la superficie útil hasta el borde.</t>
         </is>
@@ -3247,97 +3265,98 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>firm|cooling|support|hybrid|pressureRelief</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr">
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
         <is>
           <t>Rated Firm, with less give at the surface and a tight-top construction without a pillow-top layer.</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>A full layer of cool-gel memory foam over a firm hybrid core — pressure relief with a cooling effect and solid alignment.</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>Firm hybrid support topped with cooling gel memory foam.</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>Cool-gel memory foam layer</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>Adds cooling comfort a plain firm innerspring doesn't have.</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>Firm hybrid core</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr">
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr">
         <is>
           <t>Gel Fresco|Firme|Híbrido</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>Espuma viscoelástica con gel fresco sobre soporte híbrido firme</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr">
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr">
         <is>
           <t>Nivel de confort firme, con menos hundimiento en la superficie y una construcción tight top sin capa tipo pillow top.</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr">
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr">
         <is>
           <t>Una capa completa de espuma con gel fresco sobre un núcleo híbrido firme — alivio de presión con efecto refrescante y alineación sólida.</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="AQ15" t="inlineStr">
         <is>
           <t>Soporte híbrido firme coronado con espuma viscoelástica de gel fresco.</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr">
+      <c r="AR15" t="inlineStr">
         <is>
           <t>Capa de espuma con gel fresco</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
+      <c r="AS15" t="inlineStr">
         <is>
           <t>Agrega confort refrescante que un firme de resortes común no tiene.</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
+      <c r="AT15" t="inlineStr">
         <is>
           <t>Núcleo híbrido firme</t>
         </is>
       </c>
-      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3391,69 +3410,70 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>medium|cooling|pressureRelief|hybrid|support</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
         <is>
           <t>Rated Medium — a balanced feel between plush and firm.</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr">
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
         <is>
           <t>Crowd-pleasing medium</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>The feel most couples agree on — balanced give and support.</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr">
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr">
         <is>
           <t>Medio|Híbrido</t>
         </is>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr">
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr">
         <is>
           <t>Nivel de confort medio: una sensación equilibrada entre suave y firme.</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr">
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr">
         <is>
           <t>Medio que agrada a todos</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
+      <c r="AS16" t="inlineStr">
         <is>
           <t>La sensación en la que la mayoría de las parejas están de acuerdo — equilibrio entre suavidad y soporte.</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3507,61 +3527,62 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>plush|soft|cooling|pressureRelief|hybrid</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
         <is>
           <t>Rated Plush — a softer feel with more give at the surface.</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr">
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>Supported softness</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr">
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>Suave|Híbrido</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr">
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr">
         <is>
           <t>Nivel de confort suave: una sensación más suave, con más hundimiento en la superficie.</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr">
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr">
         <is>
           <t>Suavidad con soporte</t>
         </is>
       </c>
-      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3619,89 +3640,90 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>firm|support|zoned|hybrid</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr">
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
         <is>
           <t>Rated Firm, with less give and more pushback at the surface.</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr">
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Zoned firm support with a euro-top finish — firm without feeling bare.</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>Euro-top over firm coils</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>A sewn-under cushion layer takes the edge off a true firm feel.</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AD18" t="inlineStr">
         <is>
           <t>Thicker center-third coils</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AE18" t="inlineStr">
         <is>
           <t>Restonic's signature zoning holds hips level where beds break down first.</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>Marvelous Middle|Firme|Euro Top</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
       <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr">
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr">
         <is>
           <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr">
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr">
         <is>
           <t>Soporte firme zonificado con acabado euro-top — firme sin sentirse desnudo.</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr">
+      <c r="AR18" t="inlineStr">
         <is>
           <t>Euro-top sobre resortes firmes</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
+      <c r="AS18" t="inlineStr">
         <is>
           <t>Una capa de cojín cosida por debajo suaviza la sensación de un firme verdadero.</t>
         </is>
       </c>
-      <c r="AS18" t="inlineStr">
+      <c r="AT18" t="inlineStr">
         <is>
           <t>Resortes centrales más gruesos</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
+      <c r="AU18" t="inlineStr">
         <is>
           <t>La zonificación distintiva de Restonic mantiene las caderas niveladas donde las camas fallan primero.</t>
         </is>
@@ -3767,12 +3789,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>medium|motionIsolation|pressureRelief|hybrid|support</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
@@ -3780,39 +3802,39 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>Layers of conforming foam over wrapped coils — balanced medium comfort that absorbs a partner's movement.</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr">
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>Wrapped-coil motion isolation</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr">
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>Conforming comfort layers</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
+      <c r="AE19" t="inlineStr">
         <is>
           <t>Foam layers contour without the deep sink of memory-foam beds.</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>Híbrido|Medio|Aislamiento de Movimiento</t>
         </is>
       </c>
-      <c r="AF19" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>Medio de lujo que se adapta y permanece quieto toda la noche</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr"/>
@@ -3820,24 +3842,25 @@
       <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr">
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr">
         <is>
           <t>Capas de espuma adaptable sobre resortes envueltos — confort medio equilibrado que absorbe el movimiento de la pareja.</t>
         </is>
       </c>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr">
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr">
         <is>
           <t>Aislamiento de movimiento con resortes envueltos</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr">
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr">
         <is>
           <t>Capas de confort adaptables</t>
         </is>
       </c>
-      <c r="AT19" t="inlineStr">
+      <c r="AU19" t="inlineStr">
         <is>
           <t>Las capas de espuma se contornean sin el hundimiento profundo de las camas viscoelásticas.</t>
         </is>
@@ -3903,12 +3926,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>firm|support|zoned|hybrid|durability</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
@@ -3918,37 +3941,37 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>Extra-firm tight top</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>A flat, supportive surface with no plush give — for sleepers who want solid.</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
+      <c r="AD20" t="inlineStr">
         <is>
           <t>Zoned center support</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
+      <c r="AE20" t="inlineStr">
         <is>
           <t>Thicker center coils protect the firm feel from early body impressions.</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AF20" t="inlineStr">
         <is>
           <t>Marvelous Middle|Extra Firme|Tight Top</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>Soporte extra firme zonificado a un precio accesible</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
@@ -3958,22 +3981,23 @@
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr">
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr">
         <is>
           <t>Tight top extra firme</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
+      <c r="AS20" t="inlineStr">
         <is>
           <t>Una superficie plana y de soporte sin suavidad — para quienes quieren algo sólido.</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
+      <c r="AT20" t="inlineStr">
         <is>
           <t>Soporte central zonificado</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
+      <c r="AU20" t="inlineStr">
         <is>
           <t>Resortes centrales más gruesos protegen la firmeza de las marcas corporales tempranas.</t>
         </is>
@@ -4039,12 +4063,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>plush|soft|pressureRelief</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
@@ -4052,43 +4076,43 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>A 12.5-inch plush build that cushions shoulders and hips — easy softness at a price that makes sense.</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>True plush surface</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>Softer than the Gracie — made for sleepers who want cushion first.</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>Everyday value</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>Restonic quality without the Platinum price.</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>Suave|12.5 Pulgadas|Valor</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>Suavidad acogedora a un precio cotidiano</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
@@ -4096,28 +4120,29 @@
       <c r="AL21" t="inlineStr"/>
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr">
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr">
         <is>
           <t>Una construcción suave de 12.5 pulgadas que acolcha hombros y caderas — suavidad fácil a un precio razonable.</t>
         </is>
       </c>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr">
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr">
         <is>
           <t>Superficie verdaderamente suave</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
+      <c r="AS21" t="inlineStr">
         <is>
           <t>Más suave que el Gracie — hecho para quienes buscan acolchado primero.</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
+      <c r="AT21" t="inlineStr">
         <is>
           <t>Valor cotidiano</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr">
+      <c r="AU21" t="inlineStr">
         <is>
           <t>Calidad Restonic sin el precio Platinum.</t>
         </is>
@@ -4183,101 +4208,102 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>firm|support|durability</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr">
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
         <is>
           <t>Rated Firm, with less give and more pushback at the surface.</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>A no-nonsense 12.5-inch firm that keeps your spine aligned — dependable support night after night.</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>Dependable firm alignment at an everyday price.</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>Straightforward firm feel</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>Solid support without plush layers softening the surface.</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>Everyday value</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr">
+      <c r="AE22" t="inlineStr">
         <is>
           <t>The affordable path to a true firm mattress.</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AF22" t="inlineStr">
         <is>
           <t>Firme|12.5 Pulgadas|Valor</t>
         </is>
       </c>
-      <c r="AF22" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>Soporte firme directo a un precio cotidiano</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr">
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr">
         <is>
           <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr">
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr">
         <is>
           <t>Un firme de 12.5 pulgadas sin rodeos que mantiene tu columna alineada — soporte confiable noche tras noche.</t>
         </is>
       </c>
-      <c r="AP22" t="inlineStr">
+      <c r="AQ22" t="inlineStr">
         <is>
           <t>Alineación firme confiable a precio cotidiano.</t>
         </is>
       </c>
-      <c r="AQ22" t="inlineStr">
+      <c r="AR22" t="inlineStr">
         <is>
           <t>Sensación firme directa</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
+      <c r="AS22" t="inlineStr">
         <is>
           <t>Soporte sólido sin capas suaves que ablanden la superficie.</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
+      <c r="AT22" t="inlineStr">
         <is>
           <t>Valor cotidiano</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr">
+      <c r="AU22" t="inlineStr">
         <is>
           <t>El camino accesible a un colchón firme verdadero.</t>
         </is>
@@ -4343,12 +4369,12 @@
           <t>no</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>medium|hybrid|support|durability|pressureRelief</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
@@ -4356,47 +4382,47 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>Thirty years of Kingdom Mattress family know-how in a euro-top hybrid engineered entirely in the USA.</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>A family-company euro-top hybrid built to take years of real life.</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>Euro-top comfort layer</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>A cushioned top the plain Genesis Firm doesn't have.</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
+      <c r="AD23" t="inlineStr">
         <is>
           <t>Built-to-last engineering</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr">
+      <c r="AE23" t="inlineStr">
         <is>
           <t>Designed by a 30-year family company for durability first.</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AF23" t="inlineStr">
         <is>
           <t>Híbrido|Euro Top|Hecho en EE. UU.</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>Híbrido euro-top de empresa familiar, diseñado en EE. UU.</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr"/>
@@ -4404,32 +4430,33 @@
       <c r="AL23" t="inlineStr"/>
       <c r="AM23" t="inlineStr"/>
       <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr">
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr">
         <is>
           <t>Treinta años de experiencia familiar de Kingdom Mattress en un híbrido euro-top diseñado completamente en EE. UU.</t>
         </is>
       </c>
-      <c r="AP23" t="inlineStr">
+      <c r="AQ23" t="inlineStr">
         <is>
           <t>Un híbrido euro-top de empresa familiar hecho para aguantar años de vida real.</t>
         </is>
       </c>
-      <c r="AQ23" t="inlineStr">
+      <c r="AR23" t="inlineStr">
         <is>
           <t>Capa de confort euro-top</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
+      <c r="AS23" t="inlineStr">
         <is>
           <t>Una superficie acolchada que el Genesis Firme no tiene.</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="AT23" t="inlineStr">
         <is>
           <t>Ingeniería para durar</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr">
+      <c r="AU23" t="inlineStr">
         <is>
           <t>Diseñado por una empresa familiar de 30 años con la durabilidad primero.</t>
         </is>
@@ -4495,101 +4522,102 @@
           <t>no</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>firm|hybrid|support|durability</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr">
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
         <is>
           <t>Rated Firm, with less give and more pushback at the surface.</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>A firm hybrid engineered entirely in the USA by a 30-year family company — solid support at the best value in the store.</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>Firm hybrid support, family-built and priced to make sense.</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>Firm hybrid core</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>Coil support with a firm surface — more responsive than foam value beds.</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
+      <c r="AD24" t="inlineStr">
         <is>
           <t>Best-value firm</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr">
+      <c r="AE24" t="inlineStr">
         <is>
           <t>The most affordable true firm hybrid in the lineup.</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AF24" t="inlineStr">
         <is>
           <t>Híbrido|Firme|Hecho en EE. UU.</t>
         </is>
       </c>
-      <c r="AF24" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>Híbrido firme de empresa familiar al mejor valor</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr">
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr">
         <is>
           <t>Nivel de confort firme, con menos hundimiento y más empuje en la superficie.</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr">
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr">
         <is>
           <t>Un híbrido firme diseñado completamente en EE. UU. por una empresa familiar de 30 años — soporte sólido al mejor valor de la tienda.</t>
         </is>
       </c>
-      <c r="AP24" t="inlineStr">
+      <c r="AQ24" t="inlineStr">
         <is>
           <t>Soporte híbrido firme, de empresa familiar y a un precio razonable.</t>
         </is>
       </c>
-      <c r="AQ24" t="inlineStr">
+      <c r="AR24" t="inlineStr">
         <is>
           <t>Núcleo híbrido firme</t>
         </is>
       </c>
-      <c r="AR24" t="inlineStr">
+      <c r="AS24" t="inlineStr">
         <is>
           <t>Soporte de resortes con superficie firme — más receptivo que las camas de espuma de valor.</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr">
+      <c r="AT24" t="inlineStr">
         <is>
           <t>Firme del mejor valor</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr">
+      <c r="AU24" t="inlineStr">
         <is>
           <t>El híbrido firme verdadero más accesible de la línea.</t>
         </is>
@@ -4651,65 +4679,66 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>plush|soft|pressureRelief|zoned</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr">
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
         <is>
           <t>Rated Plush — a softer feel with more give at the surface.</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr">
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>3-inch edge encasement</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
+      <c r="AE25" t="inlineStr">
         <is>
           <t>High-density foam rails give a bigger usable sleep surface than value plush beds.</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AF25" t="inlineStr">
         <is>
           <t>Marvelous Middle|Suave|Para Dormir de Lado</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr">
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr">
         <is>
           <t>Nivel de confort suave: una sensación más suave, con más hundimiento en la superficie.</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr"/>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr"/>
       <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr">
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr">
         <is>
           <t>Encasado de borde de 3 pulgadas</t>
         </is>
       </c>
-      <c r="AT25" t="inlineStr">
+      <c r="AU25" t="inlineStr">
         <is>
           <t>Rieles de espuma de alta densidad dan más superficie útil que las camas suaves de valor.</t>
         </is>
@@ -4775,93 +4804,94 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>firm|support|zoned|hybrid</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr">
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
         <is>
           <t>Rated Extra Firm — a very firm feel with little give at the surface.</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr">
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>The value path to real extra-firm zoned support.</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>Value extra-firm</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>The firmest feel in the bronze tier — no plush give at all.</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>Zoned hybrid core</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr">
+      <c r="AE26" t="inlineStr">
         <is>
           <t>Center-third reinforcement most value firm beds skip.</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AF26" t="inlineStr">
         <is>
           <t>Marvelous Middle|Extra Firme|Híbrido</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>Soporte híbrido extra firme a precio de valor</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr">
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr">
         <is>
           <t>Nivel de confort extra firme: una sensación muy firme, con poco hundimiento en la superficie.</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr">
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr">
         <is>
           <t>El camino de valor al verdadero soporte extra firme zonificado.</t>
         </is>
       </c>
-      <c r="AQ26" t="inlineStr">
+      <c r="AR26" t="inlineStr">
         <is>
           <t>Extra firme de valor</t>
         </is>
       </c>
-      <c r="AR26" t="inlineStr">
+      <c r="AS26" t="inlineStr">
         <is>
           <t>La sensación más firme del nivel bronce — sin nada de suavidad.</t>
         </is>
       </c>
-      <c r="AS26" t="inlineStr">
+      <c r="AT26" t="inlineStr">
         <is>
           <t>Núcleo híbrido zonificado</t>
         </is>
       </c>
-      <c r="AT26" t="inlineStr">
+      <c r="AU26" t="inlineStr">
         <is>
           <t>Refuerzo del tercio central que la mayoría de las camas firmes de valor omiten.</t>
         </is>
@@ -4927,101 +4957,102 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>medium|support|zoned|responsive</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
         <is>
           <t>Rated Medium — a balanced feel between plush and firm.</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>A balanced medium innerspring with Restonic's thicker center coils — real quality at the friendliest price in the store.</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>Easy balanced comfort with zoned support — the smart starter pick.</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>Responsive innerspring feel</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>Classic coil bounce that's easy to move on — no stuck-in-foam feeling.</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>Friendliest price</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr">
+      <c r="AE27" t="inlineStr">
         <is>
           <t>The most affordable way into a zoned Restonic build.</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AF27" t="inlineStr">
         <is>
           <t>Resortes|Medio|Mejor Valor</t>
         </is>
       </c>
-      <c r="AF27" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>Confort medio equilibrado al precio más amigable</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr">
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr">
         <is>
           <t>Nivel de confort medio: una sensación equilibrada entre suave y firme.</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr">
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr">
         <is>
           <t>Un colchón de resortes medio equilibrado con los resortes centrales más gruesos de Restonic — calidad real al precio más amigable de la tienda.</t>
         </is>
       </c>
-      <c r="AP27" t="inlineStr">
+      <c r="AQ27" t="inlineStr">
         <is>
           <t>Confort equilibrado fácil con soporte zonificado — la elección inteligente para empezar.</t>
         </is>
       </c>
-      <c r="AQ27" t="inlineStr">
+      <c r="AR27" t="inlineStr">
         <is>
           <t>Sensación de resortes receptiva</t>
         </is>
       </c>
-      <c r="AR27" t="inlineStr">
+      <c r="AS27" t="inlineStr">
         <is>
           <t>Rebote clásico de resortes fácil para moverse — sin sensación de quedar atrapado en espuma.</t>
         </is>
       </c>
-      <c r="AS27" t="inlineStr">
+      <c r="AT27" t="inlineStr">
         <is>
           <t>El precio más amigable</t>
         </is>
       </c>
-      <c r="AT27" t="inlineStr">
+      <c r="AU27" t="inlineStr">
         <is>
           <t>La forma más accesible de entrar a una construcción Restonic zonificada.</t>
         </is>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -5069,7 +5069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5105,80 +5105,85 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Description (ES)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Image File Name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Match Tags</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Score: Default</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Score: Cooling</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Score: Hot</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Score: Back Pain</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Score: Snoring</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Score: Reflux</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Score: Premium</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Score: Position Side</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Score: Position Back</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Score: Position Stomach</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Score: Allergies</t>
         </is>
@@ -5215,35 +5220,33 @@
           <t>adjustable</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>899</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Adjustable power base with head &amp; foot articulation, wireless remote, and programmable memory positions.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Base eléctrica ajustable con elevación de cabeza y pies, control inalámbrico y posiciones de memoria programables.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>images/accessories/base-bt2000.jpg</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>snoring, reflux, back_pain</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>3</v>
       </c>
@@ -5251,12 +5254,15 @@
         <v>3</v>
       </c>
       <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5289,48 +5295,49 @@
           <t>adjustable</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>1099</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Adjustable base with head &amp; foot massage, 5 vibration modes, one-touch flat, and wireless remote with presets.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Base ajustable con masaje de cabeza y pies, 5 modos de vibración, regreso plano de un toque y control inalámbrico con posiciones predeterminadas.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>images/accessories/base-bt3000.jpg</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>snoring, reflux, back_pain</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
         <v>4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3</v>
       </c>
       <c r="Q3" t="n">
         <v>3</v>
       </c>
       <c r="R3" t="n">
+        <v>3</v>
+      </c>
+      <c r="S3" t="n">
         <v>2</v>
       </c>
-      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5363,35 +5370,33 @@
           <t>adjustable</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>1599</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Premium adjustable base with lumbar support and a virtually unlimited range of head &amp; foot positions, including Zero Gravity.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Base ajustable premium con soporte lumbar y un rango casi ilimitado de posiciones de cabeza y pies, incluida Gravedad Cero.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>images/accessories/base-tempur-ergo.jpg</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>snoring, reflux, back_pain</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>4</v>
       </c>
@@ -5399,12 +5404,15 @@
         <v>4</v>
       </c>
       <c r="R4" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" t="n">
         <v>3</v>
       </c>
-      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5437,33 +5445,33 @@
           <t>foundation</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>499</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>9-inch wood foundation engineered to support your mattress edge to edge and extend its life.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Base de madera de 9 pulgadas diseñada para soportar tu colchón de borde a borde y extender su vida útil.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>images/accessories/foundation-princess.jpg</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>2</v>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -5473,6 +5481,7 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5501,48 +5510,49 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>108</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Performance pillow with a soft t-shirt-like cover and airflow design for cooler, better-supported sleep.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Almohada de alto rendimiento con funda suave tipo camiseta y diseño de ventilación para dormir más fresco y con mejor soporte.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>images/accessories/pillow-flow.jpg</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>cooling, hot_sleeper, all, all_positions</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
         <v>3</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
       <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5571,31 +5581,29 @@
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>99</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Cool-gel memory foam that softens and adjusts to your neck, taking pressure off your spine without overheating.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Espuma viscoelástica con gel fresco que se suaviza y se ajusta a tu cuello, quitando presión de la columna sin sobrecalentarte.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>images/accessories/pillow-gel-memory.jpg</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>cooling, hot_sleeper, all, all_positions</t>
         </is>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
@@ -5603,16 +5611,19 @@
       <c r="N7" t="n">
         <v>2</v>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5641,44 +5652,45 @@
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
         <v>149</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Moisture-wicking, breathable protection that keeps you dry and comfortable while guarding against spills.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Protección transpirable que absorbe la humedad, te mantiene seco y cómodo y protege contra derrames.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>images/accessories/protector-dritec.jpg</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>all, allergies, spills, everyday</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5709,33 +5721,33 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
         <v>89</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Simple, breathable everyday protection against spills and dust — comfort without compromise.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Protección diaria sencilla y transpirable contra derrames y polvo — confort sin compromisos.</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>images/accessories/protector-iprotect.jpg</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>all, allergies, spills, everyday</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -5744,7 +5756,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5775,39 +5788,39 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
         <v>249</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Instant-cooling top fabric for hot sleepers, with a Powerband fit that guards against spills without changing the feel.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Tela superior de enfriamiento instantáneo para quienes duermen con calor, con ajuste Powerband que protege contra derrames sin cambiar la sensación.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>images/accessories/protector-vertex.jpg</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>cooling, hot_sleeper, spills, everyday</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -5815,6 +5828,7 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5843,44 +5857,45 @@
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
         <v>189</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Cooling, moisture-wicking protector with SurfaceGuard technology and a 10-year warranty.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Protector refrescante que absorbe la humedad, con tecnología SurfaceGuard y garantía de 10 años.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>images/accessories/protector-tempur.jpg</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>all, allergies, spills, everyday</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
         <v>2</v>
       </c>
-      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
         <v>1</v>
       </c>
     </row>

--- a/incoming/Lacks_Store_Data.xlsx
+++ b/incoming/Lacks_Store_Data.xlsx
@@ -6929,7 +6929,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"quiz":{"questions":[{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"We carry your selected size into the consultation. Your sleep-fit ranking is based on your comfort and support answers.","es":"Tomamos en cuenta el tamaño que elijas en la consulta. El orden de tus opciones se basa en tus respuestas sobre comodidad y soporte."},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"This shapes the questions that follow and what we suggest testing together.","es":"Esto define las preguntas que siguen y lo que sugerimos probar juntos."},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"The more movement wakes you, the more it shapes your matches and what we suggest testing.","es":"Cuanto más te despierte el movimiento, más influye en tus opciones y en lo que sugerimos probar."},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"This helps us favor pressure relief, support, or a responsive feel.","es":"Esto nos ayuda a priorizar alivio de presión, soporte o una sensación con más respuesta."},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"If you sleep hot, we favor cooling features in your matches.","es":"Si duermes con calor, priorizamos materiales refrescantes en tus opciones."},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to the feel you prefer.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. These shape which features we favor and what we suggest testing.","es":"Toca lo que hayas notado. Esto define qué características priorizamos y qué sugerimos probar."},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durable":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. Some shape your matches; some change what we suggest trying, like an adjustable base or a mattress protector.","es":"Toca lo que aplique. Algunas influyen en tus opciones; otras cambian lo que sugerimos probar, como una base ajustable o un protector de colchón."},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durable":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
+          <t>{"quiz":{"questions":[{"id":"mattress_size","category":{"en":"Getting Started","es":"Para Empezar"},"question":{"en":"What size mattress are you looking for?","es":"¿Qué tamaño de colchón buscas?"},"helpText":{"en":"We carry your selected size into the consultation. Your sleep-fit ranking is based on your comfort and support answers.","es":"Tomamos en cuenta el tamaño que elijas en la consulta. El orden de tus opciones se basa en tus respuestas sobre comodidad y soporte."},"type":"single","options":[{"id":"twin","label":{"en":"Twin","es":"Twin"},"icon":"solo","sublabel":{"en":"Kids or tight spaces","es":"Niños o espacios pequeños"},"scores":{}},{"id":"twin_xl","label":{"en":"Twin XL","es":"Twin XL"},"icon":"solo","sublabel":{"en":"Extra length, single sleeper","es":"Largo extra, una persona"},"scores":{}},{"id":"full","label":{"en":"Full","es":"Full"},"icon":"solo","sublabel":{"en":"Solo or cozy pair","es":"Solo o pareja cómoda"},"scores":{}},{"id":"queen","label":{"en":"Queen","es":"Queen"},"icon":"partner","sublabel":{"en":"Most popular size","es":"El tamaño más popular"},"scores":{}},{"id":"king","label":{"en":"King","es":"King"},"icon":"family","sublabel":{"en":"Maximum space","es":"Espacio máximo"},"scores":{}},{"id":"cal_king","label":{"en":"Cal King","es":"Cal King"},"icon":"family","sublabel":{"en":"Extra length","es":"Largo extra"},"scores":{}}]},{"id":"partner_sleep","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Who's sharing the bed with you?","es":"¿Quién comparte la cama contigo?"},"helpText":{"en":"This shapes the questions that follow and what we suggest testing together.","es":"Esto define las preguntas que siguen y lo que sugerimos probar juntos."},"type":"single","options":[{"id":"solo","label":{"en":"Solo Sleeper","es":"Duermo Solo"},"icon":"solo","sublabel":{"en":"Just me","es":"Solo yo"},"scores":{}},{"id":"partner","label":{"en":"With a Partner","es":"Con Pareja"},"icon":"partner","sublabel":{"en":"Sharing the bed","es":"Compartimos la cama"},"scores":{"motionIsolation":2}},{"id":"family","label":{"en":"Family Bed","es":"Cama Familiar"},"icon":"family","sublabel":{"en":"Kids, pets, or both","es":"Niños, mascotas, o ambos"},"scores":{"durability":2,"motionIsolation":1}}]},{"id":"partner_disturbance","category":{"en":"Who's With You","es":"Quién Está Contigo"},"question":{"en":"Does your partner's movement wake you up?","es":"¿El movimiento de tu pareja te despierta?"},"helpText":{"en":"The more movement wakes you, the more it shapes your matches and what we suggest testing.","es":"Cuanto más te despierte el movimiento, más influye en tus opciones y en lo que sugerimos probar."},"type":"single","skipIf":{"question":"partner_sleep","answer":"solo"},"options":[{"id":"yes_often","label":{"en":"Yes, Often","es":"Sí, Seguido"},"icon":"motion","sublabel":{"en":"Every movement wakes me","es":"Cada movimiento me despierta"},"scores":{"motionIsolation":4,"hybrid":3,"memory":2}},{"id":"sometimes","label":{"en":"Sometimes","es":"A Veces"},"icon":"combo","sublabel":{"en":"Bigger movements bother me","es":"Los movimientos grandes me molestan"},"scores":{"motionIsolation":3,"hybrid":2}},{"id":"rarely","label":{"en":"Rarely","es":"Rara Vez"},"icon":"check","sublabel":{"en":"Light sleeper but mostly fine","es":"Sueño ligero pero generalmente bien"},"scores":{"motionIsolation":1}},{"id":"not_applicable","label":{"en":"Doesn't Apply","es":"No Aplica"},"icon":"solo","sublabel":{"en":"I sleep alone","es":"Duermo solo"},"scores":{}}]},{"id":"sleep_position","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"How do you usually sleep?","es":"¿Cómo duermes normalmente?"},"helpText":{"en":"This helps us favor pressure relief, support, or a responsive feel.","es":"Esto nos ayuda a priorizar alivio de presión, soporte o una sensación con más respuesta."},"type":"single","options":[{"id":"side","label":{"en":"Side Sleeper","es":"De Lado"},"icon":"side","sublabel":{"en":"Curled up","es":"Acurrucado"},"scores":{"plush":2,"pressureRelief":2,"soft":1}},{"id":"back","label":{"en":"Back Sleeper","es":"Boca Arriba"},"icon":"back","sublabel":{"en":"Flat on back","es":"Acostado de espalda"},"scores":{"support":2,"medium":2,"zoned":1}},{"id":"stomach","label":{"en":"Stomach Sleeper","es":"Boca Abajo"},"icon":"stomach","sublabel":{"en":"Face down","es":"Boca abajo"},"scores":{"firm":2,"support":1}},{"id":"combo","label":{"en":"Combination","es":"Combinación"},"icon":"combo","sublabel":{"en":"Move around","es":"Me muevo mucho"},"scores":{"medium":2,"responsive":2}},{"id":"no_idea","label":{"en":"Not Sure","es":"No Estoy Seguro"},"icon":"question","sublabel":{"en":"I wake up in weird positions","es":"Me despierto en posiciones raras"},"scores":{"medium":2,"responsive":2}}]},{"id":"body_type","category":{"en":"About You","es":"Sobre Ti"},"question":{"en":"What weight range should this mattress support?","es":"¿Qué rango de peso debe soportar este colchón?"},"helpText":{"en":"This helps us account for cushioning, support, and durability.","es":"Esto nos ayuda a considerar la amortiguación, el soporte y la durabilidad."},"type":"single","options":[{"id":"petite","label":{"en":"Under 130 lbs","es":"Menos de 130 lbs"},"icon":"cloud","sublabel":{"en":"Light support","es":"Soporte ligero"},"scores":{"plush":2,"soft":1}},{"id":"average","label":{"en":"130 to 200 lbs","es":"130 a 200 lbs"},"icon":"weight","sublabel":{"en":"Standard support","es":"Soporte estándar"},"scores":{"medium":2}},{"id":"athletic","label":{"en":"200 to 230 lbs","es":"200 a 230 lbs"},"icon":"support","sublabel":{"en":"Medium-firm support","es":"Soporte medio-firme"},"scores":{"support":2,"medium":1,"responsive":1}},{"id":"plus","label":{"en":"Over 230 lbs","es":"Más de 230 lbs"},"icon":"support","sublabel":{"en":"Maximum support","es":"Soporte máximo"},"scores":{"firm":2,"support":3,"hybrid":2,"durability":2}},{"id":"different","label":{"en":"Different weight ranges","es":"Rangos de peso diferentes"},"icon":"partner","sublabel":{"en":"Sleepers fall into different ranges","es":"Los durmientes están en rangos diferentes"},"scores":{"medium":2,"support":1,"motionIsolation":2},"hideIf":{"question":"partner_sleep","answer":"solo"}}],"copyVariants":[{"when":{"question":"partner_sleep","answerIn":["partner","family"]},"question":{"en":"What weight range should we match for the sleeper who needs more support?","es":"¿Para qué rango de peso debemos ajustar, según quien necesite más soporte?"},"helpText":{"en":"If you fall into different ranges, choose “Different weight ranges.”","es":"Si están en rangos diferentes, elige “Rangos de peso diferentes”."}}]},{"id":"temperature","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"How do you sleep temperature-wise?","es":"¿Cómo duermes en cuanto a temperatura?"},"helpText":{"en":"If you sleep hot, we favor cooling features in your matches.","es":"Si duermes con calor, priorizamos materiales refrescantes en tus opciones."},"type":"single","options":[{"id":"hot","label":{"en":"I Sleep Hot","es":"Duermo con Calor"},"icon":"flame","sublabel":{"en":"Night sweats, kick off covers","es":"Sudores nocturnos, quito las cobijas"},"scores":{"cooling":3,"hybrid":2}},{"id":"comfortable","label":{"en":"I'm Comfortable","es":"Estoy Cómodo"},"icon":"smile","sublabel":{"en":"No temperature issues","es":"Sin problemas de temperatura"},"scores":{}},{"id":"cold","label":{"en":"I Sleep Cold","es":"Duermo con Frío"},"icon":"snowflake","sublabel":{"en":"Need blankets to warm up","es":"Necesito cobijas para calentarme"},"scores":{"memory":1,"plush":1}},{"id":"opposite","label":{"en":"We're Opposite","es":"Somos Opuestos"},"icon":"hotcold","sublabel":{"en":"One hot, one cold","es":"Uno con calor, otro con frío"},"scores":{"cooling":2,"hybrid":1},"hideIf":{"question":"partner_sleep","answer":"solo"}}]},{"id":"firmness","category":{"en":"What You Like","es":"Lo Que Te Gusta"},"question":{"en":"What firmness level do you prefer?","es":"¿Qué nivel de firmeza prefieres?"},"helpText":{"en":"No wrong answer here, just slide to the feel you prefer.","es":"Desliza a tu comodidad ideal"},"type":"slider","min":1,"max":10,"defaultValue":5,"labels":[{"en":"Soft — Sink right in","es":"Suave — Hundirse"},{"en":"Medium","es":"Medio"},{"en":"Firm — Solid support","es":"Firme — Soporte sólido"}]},{"id":"sleep_issues","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Any issues with your current mattress?","es":"¿Algún problema con tu colchón actual?"},"helpText":{"en":"Tap anything you've noticed. These shape which features we favor and what we suggest testing.","es":"Toca lo que hayas notado. Esto define qué características priorizamos y qué sugerimos probar."},"type":"multiple","options":[{"id":"back_pain","label":{"en":"Back Pain","es":"Dolor de Espalda"},"icon":"spine","sublabel":{"en":"Lower or upper back","es":"Espalda baja o alta"},"scores":{"support":3,"zoned":2,"firm":1}},{"id":"hip_pain","label":{"en":"Hip or Shoulder Pain","es":"Dolor de Cadera u Hombro"},"icon":"pressure","sublabel":{"en":"Pressure points","es":"Puntos de presión"},"scores":{"pressureRelief":3,"plush":2}},{"id":"hot","label":{"en":"Sleeping Too Hot","es":"Mucho Calor al Dormir"},"icon":"flame","sublabel":{"en":"Night sweats, overheating","es":"Sudores nocturnos, sobrecalentamiento"},"scores":{"cooling":3,"hybrid":2}},{"id":"tossing","label":{"en":"Tossing &amp; Turning","es":"Dando Vueltas"},"icon":"combo","sublabel":{"en":"Can't get comfortable","es":"No encuentro comodidad"},"scores":{"comfort":2,"medium":1}},{"id":"stiff","label":{"en":"Waking Up Stiff or Sore","es":"Despertar Rígido o Adolorido"},"icon":"stiff","sublabel":{"en":"Morning aches","es":"Dolores matutinos"},"scores":{"pressureRelief":2,"comfort":2}},{"id":"sagging","label":{"en":"Mattress Sagging","es":"Colchón Hundido"},"icon":"sagging","sublabel":{"en":"Dips or indentations","es":"Hundimientos"},"scores":{"durability":2,"quality":2}},{"id":"too_soft","label":{"en":"Mattress Too Soft","es":"Colchón Muy Suave"},"icon":"couch","sublabel":{"en":"Sinking in too much","es":"Me hundo demasiado"},"scores":{"firm":3,"support":2}},{"id":"none","label":{"en":"No Major Issues","es":"Sin Problemas Grandes"},"icon":"check","sublabel":{"en":"Just time for an upgrade","es":"Solo es hora de un cambio"},"scores":{"comfort":1,"quality":1,"durability":1}}]},{"id":"health_conditions","category":{"en":"What You're Solving","es":"Lo Que Buscas Resolver"},"question":{"en":"Anything else going on that affects your sleep?","es":"¿Algo más que afecte tu sueño?"},"helpText":{"en":"Tap any that apply. Some shape your matches; some change what we suggest trying, like an adjustable base or a mattress protector.","es":"Toca lo que aplique. Algunas influyen en tus opciones; otras cambian lo que sugerimos probar, como una base ajustable o un protector de colchón."},"type":"multiple","options":[{"id":"nerve_pain","label":{"en":"Nerve Pain or Tingling","es":"Dolor Nervioso u Hormigueo"},"icon":"lightning","sublabel":{"en":"Shooting pain, numbness","es":"Dolor punzante, entumecimiento"},"scores":{"support":3,"firm":2,"zoned":2}},{"id":"allergies","label":{"en":"Allergies","es":"Alergias"},"icon":"sneeze","sublabel":{"en":"Dust, sneezing, stuffy","es":"Polvo, estornudos, congestión"},"scores":{"hypoallergenic":3}},{"id":"snoring","label":{"en":"Snoring or Sleep Apnea","es":"Ronquidos o Apnea del Sueño"},"icon":"snore","sublabel":{"en":"You or your partner","es":"Tú o tu pareja"},"scores":{"adjustable":3}},{"id":"reflux","label":{"en":"Acid Reflux / Heartburn","es":"Reflujo Ácido / Acidez"},"icon":"flame","sublabel":{"en":"Burns when lying down","es":"Arde al acostarse"},"scores":{"adjustable":3}},{"id":"extra_support","label":{"en":"Need Extra Support","es":"Necesito Soporte Extra"},"icon":"weight","sublabel":{"en":"Larger build or heavier weight","es":"Complexión grande o peso mayor"},"scores":{"support":3,"firm":2,"durability":3}},{"id":"getting_older","label":{"en":"Changing Needs","es":"Necesidades Cambiantes"},"icon":"aging","sublabel":{"en":"Looking for gentler support","es":"Buscando soporte más suave"},"scores":{"support":2,"comfort":2,"pressureRelief":1}},{"id":"none","label":{"en":"None of These","es":"Ninguno de Estos"},"icon":"check","sublabel":{"en":"I'm good","es":"Estoy bien"},"scores":{}}]}]}}</t>
         </is>
       </c>
     </row>
